--- a/LSC_Update_System.xlsx
+++ b/LSC_Update_System.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CH\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CH\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A28B64F2-693E-44E4-AB5C-4FC30CF8980C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF2BADAB-34A9-4236-A91F-295B029133B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="START HERE" sheetId="1" r:id="rId1"/>
@@ -383,10 +383,10 @@
     <t>next_opponent</t>
   </si>
   <si>
-    <t>Bayern München 5 - VfB Stuttgart 1</t>
-  </si>
-  <si>
     <t>Schalke FC</t>
+  </si>
+  <si>
+    <t>Bayern München 1 - VfB Stuttgart 5</t>
   </si>
 </sst>
 </file>
@@ -1044,6 +1044,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1532,10 +1533,10 @@
         <v>65</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I7" s="5"/>
       <c r="J7" s="6" t="str">
@@ -1544,27 +1545,27 @@
       </c>
       <c r="K7" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>Defence</v>
+        <v>Transfer</v>
       </c>
       <c r="L7" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>Bayern München</v>
+        <v>VfB Stuttgart</v>
       </c>
       <c r="M7" s="8">
         <f>IF(B7="","",IF(K7="Transfer",C7,IFERROR(LOOKUP(2,1/($B$2:B6=B7),$M$2:M6),VLOOKUP(B7,Baseline!$A$2:$H$10,5,FALSE))))</f>
-        <v>46081</v>
+        <v>46262</v>
       </c>
       <c r="N7" s="6">
         <f>IF(B7="","",IF(K7="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B6=B7),$N$2:N6),VLOOKUP(B7,Baseline!$A$2:$H$10,6,FALSE))+IF(K7="Defence",1,0)))</f>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O7" s="6">
         <f>IF(B7="","",IFERROR(LOOKUP(2,1/($B$2:B6=B7),$O$2:O6),VLOOKUP(B7,Baseline!$A$2:$H$10,7,FALSE))+IF(K7="Transfer",1,0))</f>
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="P7" s="6">
         <f>IF(B7="","",IFERROR(LOOKUP(2,1/($B$2:B6=B7),$P$2:P6),VLOOKUP(B7,Baseline!$A$2:$H$10,8,FALSE))+IF(K7="Defence",1,0))</f>
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>101</v>
@@ -1633,7 +1634,7 @@
         <v>46269</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5" t="s">
@@ -1644,7 +1645,7 @@
       <c r="I9" s="5"/>
       <c r="J9" s="6" t="str">
         <f>IF(B9="","",IFERROR(LOOKUP(2,1/($B$2:B8=B9),$L$2:L8),VLOOKUP(B9,Baseline!$A$2:$H$10,4,FALSE)))</f>
-        <v>Bayern München</v>
+        <v>VfB Stuttgart</v>
       </c>
       <c r="K9" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1652,23 +1653,23 @@
       </c>
       <c r="L9" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>Bayern München</v>
+        <v>VfB Stuttgart</v>
       </c>
       <c r="M9" s="8">
         <f>IF(B9="","",IF(K9="Transfer",C9,IFERROR(LOOKUP(2,1/($B$2:B8=B9),$M$2:M8),VLOOKUP(B9,Baseline!$A$2:$H$10,5,FALSE))))</f>
-        <v>46081</v>
+        <v>46262</v>
       </c>
       <c r="N9" s="6">
         <f>IF(B9="","",IF(K9="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B8=B9),$N$2:N8),VLOOKUP(B9,Baseline!$A$2:$H$10,6,FALSE))+IF(K9="Defence",1,0)))</f>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O9" s="6">
         <f>IF(B9="","",IFERROR(LOOKUP(2,1/($B$2:B8=B9),$O$2:O8),VLOOKUP(B9,Baseline!$A$2:$H$10,7,FALSE))+IF(K9="Transfer",1,0))</f>
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="P9" s="6">
         <f>IF(B9="","",IFERROR(LOOKUP(2,1/($B$2:B8=B9),$P$2:P8),VLOOKUP(B9,Baseline!$A$2:$H$10,8,FALSE))+IF(K9="Defence",1,0))</f>
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="Q9" s="5"/>
     </row>
@@ -5478,7 +5479,7 @@
         <v/>
       </c>
       <c r="L98" s="6" t="str">
-        <f t="shared" ref="L98:L129" si="6">IF(B98="","",IF(K98="Transfer",D98,J98))</f>
+        <f t="shared" ref="L98:L100" si="6">IF(B98="","",IF(K98="Transfer",D98,J98))</f>
         <v/>
       </c>
       <c r="M98" s="8" t="str">
@@ -5881,23 +5882,23 @@
       </c>
       <c r="B9" t="str">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A9),Updates!$L$2:$L$100),VLOOKUP(A9,Baseline!$A$2:$H$10,4,FALSE))</f>
-        <v>Bayern München</v>
+        <v>VfB Stuttgart</v>
       </c>
       <c r="C9" s="4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A9),Updates!$M$2:$M$100),VLOOKUP(A9,Baseline!$A$2:$H$10,5,FALSE))</f>
-        <v>46081</v>
+        <v>46262</v>
       </c>
       <c r="D9">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A9),Updates!$N$2:$N$100),VLOOKUP(A9,Baseline!$A$2:$H$10,6,FALSE))</f>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A9),Updates!$O$2:$O$100),VLOOKUP(A9,Baseline!$A$2:$H$10,7,FALSE))</f>
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F9">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A9),Updates!$P$2:$P$100),VLOOKUP(A9,Baseline!$A$2:$H$10,8,FALSE))</f>
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="G9" s="4">
         <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A9)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
@@ -6227,23 +6228,23 @@
       </c>
       <c r="B9" t="str">
         <f>Dashboard!B9</f>
-        <v>Bayern München</v>
+        <v>VfB Stuttgart</v>
       </c>
       <c r="C9" s="9">
         <f>Dashboard!C9</f>
-        <v>46081</v>
+        <v>46262</v>
       </c>
       <c r="D9">
         <f>Dashboard!D9</f>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <f>Dashboard!E9</f>
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F9">
         <f>Dashboard!F9</f>
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="G9" s="9">
         <f>Dashboard!G9</f>

--- a/LSC_Update_System.xlsx
+++ b/LSC_Update_System.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CH\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CH\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF2BADAB-34A9-4236-A91F-295B029133B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A28B64F2-693E-44E4-AB5C-4FC30CF8980C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="START HERE" sheetId="1" r:id="rId1"/>
@@ -383,10 +383,10 @@
     <t>next_opponent</t>
   </si>
   <si>
+    <t>Bayern München 5 - VfB Stuttgart 1</t>
+  </si>
+  <si>
     <t>Schalke FC</t>
-  </si>
-  <si>
-    <t>Bayern München 1 - VfB Stuttgart 5</t>
   </si>
 </sst>
 </file>
@@ -1044,7 +1044,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1533,10 +1532,10 @@
         <v>65</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I7" s="5"/>
       <c r="J7" s="6" t="str">
@@ -1545,27 +1544,27 @@
       </c>
       <c r="K7" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>Transfer</v>
+        <v>Defence</v>
       </c>
       <c r="L7" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>VfB Stuttgart</v>
+        <v>Bayern München</v>
       </c>
       <c r="M7" s="8">
         <f>IF(B7="","",IF(K7="Transfer",C7,IFERROR(LOOKUP(2,1/($B$2:B6=B7),$M$2:M6),VLOOKUP(B7,Baseline!$A$2:$H$10,5,FALSE))))</f>
-        <v>46262</v>
+        <v>46081</v>
       </c>
       <c r="N7" s="6">
         <f>IF(B7="","",IF(K7="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B6=B7),$N$2:N6),VLOOKUP(B7,Baseline!$A$2:$H$10,6,FALSE))+IF(K7="Defence",1,0)))</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O7" s="6">
         <f>IF(B7="","",IFERROR(LOOKUP(2,1/($B$2:B6=B7),$O$2:O6),VLOOKUP(B7,Baseline!$A$2:$H$10,7,FALSE))+IF(K7="Transfer",1,0))</f>
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="P7" s="6">
         <f>IF(B7="","",IFERROR(LOOKUP(2,1/($B$2:B6=B7),$P$2:P6),VLOOKUP(B7,Baseline!$A$2:$H$10,8,FALSE))+IF(K7="Defence",1,0))</f>
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>101</v>
@@ -1634,7 +1633,7 @@
         <v>46269</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5" t="s">
@@ -1645,7 +1644,7 @@
       <c r="I9" s="5"/>
       <c r="J9" s="6" t="str">
         <f>IF(B9="","",IFERROR(LOOKUP(2,1/($B$2:B8=B9),$L$2:L8),VLOOKUP(B9,Baseline!$A$2:$H$10,4,FALSE)))</f>
-        <v>VfB Stuttgart</v>
+        <v>Bayern München</v>
       </c>
       <c r="K9" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1653,23 +1652,23 @@
       </c>
       <c r="L9" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>VfB Stuttgart</v>
+        <v>Bayern München</v>
       </c>
       <c r="M9" s="8">
         <f>IF(B9="","",IF(K9="Transfer",C9,IFERROR(LOOKUP(2,1/($B$2:B8=B9),$M$2:M8),VLOOKUP(B9,Baseline!$A$2:$H$10,5,FALSE))))</f>
-        <v>46262</v>
+        <v>46081</v>
       </c>
       <c r="N9" s="6">
         <f>IF(B9="","",IF(K9="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B8=B9),$N$2:N8),VLOOKUP(B9,Baseline!$A$2:$H$10,6,FALSE))+IF(K9="Defence",1,0)))</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O9" s="6">
         <f>IF(B9="","",IFERROR(LOOKUP(2,1/($B$2:B8=B9),$O$2:O8),VLOOKUP(B9,Baseline!$A$2:$H$10,7,FALSE))+IF(K9="Transfer",1,0))</f>
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="P9" s="6">
         <f>IF(B9="","",IFERROR(LOOKUP(2,1/($B$2:B8=B9),$P$2:P8),VLOOKUP(B9,Baseline!$A$2:$H$10,8,FALSE))+IF(K9="Defence",1,0))</f>
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="Q9" s="5"/>
     </row>
@@ -5479,7 +5478,7 @@
         <v/>
       </c>
       <c r="L98" s="6" t="str">
-        <f t="shared" ref="L98:L100" si="6">IF(B98="","",IF(K98="Transfer",D98,J98))</f>
+        <f t="shared" ref="L98:L129" si="6">IF(B98="","",IF(K98="Transfer",D98,J98))</f>
         <v/>
       </c>
       <c r="M98" s="8" t="str">
@@ -5882,23 +5881,23 @@
       </c>
       <c r="B9" t="str">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A9),Updates!$L$2:$L$100),VLOOKUP(A9,Baseline!$A$2:$H$10,4,FALSE))</f>
-        <v>VfB Stuttgart</v>
+        <v>Bayern München</v>
       </c>
       <c r="C9" s="4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A9),Updates!$M$2:$M$100),VLOOKUP(A9,Baseline!$A$2:$H$10,5,FALSE))</f>
-        <v>46262</v>
+        <v>46081</v>
       </c>
       <c r="D9">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A9),Updates!$N$2:$N$100),VLOOKUP(A9,Baseline!$A$2:$H$10,6,FALSE))</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E9">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A9),Updates!$O$2:$O$100),VLOOKUP(A9,Baseline!$A$2:$H$10,7,FALSE))</f>
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F9">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A9),Updates!$P$2:$P$100),VLOOKUP(A9,Baseline!$A$2:$H$10,8,FALSE))</f>
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="G9" s="4">
         <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A9)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
@@ -6228,23 +6227,23 @@
       </c>
       <c r="B9" t="str">
         <f>Dashboard!B9</f>
-        <v>VfB Stuttgart</v>
+        <v>Bayern München</v>
       </c>
       <c r="C9" s="9">
         <f>Dashboard!C9</f>
-        <v>46262</v>
+        <v>46081</v>
       </c>
       <c r="D9">
         <f>Dashboard!D9</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E9">
         <f>Dashboard!E9</f>
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F9">
         <f>Dashboard!F9</f>
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="G9" s="9">
         <f>Dashboard!G9</f>

--- a/LSC_Update_System.xlsx
+++ b/LSC_Update_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CH\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1FF8A6-A208-44D3-8C8C-922EC87E1160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58384636-20AD-46C4-8C14-92DC896D51BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="118">
   <si>
     <t>LSC UPDATE SYSTEM — SAFE TEST</t>
   </si>
@@ -384,6 +384,12 @@
   </si>
   <si>
     <t>Bayern München 1 - VfB Stuttgart 5</t>
+  </si>
+  <si>
+    <t>Weder Bremen</t>
+  </si>
+  <si>
+    <t>VfB Stuttgart 2 - Werder Bremen 0</t>
   </si>
 </sst>
 </file>
@@ -1621,43 +1627,55 @@
     <row r="9" spans="1:17">
       <c r="A9" s="6" t="str">
         <f>IF(OR(B9="",C9=""),"",VLOOKUP(B9,Lists!$A$2:$B$10,2,FALSE)&amp;"-"&amp;TEXT(C9,"yyyymmdd")&amp;"-"&amp;TEXT(COUNTIFS($B$2:B9,B9,$C$2:C9,C9),"00"))</f>
-        <v/>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="5"/>
+        <v>UST-20260830-01</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="7">
+        <v>46264</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>116</v>
+      </c>
       <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
+      <c r="F9" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" t="s">
+        <v>117</v>
+      </c>
       <c r="I9" s="5"/>
       <c r="J9" s="6" t="str">
         <f>IF(B9="","",IFERROR(LOOKUP(2,1/($B$2:B8=B9),$L$2:L8),VLOOKUP(B9,Baseline!$A$2:$H$10,4,FALSE)))</f>
-        <v/>
+        <v>VfB Stuttgart</v>
       </c>
       <c r="K9" s="6" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Defence</v>
       </c>
       <c r="L9" s="6" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M9" s="8" t="str">
+        <v>VfB Stuttgart</v>
+      </c>
+      <c r="M9" s="8">
         <f>IF(B9="","",IF(K9="Transfer",C9,IFERROR(LOOKUP(2,1/($B$2:B8=B9),$M$2:M8),VLOOKUP(B9,Baseline!$A$2:$H$10,5,FALSE))))</f>
-        <v/>
-      </c>
-      <c r="N9" s="6" t="str">
+        <v>46262</v>
+      </c>
+      <c r="N9" s="6">
         <f>IF(B9="","",IF(K9="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B8=B9),$N$2:N8),VLOOKUP(B9,Baseline!$A$2:$H$10,6,FALSE))+IF(K9="Defence",1,0)))</f>
-        <v/>
-      </c>
-      <c r="O9" s="6" t="str">
+        <v>1</v>
+      </c>
+      <c r="O9" s="6">
         <f>IF(B9="","",IFERROR(LOOKUP(2,1/($B$2:B8=B9),$O$2:O8),VLOOKUP(B9,Baseline!$A$2:$H$10,7,FALSE))+IF(K9="Transfer",1,0))</f>
-        <v/>
-      </c>
-      <c r="P9" s="6" t="str">
+        <v>682</v>
+      </c>
+      <c r="P9" s="6">
         <f>IF(B9="","",IFERROR(LOOKUP(2,1/($B$2:B8=B9),$P$2:P8),VLOOKUP(B9,Baseline!$A$2:$H$10,8,FALSE))+IF(K9="Defence",1,0))</f>
-        <v/>
+        <v>1443</v>
       </c>
       <c r="Q9" s="5"/>
     </row>
@@ -5835,7 +5853,7 @@
       </c>
       <c r="D9">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A9),Updates!$N$2:$N$99),VLOOKUP(A9,Baseline!$A$2:$H$10,6,FALSE))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A9),Updates!$O$2:$O$99),VLOOKUP(A9,Baseline!$A$2:$H$10,7,FALSE))</f>
@@ -5843,7 +5861,7 @@
       </c>
       <c r="F9">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A9),Updates!$P$2:$P$99),VLOOKUP(A9,Baseline!$A$2:$H$10,8,FALSE))</f>
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="G9" s="4" t="str">
         <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A9)*(Updates!$F$2:$F$99&lt;&gt;"Completed")*(Updates!$F$2:$F$99&lt;&gt;"Cancelled")*(Updates!$F$2:$F$99&lt;&gt;"Postponed")),Updates!$C$2:$C$99),"TBD")</f>
@@ -6181,7 +6199,7 @@
       </c>
       <c r="D9">
         <f>Dashboard!D9</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9">
         <f>Dashboard!E9</f>
@@ -6189,7 +6207,7 @@
       </c>
       <c r="F9">
         <f>Dashboard!F9</f>
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="G9" s="9" t="str">
         <f>Dashboard!G9</f>

--- a/LSC_Update_System.xlsx
+++ b/LSC_Update_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CH\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58384636-20AD-46C4-8C14-92DC896D51BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67880B8E-542B-4D44-ADD7-F3C85DCF795F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="116">
   <si>
     <t>LSC UPDATE SYSTEM — SAFE TEST</t>
   </si>
@@ -341,7 +341,7 @@
     <t>VfB Stuttgart</t>
   </si>
   <si>
-    <t>Fixture shown on current page; result not entered here.</t>
+    <t>Bayern München 5 - VfB Stuttgart 1</t>
   </si>
   <si>
     <t>1. FSV Mainz 05</t>
@@ -383,13 +383,7 @@
     <t>next_opponent</t>
   </si>
   <si>
-    <t>Bayern München 1 - VfB Stuttgart 5</t>
-  </si>
-  <si>
-    <t>Weder Bremen</t>
-  </si>
-  <si>
-    <t>VfB Stuttgart 2 - Werder Bremen 0</t>
+    <t>FC Schalke 04</t>
   </si>
 </sst>
 </file>
@@ -447,7 +441,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -462,6 +456,8 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1176,7 +1172,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:Q99"/>
+  <dimension ref="A1:Q100"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1270,18 +1266,18 @@
         <v>59</v>
       </c>
       <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
+      <c r="H2" s="10"/>
       <c r="I2" s="5"/>
       <c r="J2" s="6" t="str">
         <f>IF(B2="","",VLOOKUP(B2,Baseline!$A$2:$H$10,4,FALSE))</f>
         <v>South Africa</v>
       </c>
       <c r="K2" s="6" t="str">
-        <f t="shared" ref="K2:K32" si="0">IF(B2="","",IF(F2&lt;&gt;"Completed",F2,IF(G2="Challenger win","Transfer",IF(OR(G2="Holder win",G2="Draw / tie"),"Defence",IF(G2="No result","No result","REVIEW")))))</f>
+        <f t="shared" ref="K2:K33" si="0">IF(B2="","",IF(F2&lt;&gt;"Completed",F2,IF(G2="Challenger win","Transfer",IF(OR(G2="Holder win",G2="Draw / tie"),"Defence",IF(G2="No result","No result","REVIEW")))))</f>
         <v>Scheduled</v>
       </c>
       <c r="L2" s="6" t="str">
-        <f t="shared" ref="L2:L32" si="1">IF(B2="","",IF(K2="Transfer",D2,J2))</f>
+        <f t="shared" ref="L2:L33" si="1">IF(B2="","",IF(K2="Transfer",D2,J2))</f>
         <v>South Africa</v>
       </c>
       <c r="M2" s="8">
@@ -1323,7 +1319,7 @@
         <v>59</v>
       </c>
       <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
+      <c r="H3" s="10"/>
       <c r="I3" s="5"/>
       <c r="J3" s="6" t="str">
         <f>IF(B3="","",IFERROR(LOOKUP(2,1/($B$2:B2=B3),$L$2:L2),VLOOKUP(B3,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -1378,7 +1374,7 @@
         <v>59</v>
       </c>
       <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
+      <c r="H4" s="10"/>
       <c r="I4" s="5"/>
       <c r="J4" s="6" t="str">
         <f>IF(B4="","",IFERROR(LOOKUP(2,1/($B$2:B3=B4),$L$2:L3),VLOOKUP(B4,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -1431,7 +1427,7 @@
         <v>59</v>
       </c>
       <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
+      <c r="H5" s="10"/>
       <c r="I5" s="5"/>
       <c r="J5" s="6" t="str">
         <f>IF(B5="","",IFERROR(LOOKUP(2,1/($B$2:B4=B5),$L$2:L4),VLOOKUP(B5,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -1484,7 +1480,7 @@
         <v>59</v>
       </c>
       <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
+      <c r="H6" s="10"/>
       <c r="I6" s="5"/>
       <c r="J6" s="6" t="str">
         <f>IF(B6="","",IFERROR(LOOKUP(2,1/($B$2:B5=B6),$L$2:L5),VLOOKUP(B6,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -1535,10 +1531,10 @@
         <v>65</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="H7" t="s">
-        <v>115</v>
+        <v>60</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>101</v>
       </c>
       <c r="I7" s="5"/>
       <c r="J7" s="6" t="str">
@@ -1547,31 +1543,29 @@
       </c>
       <c r="K7" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>Transfer</v>
+        <v>Defence</v>
       </c>
       <c r="L7" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>VfB Stuttgart</v>
+        <v>Bayern München</v>
       </c>
       <c r="M7" s="8">
         <f>IF(B7="","",IF(K7="Transfer",C7,IFERROR(LOOKUP(2,1/($B$2:B6=B7),$M$2:M6),VLOOKUP(B7,Baseline!$A$2:$H$10,5,FALSE))))</f>
-        <v>46262</v>
+        <v>46081</v>
       </c>
       <c r="N7" s="6">
         <f>IF(B7="","",IF(K7="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B6=B7),$N$2:N6),VLOOKUP(B7,Baseline!$A$2:$H$10,6,FALSE))+IF(K7="Defence",1,0)))</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O7" s="6">
         <f>IF(B7="","",IFERROR(LOOKUP(2,1/($B$2:B6=B7),$O$2:O6),VLOOKUP(B7,Baseline!$A$2:$H$10,7,FALSE))+IF(K7="Transfer",1,0))</f>
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="P7" s="6">
         <f>IF(B7="","",IFERROR(LOOKUP(2,1/($B$2:B6=B7),$P$2:P6),VLOOKUP(B7,Baseline!$A$2:$H$10,8,FALSE))+IF(K7="Defence",1,0))</f>
-        <v>1442</v>
-      </c>
-      <c r="Q7" s="5" t="s">
-        <v>101</v>
-      </c>
+        <v>1443</v>
+      </c>
+      <c r="Q7" s="5"/>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="6" t="str">
@@ -1592,7 +1586,7 @@
         <v>59</v>
       </c>
       <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
+      <c r="H8" s="10"/>
       <c r="I8" s="5"/>
       <c r="J8" s="6" t="str">
         <f>IF(B8="","",IFERROR(LOOKUP(2,1/($B$2:B7=B8),$L$2:L7),VLOOKUP(B8,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -1627,51 +1621,47 @@
     <row r="9" spans="1:17">
       <c r="A9" s="6" t="str">
         <f>IF(OR(B9="",C9=""),"",VLOOKUP(B9,Lists!$A$2:$B$10,2,FALSE)&amp;"-"&amp;TEXT(C9,"yyyymmdd")&amp;"-"&amp;TEXT(COUNTIFS($B$2:B9,B9,$C$2:C9,C9),"00"))</f>
-        <v>UST-20260830-01</v>
+        <v>UST-20260904-01</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>49</v>
       </c>
       <c r="C9" s="7">
-        <v>46264</v>
+        <v>46269</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="H9" t="s">
-        <v>117</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="G9" s="5"/>
+      <c r="H9" s="10"/>
       <c r="I9" s="5"/>
       <c r="J9" s="6" t="str">
         <f>IF(B9="","",IFERROR(LOOKUP(2,1/($B$2:B8=B9),$L$2:L8),VLOOKUP(B9,Baseline!$A$2:$H$10,4,FALSE)))</f>
-        <v>VfB Stuttgart</v>
+        <v>Bayern München</v>
       </c>
       <c r="K9" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>Defence</v>
+        <v>Scheduled</v>
       </c>
       <c r="L9" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>VfB Stuttgart</v>
+        <v>Bayern München</v>
       </c>
       <c r="M9" s="8">
         <f>IF(B9="","",IF(K9="Transfer",C9,IFERROR(LOOKUP(2,1/($B$2:B8=B9),$M$2:M8),VLOOKUP(B9,Baseline!$A$2:$H$10,5,FALSE))))</f>
-        <v>46262</v>
+        <v>46081</v>
       </c>
       <c r="N9" s="6">
         <f>IF(B9="","",IF(K9="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B8=B9),$N$2:N8),VLOOKUP(B9,Baseline!$A$2:$H$10,6,FALSE))+IF(K9="Defence",1,0)))</f>
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O9" s="6">
         <f>IF(B9="","",IFERROR(LOOKUP(2,1/($B$2:B8=B9),$O$2:O8),VLOOKUP(B9,Baseline!$A$2:$H$10,7,FALSE))+IF(K9="Transfer",1,0))</f>
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="P9" s="6">
         <f>IF(B9="","",IFERROR(LOOKUP(2,1/($B$2:B8=B9),$P$2:P8),VLOOKUP(B9,Baseline!$A$2:$H$10,8,FALSE))+IF(K9="Defence",1,0))</f>
@@ -1690,7 +1680,7 @@
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
+      <c r="H10" s="10"/>
       <c r="I10" s="5"/>
       <c r="J10" s="6" t="str">
         <f>IF(B10="","",IFERROR(LOOKUP(2,1/($B$2:B9=B10),$L$2:L9),VLOOKUP(B10,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -1733,7 +1723,7 @@
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
+      <c r="H11" s="10"/>
       <c r="I11" s="5"/>
       <c r="J11" s="6" t="str">
         <f>IF(B11="","",IFERROR(LOOKUP(2,1/($B$2:B10=B11),$L$2:L10),VLOOKUP(B11,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -1776,7 +1766,7 @@
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
+      <c r="H12" s="10"/>
       <c r="I12" s="5"/>
       <c r="J12" s="6" t="str">
         <f>IF(B12="","",IFERROR(LOOKUP(2,1/($B$2:B11=B12),$L$2:L11),VLOOKUP(B12,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -1819,7 +1809,7 @@
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
+      <c r="H13" s="10"/>
       <c r="I13" s="5"/>
       <c r="J13" s="6" t="str">
         <f>IF(B13="","",IFERROR(LOOKUP(2,1/($B$2:B12=B13),$L$2:L12),VLOOKUP(B13,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -1862,7 +1852,7 @@
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
+      <c r="H14" s="10"/>
       <c r="I14" s="5"/>
       <c r="J14" s="6" t="str">
         <f>IF(B14="","",IFERROR(LOOKUP(2,1/($B$2:B13=B14),$L$2:L13),VLOOKUP(B14,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -1905,7 +1895,7 @@
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
+      <c r="H15" s="10"/>
       <c r="I15" s="5"/>
       <c r="J15" s="6" t="str">
         <f>IF(B15="","",IFERROR(LOOKUP(2,1/($B$2:B14=B15),$L$2:L14),VLOOKUP(B15,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -1948,7 +1938,7 @@
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
+      <c r="H16" s="10"/>
       <c r="I16" s="5"/>
       <c r="J16" s="6" t="str">
         <f>IF(B16="","",IFERROR(LOOKUP(2,1/($B$2:B15=B16),$L$2:L15),VLOOKUP(B16,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -1991,7 +1981,7 @@
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
+      <c r="H17" s="10"/>
       <c r="I17" s="5"/>
       <c r="J17" s="6" t="str">
         <f>IF(B17="","",IFERROR(LOOKUP(2,1/($B$2:B16=B17),$L$2:L16),VLOOKUP(B17,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -2034,7 +2024,7 @@
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
+      <c r="H18" s="10"/>
       <c r="I18" s="5"/>
       <c r="J18" s="6" t="str">
         <f>IF(B18="","",IFERROR(LOOKUP(2,1/($B$2:B17=B18),$L$2:L17),VLOOKUP(B18,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -2077,7 +2067,7 @@
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
+      <c r="H19" s="10"/>
       <c r="I19" s="5"/>
       <c r="J19" s="6" t="str">
         <f>IF(B19="","",IFERROR(LOOKUP(2,1/($B$2:B18=B19),$L$2:L18),VLOOKUP(B19,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -2120,7 +2110,7 @@
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
+      <c r="H20" s="10"/>
       <c r="I20" s="5"/>
       <c r="J20" s="6" t="str">
         <f>IF(B20="","",IFERROR(LOOKUP(2,1/($B$2:B19=B20),$L$2:L19),VLOOKUP(B20,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -2163,7 +2153,7 @@
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
+      <c r="H21" s="10"/>
       <c r="I21" s="5"/>
       <c r="J21" s="6" t="str">
         <f>IF(B21="","",IFERROR(LOOKUP(2,1/($B$2:B20=B21),$L$2:L20),VLOOKUP(B21,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -2206,7 +2196,7 @@
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
+      <c r="H22" s="10"/>
       <c r="I22" s="5"/>
       <c r="J22" s="6" t="str">
         <f>IF(B22="","",IFERROR(LOOKUP(2,1/($B$2:B21=B22),$L$2:L21),VLOOKUP(B22,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -2249,7 +2239,7 @@
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
+      <c r="H23" s="10"/>
       <c r="I23" s="5"/>
       <c r="J23" s="6" t="str">
         <f>IF(B23="","",IFERROR(LOOKUP(2,1/($B$2:B22=B23),$L$2:L22),VLOOKUP(B23,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -2292,7 +2282,7 @@
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
+      <c r="H24" s="10"/>
       <c r="I24" s="5"/>
       <c r="J24" s="6" t="str">
         <f>IF(B24="","",IFERROR(LOOKUP(2,1/($B$2:B23=B24),$L$2:L23),VLOOKUP(B24,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -2335,7 +2325,7 @@
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
+      <c r="H25" s="10"/>
       <c r="I25" s="5"/>
       <c r="J25" s="6" t="str">
         <f>IF(B25="","",IFERROR(LOOKUP(2,1/($B$2:B24=B25),$L$2:L24),VLOOKUP(B25,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -2378,7 +2368,7 @@
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
+      <c r="H26" s="10"/>
       <c r="I26" s="5"/>
       <c r="J26" s="6" t="str">
         <f>IF(B26="","",IFERROR(LOOKUP(2,1/($B$2:B25=B26),$L$2:L25),VLOOKUP(B26,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -2421,7 +2411,7 @@
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
+      <c r="H27" s="10"/>
       <c r="I27" s="5"/>
       <c r="J27" s="6" t="str">
         <f>IF(B27="","",IFERROR(LOOKUP(2,1/($B$2:B26=B27),$L$2:L26),VLOOKUP(B27,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -2464,7 +2454,7 @@
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
+      <c r="H28" s="10"/>
       <c r="I28" s="5"/>
       <c r="J28" s="6" t="str">
         <f>IF(B28="","",IFERROR(LOOKUP(2,1/($B$2:B27=B28),$L$2:L27),VLOOKUP(B28,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -2507,7 +2497,7 @@
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
+      <c r="H29" s="10"/>
       <c r="I29" s="5"/>
       <c r="J29" s="6" t="str">
         <f>IF(B29="","",IFERROR(LOOKUP(2,1/($B$2:B28=B29),$L$2:L28),VLOOKUP(B29,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -2550,7 +2540,7 @@
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
+      <c r="H30" s="10"/>
       <c r="I30" s="5"/>
       <c r="J30" s="6" t="str">
         <f>IF(B30="","",IFERROR(LOOKUP(2,1/($B$2:B29=B30),$L$2:L29),VLOOKUP(B30,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -2593,7 +2583,7 @@
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
+      <c r="H31" s="10"/>
       <c r="I31" s="5"/>
       <c r="J31" s="6" t="str">
         <f>IF(B31="","",IFERROR(LOOKUP(2,1/($B$2:B30=B31),$L$2:L30),VLOOKUP(B31,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -2636,7 +2626,7 @@
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
+      <c r="H32" s="10"/>
       <c r="I32" s="5"/>
       <c r="J32" s="6" t="str">
         <f>IF(B32="","",IFERROR(LOOKUP(2,1/($B$2:B31=B32),$L$2:L31),VLOOKUP(B32,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -2679,18 +2669,18 @@
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
+      <c r="H33" s="10"/>
       <c r="I33" s="5"/>
       <c r="J33" s="6" t="str">
         <f>IF(B33="","",IFERROR(LOOKUP(2,1/($B$2:B32=B33),$L$2:L32),VLOOKUP(B33,Baseline!$A$2:$H$10,4,FALSE)))</f>
         <v/>
       </c>
       <c r="K33" s="6" t="str">
-        <f t="shared" ref="K33:K64" si="2">IF(B33="","",IF(F33&lt;&gt;"Completed",F33,IF(G33="Challenger win","Transfer",IF(OR(G33="Holder win",G33="Draw / tie"),"Defence",IF(G33="No result","No result","REVIEW")))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L33" s="6" t="str">
-        <f t="shared" ref="L33:L64" si="3">IF(B33="","",IF(K33="Transfer",D33,J33))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M33" s="8" t="str">
@@ -2722,18 +2712,18 @@
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
+      <c r="H34" s="10"/>
       <c r="I34" s="5"/>
       <c r="J34" s="6" t="str">
         <f>IF(B34="","",IFERROR(LOOKUP(2,1/($B$2:B33=B34),$L$2:L33),VLOOKUP(B34,Baseline!$A$2:$H$10,4,FALSE)))</f>
         <v/>
       </c>
       <c r="K34" s="6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="K34:K65" si="2">IF(B34="","",IF(F34&lt;&gt;"Completed",F34,IF(G34="Challenger win","Transfer",IF(OR(G34="Holder win",G34="Draw / tie"),"Defence",IF(G34="No result","No result","REVIEW")))))</f>
         <v/>
       </c>
       <c r="L34" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="L34:L65" si="3">IF(B34="","",IF(K34="Transfer",D34,J34))</f>
         <v/>
       </c>
       <c r="M34" s="8" t="str">
@@ -2765,7 +2755,7 @@
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
+      <c r="H35" s="10"/>
       <c r="I35" s="5"/>
       <c r="J35" s="6" t="str">
         <f>IF(B35="","",IFERROR(LOOKUP(2,1/($B$2:B34=B35),$L$2:L34),VLOOKUP(B35,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -2808,7 +2798,7 @@
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
+      <c r="H36" s="10"/>
       <c r="I36" s="5"/>
       <c r="J36" s="6" t="str">
         <f>IF(B36="","",IFERROR(LOOKUP(2,1/($B$2:B35=B36),$L$2:L35),VLOOKUP(B36,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -2851,7 +2841,7 @@
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
+      <c r="H37" s="10"/>
       <c r="I37" s="5"/>
       <c r="J37" s="6" t="str">
         <f>IF(B37="","",IFERROR(LOOKUP(2,1/($B$2:B36=B37),$L$2:L36),VLOOKUP(B37,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -2894,7 +2884,7 @@
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
+      <c r="H38" s="10"/>
       <c r="I38" s="5"/>
       <c r="J38" s="6" t="str">
         <f>IF(B38="","",IFERROR(LOOKUP(2,1/($B$2:B37=B38),$L$2:L37),VLOOKUP(B38,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -2937,7 +2927,7 @@
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
+      <c r="H39" s="10"/>
       <c r="I39" s="5"/>
       <c r="J39" s="6" t="str">
         <f>IF(B39="","",IFERROR(LOOKUP(2,1/($B$2:B38=B39),$L$2:L38),VLOOKUP(B39,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -2980,7 +2970,7 @@
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
+      <c r="H40" s="10"/>
       <c r="I40" s="5"/>
       <c r="J40" s="6" t="str">
         <f>IF(B40="","",IFERROR(LOOKUP(2,1/($B$2:B39=B40),$L$2:L39),VLOOKUP(B40,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -3023,7 +3013,7 @@
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
+      <c r="H41" s="10"/>
       <c r="I41" s="5"/>
       <c r="J41" s="6" t="str">
         <f>IF(B41="","",IFERROR(LOOKUP(2,1/($B$2:B40=B41),$L$2:L40),VLOOKUP(B41,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -3066,7 +3056,7 @@
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
+      <c r="H42" s="10"/>
       <c r="I42" s="5"/>
       <c r="J42" s="6" t="str">
         <f>IF(B42="","",IFERROR(LOOKUP(2,1/($B$2:B41=B42),$L$2:L41),VLOOKUP(B42,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -3109,7 +3099,7 @@
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
+      <c r="H43" s="10"/>
       <c r="I43" s="5"/>
       <c r="J43" s="6" t="str">
         <f>IF(B43="","",IFERROR(LOOKUP(2,1/($B$2:B42=B43),$L$2:L42),VLOOKUP(B43,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -3152,7 +3142,7 @@
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
+      <c r="H44" s="10"/>
       <c r="I44" s="5"/>
       <c r="J44" s="6" t="str">
         <f>IF(B44="","",IFERROR(LOOKUP(2,1/($B$2:B43=B44),$L$2:L43),VLOOKUP(B44,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -3195,7 +3185,7 @@
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
+      <c r="H45" s="10"/>
       <c r="I45" s="5"/>
       <c r="J45" s="6" t="str">
         <f>IF(B45="","",IFERROR(LOOKUP(2,1/($B$2:B44=B45),$L$2:L44),VLOOKUP(B45,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -3238,7 +3228,7 @@
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
-      <c r="H46" s="5"/>
+      <c r="H46" s="10"/>
       <c r="I46" s="5"/>
       <c r="J46" s="6" t="str">
         <f>IF(B46="","",IFERROR(LOOKUP(2,1/($B$2:B45=B46),$L$2:L45),VLOOKUP(B46,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -3281,7 +3271,7 @@
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
-      <c r="H47" s="5"/>
+      <c r="H47" s="10"/>
       <c r="I47" s="5"/>
       <c r="J47" s="6" t="str">
         <f>IF(B47="","",IFERROR(LOOKUP(2,1/($B$2:B46=B47),$L$2:L46),VLOOKUP(B47,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -3324,7 +3314,7 @@
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
-      <c r="H48" s="5"/>
+      <c r="H48" s="10"/>
       <c r="I48" s="5"/>
       <c r="J48" s="6" t="str">
         <f>IF(B48="","",IFERROR(LOOKUP(2,1/($B$2:B47=B48),$L$2:L47),VLOOKUP(B48,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -3367,7 +3357,7 @@
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
-      <c r="H49" s="5"/>
+      <c r="H49" s="10"/>
       <c r="I49" s="5"/>
       <c r="J49" s="6" t="str">
         <f>IF(B49="","",IFERROR(LOOKUP(2,1/($B$2:B48=B49),$L$2:L48),VLOOKUP(B49,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -3410,7 +3400,7 @@
       <c r="E50" s="5"/>
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
-      <c r="H50" s="5"/>
+      <c r="H50" s="10"/>
       <c r="I50" s="5"/>
       <c r="J50" s="6" t="str">
         <f>IF(B50="","",IFERROR(LOOKUP(2,1/($B$2:B49=B50),$L$2:L49),VLOOKUP(B50,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -3453,7 +3443,7 @@
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
+      <c r="H51" s="10"/>
       <c r="I51" s="5"/>
       <c r="J51" s="6" t="str">
         <f>IF(B51="","",IFERROR(LOOKUP(2,1/($B$2:B50=B51),$L$2:L50),VLOOKUP(B51,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -3496,7 +3486,7 @@
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
-      <c r="H52" s="5"/>
+      <c r="H52" s="10"/>
       <c r="I52" s="5"/>
       <c r="J52" s="6" t="str">
         <f>IF(B52="","",IFERROR(LOOKUP(2,1/($B$2:B51=B52),$L$2:L51),VLOOKUP(B52,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -3539,7 +3529,7 @@
       <c r="E53" s="5"/>
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
-      <c r="H53" s="5"/>
+      <c r="H53" s="10"/>
       <c r="I53" s="5"/>
       <c r="J53" s="6" t="str">
         <f>IF(B53="","",IFERROR(LOOKUP(2,1/($B$2:B52=B53),$L$2:L52),VLOOKUP(B53,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -3582,7 +3572,7 @@
       <c r="E54" s="5"/>
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
-      <c r="H54" s="5"/>
+      <c r="H54" s="10"/>
       <c r="I54" s="5"/>
       <c r="J54" s="6" t="str">
         <f>IF(B54="","",IFERROR(LOOKUP(2,1/($B$2:B53=B54),$L$2:L53),VLOOKUP(B54,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -3625,7 +3615,7 @@
       <c r="E55" s="5"/>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
-      <c r="H55" s="5"/>
+      <c r="H55" s="10"/>
       <c r="I55" s="5"/>
       <c r="J55" s="6" t="str">
         <f>IF(B55="","",IFERROR(LOOKUP(2,1/($B$2:B54=B55),$L$2:L54),VLOOKUP(B55,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -3668,7 +3658,7 @@
       <c r="E56" s="5"/>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
-      <c r="H56" s="5"/>
+      <c r="H56" s="10"/>
       <c r="I56" s="5"/>
       <c r="J56" s="6" t="str">
         <f>IF(B56="","",IFERROR(LOOKUP(2,1/($B$2:B55=B56),$L$2:L55),VLOOKUP(B56,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -3711,7 +3701,7 @@
       <c r="E57" s="5"/>
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
-      <c r="H57" s="5"/>
+      <c r="H57" s="10"/>
       <c r="I57" s="5"/>
       <c r="J57" s="6" t="str">
         <f>IF(B57="","",IFERROR(LOOKUP(2,1/($B$2:B56=B57),$L$2:L56),VLOOKUP(B57,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -3754,7 +3744,7 @@
       <c r="E58" s="5"/>
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
-      <c r="H58" s="5"/>
+      <c r="H58" s="10"/>
       <c r="I58" s="5"/>
       <c r="J58" s="6" t="str">
         <f>IF(B58="","",IFERROR(LOOKUP(2,1/($B$2:B57=B58),$L$2:L57),VLOOKUP(B58,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -3797,7 +3787,7 @@
       <c r="E59" s="5"/>
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
-      <c r="H59" s="5"/>
+      <c r="H59" s="10"/>
       <c r="I59" s="5"/>
       <c r="J59" s="6" t="str">
         <f>IF(B59="","",IFERROR(LOOKUP(2,1/($B$2:B58=B59),$L$2:L58),VLOOKUP(B59,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -3840,7 +3830,7 @@
       <c r="E60" s="5"/>
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
-      <c r="H60" s="5"/>
+      <c r="H60" s="10"/>
       <c r="I60" s="5"/>
       <c r="J60" s="6" t="str">
         <f>IF(B60="","",IFERROR(LOOKUP(2,1/($B$2:B59=B60),$L$2:L59),VLOOKUP(B60,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -3883,7 +3873,7 @@
       <c r="E61" s="5"/>
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
-      <c r="H61" s="5"/>
+      <c r="H61" s="10"/>
       <c r="I61" s="5"/>
       <c r="J61" s="6" t="str">
         <f>IF(B61="","",IFERROR(LOOKUP(2,1/($B$2:B60=B61),$L$2:L60),VLOOKUP(B61,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -3926,7 +3916,7 @@
       <c r="E62" s="5"/>
       <c r="F62" s="5"/>
       <c r="G62" s="5"/>
-      <c r="H62" s="5"/>
+      <c r="H62" s="10"/>
       <c r="I62" s="5"/>
       <c r="J62" s="6" t="str">
         <f>IF(B62="","",IFERROR(LOOKUP(2,1/($B$2:B61=B62),$L$2:L61),VLOOKUP(B62,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -3969,7 +3959,7 @@
       <c r="E63" s="5"/>
       <c r="F63" s="5"/>
       <c r="G63" s="5"/>
-      <c r="H63" s="5"/>
+      <c r="H63" s="10"/>
       <c r="I63" s="5"/>
       <c r="J63" s="6" t="str">
         <f>IF(B63="","",IFERROR(LOOKUP(2,1/($B$2:B62=B63),$L$2:L62),VLOOKUP(B63,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -4012,7 +4002,7 @@
       <c r="E64" s="5"/>
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
-      <c r="H64" s="5"/>
+      <c r="H64" s="10"/>
       <c r="I64" s="5"/>
       <c r="J64" s="6" t="str">
         <f>IF(B64="","",IFERROR(LOOKUP(2,1/($B$2:B63=B64),$L$2:L63),VLOOKUP(B64,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -4055,18 +4045,18 @@
       <c r="E65" s="5"/>
       <c r="F65" s="5"/>
       <c r="G65" s="5"/>
-      <c r="H65" s="5"/>
+      <c r="H65" s="10"/>
       <c r="I65" s="5"/>
       <c r="J65" s="6" t="str">
         <f>IF(B65="","",IFERROR(LOOKUP(2,1/($B$2:B64=B65),$L$2:L64),VLOOKUP(B65,Baseline!$A$2:$H$10,4,FALSE)))</f>
         <v/>
       </c>
       <c r="K65" s="6" t="str">
-        <f t="shared" ref="K65:K99" si="4">IF(B65="","",IF(F65&lt;&gt;"Completed",F65,IF(G65="Challenger win","Transfer",IF(OR(G65="Holder win",G65="Draw / tie"),"Defence",IF(G65="No result","No result","REVIEW")))))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L65" s="6" t="str">
-        <f t="shared" ref="L65:L96" si="5">IF(B65="","",IF(K65="Transfer",D65,J65))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M65" s="8" t="str">
@@ -4098,18 +4088,18 @@
       <c r="E66" s="5"/>
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
-      <c r="H66" s="5"/>
+      <c r="H66" s="10"/>
       <c r="I66" s="5"/>
       <c r="J66" s="6" t="str">
         <f>IF(B66="","",IFERROR(LOOKUP(2,1/($B$2:B65=B66),$L$2:L65),VLOOKUP(B66,Baseline!$A$2:$H$10,4,FALSE)))</f>
         <v/>
       </c>
       <c r="K66" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="K66:K100" si="4">IF(B66="","",IF(F66&lt;&gt;"Completed",F66,IF(G66="Challenger win","Transfer",IF(OR(G66="Holder win",G66="Draw / tie"),"Defence",IF(G66="No result","No result","REVIEW")))))</f>
         <v/>
       </c>
       <c r="L66" s="6" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="L66:L97" si="5">IF(B66="","",IF(K66="Transfer",D66,J66))</f>
         <v/>
       </c>
       <c r="M66" s="8" t="str">
@@ -4141,7 +4131,7 @@
       <c r="E67" s="5"/>
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
-      <c r="H67" s="5"/>
+      <c r="H67" s="10"/>
       <c r="I67" s="5"/>
       <c r="J67" s="6" t="str">
         <f>IF(B67="","",IFERROR(LOOKUP(2,1/($B$2:B66=B67),$L$2:L66),VLOOKUP(B67,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -4184,7 +4174,7 @@
       <c r="E68" s="5"/>
       <c r="F68" s="5"/>
       <c r="G68" s="5"/>
-      <c r="H68" s="5"/>
+      <c r="H68" s="10"/>
       <c r="I68" s="5"/>
       <c r="J68" s="6" t="str">
         <f>IF(B68="","",IFERROR(LOOKUP(2,1/($B$2:B67=B68),$L$2:L67),VLOOKUP(B68,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -4227,7 +4217,7 @@
       <c r="E69" s="5"/>
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
-      <c r="H69" s="5"/>
+      <c r="H69" s="10"/>
       <c r="I69" s="5"/>
       <c r="J69" s="6" t="str">
         <f>IF(B69="","",IFERROR(LOOKUP(2,1/($B$2:B68=B69),$L$2:L68),VLOOKUP(B69,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -4270,7 +4260,7 @@
       <c r="E70" s="5"/>
       <c r="F70" s="5"/>
       <c r="G70" s="5"/>
-      <c r="H70" s="5"/>
+      <c r="H70" s="10"/>
       <c r="I70" s="5"/>
       <c r="J70" s="6" t="str">
         <f>IF(B70="","",IFERROR(LOOKUP(2,1/($B$2:B69=B70),$L$2:L69),VLOOKUP(B70,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -4313,7 +4303,7 @@
       <c r="E71" s="5"/>
       <c r="F71" s="5"/>
       <c r="G71" s="5"/>
-      <c r="H71" s="5"/>
+      <c r="H71" s="10"/>
       <c r="I71" s="5"/>
       <c r="J71" s="6" t="str">
         <f>IF(B71="","",IFERROR(LOOKUP(2,1/($B$2:B70=B71),$L$2:L70),VLOOKUP(B71,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -4356,7 +4346,7 @@
       <c r="E72" s="5"/>
       <c r="F72" s="5"/>
       <c r="G72" s="5"/>
-      <c r="H72" s="5"/>
+      <c r="H72" s="10"/>
       <c r="I72" s="5"/>
       <c r="J72" s="6" t="str">
         <f>IF(B72="","",IFERROR(LOOKUP(2,1/($B$2:B71=B72),$L$2:L71),VLOOKUP(B72,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -4399,7 +4389,7 @@
       <c r="E73" s="5"/>
       <c r="F73" s="5"/>
       <c r="G73" s="5"/>
-      <c r="H73" s="5"/>
+      <c r="H73" s="10"/>
       <c r="I73" s="5"/>
       <c r="J73" s="6" t="str">
         <f>IF(B73="","",IFERROR(LOOKUP(2,1/($B$2:B72=B73),$L$2:L72),VLOOKUP(B73,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -4442,7 +4432,7 @@
       <c r="E74" s="5"/>
       <c r="F74" s="5"/>
       <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
+      <c r="H74" s="10"/>
       <c r="I74" s="5"/>
       <c r="J74" s="6" t="str">
         <f>IF(B74="","",IFERROR(LOOKUP(2,1/($B$2:B73=B74),$L$2:L73),VLOOKUP(B74,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -4485,7 +4475,7 @@
       <c r="E75" s="5"/>
       <c r="F75" s="5"/>
       <c r="G75" s="5"/>
-      <c r="H75" s="5"/>
+      <c r="H75" s="10"/>
       <c r="I75" s="5"/>
       <c r="J75" s="6" t="str">
         <f>IF(B75="","",IFERROR(LOOKUP(2,1/($B$2:B74=B75),$L$2:L74),VLOOKUP(B75,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -4528,7 +4518,7 @@
       <c r="E76" s="5"/>
       <c r="F76" s="5"/>
       <c r="G76" s="5"/>
-      <c r="H76" s="5"/>
+      <c r="H76" s="10"/>
       <c r="I76" s="5"/>
       <c r="J76" s="6" t="str">
         <f>IF(B76="","",IFERROR(LOOKUP(2,1/($B$2:B75=B76),$L$2:L75),VLOOKUP(B76,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -4571,7 +4561,7 @@
       <c r="E77" s="5"/>
       <c r="F77" s="5"/>
       <c r="G77" s="5"/>
-      <c r="H77" s="5"/>
+      <c r="H77" s="10"/>
       <c r="I77" s="5"/>
       <c r="J77" s="6" t="str">
         <f>IF(B77="","",IFERROR(LOOKUP(2,1/($B$2:B76=B77),$L$2:L76),VLOOKUP(B77,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -4614,7 +4604,7 @@
       <c r="E78" s="5"/>
       <c r="F78" s="5"/>
       <c r="G78" s="5"/>
-      <c r="H78" s="5"/>
+      <c r="H78" s="10"/>
       <c r="I78" s="5"/>
       <c r="J78" s="6" t="str">
         <f>IF(B78="","",IFERROR(LOOKUP(2,1/($B$2:B77=B78),$L$2:L77),VLOOKUP(B78,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -4657,7 +4647,7 @@
       <c r="E79" s="5"/>
       <c r="F79" s="5"/>
       <c r="G79" s="5"/>
-      <c r="H79" s="5"/>
+      <c r="H79" s="10"/>
       <c r="I79" s="5"/>
       <c r="J79" s="6" t="str">
         <f>IF(B79="","",IFERROR(LOOKUP(2,1/($B$2:B78=B79),$L$2:L78),VLOOKUP(B79,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -4700,7 +4690,7 @@
       <c r="E80" s="5"/>
       <c r="F80" s="5"/>
       <c r="G80" s="5"/>
-      <c r="H80" s="5"/>
+      <c r="H80" s="10"/>
       <c r="I80" s="5"/>
       <c r="J80" s="6" t="str">
         <f>IF(B80="","",IFERROR(LOOKUP(2,1/($B$2:B79=B80),$L$2:L79),VLOOKUP(B80,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -4743,7 +4733,7 @@
       <c r="E81" s="5"/>
       <c r="F81" s="5"/>
       <c r="G81" s="5"/>
-      <c r="H81" s="5"/>
+      <c r="H81" s="10"/>
       <c r="I81" s="5"/>
       <c r="J81" s="6" t="str">
         <f>IF(B81="","",IFERROR(LOOKUP(2,1/($B$2:B80=B81),$L$2:L80),VLOOKUP(B81,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -4786,7 +4776,7 @@
       <c r="E82" s="5"/>
       <c r="F82" s="5"/>
       <c r="G82" s="5"/>
-      <c r="H82" s="5"/>
+      <c r="H82" s="10"/>
       <c r="I82" s="5"/>
       <c r="J82" s="6" t="str">
         <f>IF(B82="","",IFERROR(LOOKUP(2,1/($B$2:B81=B82),$L$2:L81),VLOOKUP(B82,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -4829,7 +4819,7 @@
       <c r="E83" s="5"/>
       <c r="F83" s="5"/>
       <c r="G83" s="5"/>
-      <c r="H83" s="5"/>
+      <c r="H83" s="10"/>
       <c r="I83" s="5"/>
       <c r="J83" s="6" t="str">
         <f>IF(B83="","",IFERROR(LOOKUP(2,1/($B$2:B82=B83),$L$2:L82),VLOOKUP(B83,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -4872,7 +4862,7 @@
       <c r="E84" s="5"/>
       <c r="F84" s="5"/>
       <c r="G84" s="5"/>
-      <c r="H84" s="5"/>
+      <c r="H84" s="10"/>
       <c r="I84" s="5"/>
       <c r="J84" s="6" t="str">
         <f>IF(B84="","",IFERROR(LOOKUP(2,1/($B$2:B83=B84),$L$2:L83),VLOOKUP(B84,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -4915,7 +4905,7 @@
       <c r="E85" s="5"/>
       <c r="F85" s="5"/>
       <c r="G85" s="5"/>
-      <c r="H85" s="5"/>
+      <c r="H85" s="10"/>
       <c r="I85" s="5"/>
       <c r="J85" s="6" t="str">
         <f>IF(B85="","",IFERROR(LOOKUP(2,1/($B$2:B84=B85),$L$2:L84),VLOOKUP(B85,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -4958,7 +4948,7 @@
       <c r="E86" s="5"/>
       <c r="F86" s="5"/>
       <c r="G86" s="5"/>
-      <c r="H86" s="5"/>
+      <c r="H86" s="10"/>
       <c r="I86" s="5"/>
       <c r="J86" s="6" t="str">
         <f>IF(B86="","",IFERROR(LOOKUP(2,1/($B$2:B85=B86),$L$2:L85),VLOOKUP(B86,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -5001,7 +4991,7 @@
       <c r="E87" s="5"/>
       <c r="F87" s="5"/>
       <c r="G87" s="5"/>
-      <c r="H87" s="5"/>
+      <c r="H87" s="10"/>
       <c r="I87" s="5"/>
       <c r="J87" s="6" t="str">
         <f>IF(B87="","",IFERROR(LOOKUP(2,1/($B$2:B86=B87),$L$2:L86),VLOOKUP(B87,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -5044,7 +5034,7 @@
       <c r="E88" s="5"/>
       <c r="F88" s="5"/>
       <c r="G88" s="5"/>
-      <c r="H88" s="5"/>
+      <c r="H88" s="10"/>
       <c r="I88" s="5"/>
       <c r="J88" s="6" t="str">
         <f>IF(B88="","",IFERROR(LOOKUP(2,1/($B$2:B87=B88),$L$2:L87),VLOOKUP(B88,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -5087,7 +5077,7 @@
       <c r="E89" s="5"/>
       <c r="F89" s="5"/>
       <c r="G89" s="5"/>
-      <c r="H89" s="5"/>
+      <c r="H89" s="10"/>
       <c r="I89" s="5"/>
       <c r="J89" s="6" t="str">
         <f>IF(B89="","",IFERROR(LOOKUP(2,1/($B$2:B88=B89),$L$2:L88),VLOOKUP(B89,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -5130,7 +5120,7 @@
       <c r="E90" s="5"/>
       <c r="F90" s="5"/>
       <c r="G90" s="5"/>
-      <c r="H90" s="5"/>
+      <c r="H90" s="10"/>
       <c r="I90" s="5"/>
       <c r="J90" s="6" t="str">
         <f>IF(B90="","",IFERROR(LOOKUP(2,1/($B$2:B89=B90),$L$2:L89),VLOOKUP(B90,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -5173,7 +5163,7 @@
       <c r="E91" s="5"/>
       <c r="F91" s="5"/>
       <c r="G91" s="5"/>
-      <c r="H91" s="5"/>
+      <c r="H91" s="10"/>
       <c r="I91" s="5"/>
       <c r="J91" s="6" t="str">
         <f>IF(B91="","",IFERROR(LOOKUP(2,1/($B$2:B90=B91),$L$2:L90),VLOOKUP(B91,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -5216,7 +5206,7 @@
       <c r="E92" s="5"/>
       <c r="F92" s="5"/>
       <c r="G92" s="5"/>
-      <c r="H92" s="5"/>
+      <c r="H92" s="10"/>
       <c r="I92" s="5"/>
       <c r="J92" s="6" t="str">
         <f>IF(B92="","",IFERROR(LOOKUP(2,1/($B$2:B91=B92),$L$2:L91),VLOOKUP(B92,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -5259,7 +5249,7 @@
       <c r="E93" s="5"/>
       <c r="F93" s="5"/>
       <c r="G93" s="5"/>
-      <c r="H93" s="5"/>
+      <c r="H93" s="10"/>
       <c r="I93" s="5"/>
       <c r="J93" s="6" t="str">
         <f>IF(B93="","",IFERROR(LOOKUP(2,1/($B$2:B92=B93),$L$2:L92),VLOOKUP(B93,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -5302,7 +5292,7 @@
       <c r="E94" s="5"/>
       <c r="F94" s="5"/>
       <c r="G94" s="5"/>
-      <c r="H94" s="5"/>
+      <c r="H94" s="10"/>
       <c r="I94" s="5"/>
       <c r="J94" s="6" t="str">
         <f>IF(B94="","",IFERROR(LOOKUP(2,1/($B$2:B93=B94),$L$2:L93),VLOOKUP(B94,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -5345,7 +5335,7 @@
       <c r="E95" s="5"/>
       <c r="F95" s="5"/>
       <c r="G95" s="5"/>
-      <c r="H95" s="5"/>
+      <c r="H95" s="10"/>
       <c r="I95" s="5"/>
       <c r="J95" s="6" t="str">
         <f>IF(B95="","",IFERROR(LOOKUP(2,1/($B$2:B94=B95),$L$2:L94),VLOOKUP(B95,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -5388,7 +5378,7 @@
       <c r="E96" s="5"/>
       <c r="F96" s="5"/>
       <c r="G96" s="5"/>
-      <c r="H96" s="5"/>
+      <c r="H96" s="10"/>
       <c r="I96" s="5"/>
       <c r="J96" s="6" t="str">
         <f>IF(B96="","",IFERROR(LOOKUP(2,1/($B$2:B95=B96),$L$2:L95),VLOOKUP(B96,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -5431,7 +5421,7 @@
       <c r="E97" s="5"/>
       <c r="F97" s="5"/>
       <c r="G97" s="5"/>
-      <c r="H97" s="5"/>
+      <c r="H97" s="10"/>
       <c r="I97" s="5"/>
       <c r="J97" s="6" t="str">
         <f>IF(B97="","",IFERROR(LOOKUP(2,1/($B$2:B96=B97),$L$2:L96),VLOOKUP(B97,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -5442,7 +5432,7 @@
         <v/>
       </c>
       <c r="L97" s="6" t="str">
-        <f t="shared" ref="L97:L99" si="6">IF(B97="","",IF(K97="Transfer",D97,J97))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="M97" s="8" t="str">
@@ -5474,7 +5464,7 @@
       <c r="E98" s="5"/>
       <c r="F98" s="5"/>
       <c r="G98" s="5"/>
-      <c r="H98" s="5"/>
+      <c r="H98" s="10"/>
       <c r="I98" s="5"/>
       <c r="J98" s="6" t="str">
         <f>IF(B98="","",IFERROR(LOOKUP(2,1/($B$2:B97=B98),$L$2:L97),VLOOKUP(B98,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -5485,7 +5475,7 @@
         <v/>
       </c>
       <c r="L98" s="6" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="L98:L100" si="6">IF(B98="","",IF(K98="Transfer",D98,J98))</f>
         <v/>
       </c>
       <c r="M98" s="8" t="str">
@@ -5517,7 +5507,7 @@
       <c r="E99" s="5"/>
       <c r="F99" s="5"/>
       <c r="G99" s="5"/>
-      <c r="H99" s="5"/>
+      <c r="H99" s="10"/>
       <c r="I99" s="5"/>
       <c r="J99" s="6" t="str">
         <f>IF(B99="","",IFERROR(LOOKUP(2,1/($B$2:B98=B99),$L$2:L98),VLOOKUP(B99,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -5549,27 +5539,51 @@
       </c>
       <c r="Q99" s="5"/>
     </row>
+    <row r="100" spans="1:17">
+      <c r="A100" s="6" t="str">
+        <f>IF(OR(B100="",C100=""),"",VLOOKUP(B100,Lists!$A$2:$B$10,2,FALSE)&amp;"-"&amp;TEXT(C100,"yyyymmdd")&amp;"-"&amp;TEXT(COUNTIFS($B$2:B100,B100,$C$2:C100,C100),"00"))</f>
+        <v/>
+      </c>
+      <c r="B100" s="5"/>
+      <c r="C100" s="7"/>
+      <c r="D100" s="5"/>
+      <c r="E100" s="5"/>
+      <c r="F100" s="5"/>
+      <c r="G100" s="5"/>
+      <c r="H100" s="10"/>
+      <c r="I100" s="5"/>
+      <c r="J100" s="6" t="str">
+        <f>IF(B100="","",IFERROR(LOOKUP(2,1/($B$2:B99=B100),$L$2:L99),VLOOKUP(B100,Baseline!$A$2:$H$10,4,FALSE)))</f>
+        <v/>
+      </c>
+      <c r="K100" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L100" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="M100" s="8" t="str">
+        <f>IF(B100="","",IF(K100="Transfer",C100,IFERROR(LOOKUP(2,1/($B$2:B99=B100),$M$2:M99),VLOOKUP(B100,Baseline!$A$2:$H$10,5,FALSE))))</f>
+        <v/>
+      </c>
+      <c r="N100" s="6" t="str">
+        <f>IF(B100="","",IF(K100="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B99=B100),$N$2:N99),VLOOKUP(B100,Baseline!$A$2:$H$10,6,FALSE))+IF(K100="Defence",1,0)))</f>
+        <v/>
+      </c>
+      <c r="O100" s="6" t="str">
+        <f>IF(B100="","",IFERROR(LOOKUP(2,1/($B$2:B99=B100),$O$2:O99),VLOOKUP(B100,Baseline!$A$2:$H$10,7,FALSE))+IF(K100="Transfer",1,0))</f>
+        <v/>
+      </c>
+      <c r="P100" s="6" t="str">
+        <f>IF(B100="","",IFERROR(LOOKUP(2,1/($B$2:B99=B100),$P$2:P99),VLOOKUP(B100,Baseline!$A$2:$H$10,8,FALSE))+IF(K100="Defence",1,0))</f>
+        <v/>
+      </c>
+      <c r="Q100" s="5"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0300-000000000000}">
-          <x14:formula1>
-            <xm:f>Lists!$D$2:$D$6</xm:f>
-          </x14:formula1>
-          <xm:sqref>F2:F99</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0300-000001000000}">
-          <x14:formula1>
-            <xm:f>Lists!$E$2:$E$5</xm:f>
-          </x14:formula1>
-          <xm:sqref>G2:G99</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -5613,31 +5627,31 @@
         <v>30</v>
       </c>
       <c r="B2" t="str">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A2),Updates!$L$2:$L$99),VLOOKUP(A2,Baseline!$A$2:$H$10,4,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A2),Updates!$L$2:$L$100),VLOOKUP(A2,Baseline!$A$2:$H$10,4,FALSE))</f>
         <v>South Africa</v>
       </c>
       <c r="C2" s="4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A2),Updates!$M$2:$M$99),VLOOKUP(A2,Baseline!$A$2:$H$10,5,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A2),Updates!$M$2:$M$100),VLOOKUP(A2,Baseline!$A$2:$H$10,5,FALSE))</f>
         <v>45953</v>
       </c>
       <c r="D2">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A2),Updates!$N$2:$N$99),VLOOKUP(A2,Baseline!$A$2:$H$10,6,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A2),Updates!$N$2:$N$100),VLOOKUP(A2,Baseline!$A$2:$H$10,6,FALSE))</f>
         <v>2</v>
       </c>
       <c r="E2">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A2),Updates!$O$2:$O$99),VLOOKUP(A2,Baseline!$A$2:$H$10,7,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A2),Updates!$O$2:$O$100),VLOOKUP(A2,Baseline!$A$2:$H$10,7,FALSE))</f>
         <v>172</v>
       </c>
       <c r="F2">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A2),Updates!$P$2:$P$99),VLOOKUP(A2,Baseline!$A$2:$H$10,8,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A2),Updates!$P$2:$P$100),VLOOKUP(A2,Baseline!$A$2:$H$10,8,FALSE))</f>
         <v>270</v>
       </c>
       <c r="G2" s="4">
-        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A2)*(Updates!$F$2:$F$99&lt;&gt;"Completed")*(Updates!$F$2:$F$99&lt;&gt;"Cancelled")*(Updates!$F$2:$F$99&lt;&gt;"Postponed")),Updates!$C$2:$C$99),"TBD")</f>
+        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A2)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
         <v>46304</v>
       </c>
       <c r="H2" t="str">
-        <f>IF(G2="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A2)*(Updates!$C$2:$C$99=G2)),Updates!$D$2:$D$99),"TBD"))</f>
+        <f>IF(G2="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A2)*(Updates!$C$2:$C$100=G2)),Updates!$D$2:$D$100),"TBD"))</f>
         <v>Australia</v>
       </c>
     </row>
@@ -5646,31 +5660,31 @@
         <v>34</v>
       </c>
       <c r="B3" t="str">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A3),Updates!$L$2:$L$99),VLOOKUP(A3,Baseline!$A$2:$H$10,4,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A3),Updates!$L$2:$L$100),VLOOKUP(A3,Baseline!$A$2:$H$10,4,FALSE))</f>
         <v>Australia</v>
       </c>
       <c r="C3" s="4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A3),Updates!$M$2:$M$99),VLOOKUP(A3,Baseline!$A$2:$H$10,5,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A3),Updates!$M$2:$M$100),VLOOKUP(A3,Baseline!$A$2:$H$10,5,FALSE))</f>
         <v>46089</v>
       </c>
       <c r="D3">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A3),Updates!$N$2:$N$99),VLOOKUP(A3,Baseline!$A$2:$H$10,6,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A3),Updates!$N$2:$N$100),VLOOKUP(A3,Baseline!$A$2:$H$10,6,FALSE))</f>
         <v>0</v>
       </c>
       <c r="E3">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A3),Updates!$O$2:$O$99),VLOOKUP(A3,Baseline!$A$2:$H$10,7,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A3),Updates!$O$2:$O$100),VLOOKUP(A3,Baseline!$A$2:$H$10,7,FALSE))</f>
         <v>8</v>
       </c>
       <c r="F3">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A3),Updates!$P$2:$P$99),VLOOKUP(A3,Baseline!$A$2:$H$10,8,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A3),Updates!$P$2:$P$100),VLOOKUP(A3,Baseline!$A$2:$H$10,8,FALSE))</f>
         <v>4</v>
       </c>
       <c r="G3" s="4">
-        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A3)*(Updates!$F$2:$F$99&lt;&gt;"Completed")*(Updates!$F$2:$F$99&lt;&gt;"Cancelled")*(Updates!$F$2:$F$99&lt;&gt;"Postponed")),Updates!$C$2:$C$99),"TBD")</f>
+        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A3)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
         <v>46562</v>
       </c>
       <c r="H3" t="str">
-        <f>IF(G3="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A3)*(Updates!$C$2:$C$99=G3)),Updates!$D$2:$D$99),"TBD"))</f>
+        <f>IF(G3="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A3)*(Updates!$C$2:$C$100=G3)),Updates!$D$2:$D$100),"TBD"))</f>
         <v>England</v>
       </c>
     </row>
@@ -5679,31 +5693,31 @@
         <v>37</v>
       </c>
       <c r="B4" t="str">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A4),Updates!$L$2:$L$99),VLOOKUP(A4,Baseline!$A$2:$H$10,4,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A4),Updates!$L$2:$L$100),VLOOKUP(A4,Baseline!$A$2:$H$10,4,FALSE))</f>
         <v>Australia</v>
       </c>
       <c r="C4" s="4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A4),Updates!$M$2:$M$99),VLOOKUP(A4,Baseline!$A$2:$H$10,5,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A4),Updates!$M$2:$M$100),VLOOKUP(A4,Baseline!$A$2:$H$10,5,FALSE))</f>
         <v>46187</v>
       </c>
       <c r="D4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A4),Updates!$N$2:$N$99),VLOOKUP(A4,Baseline!$A$2:$H$10,6,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A4),Updates!$N$2:$N$100),VLOOKUP(A4,Baseline!$A$2:$H$10,6,FALSE))</f>
         <v>0</v>
       </c>
       <c r="E4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A4),Updates!$O$2:$O$99),VLOOKUP(A4,Baseline!$A$2:$H$10,7,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A4),Updates!$O$2:$O$100),VLOOKUP(A4,Baseline!$A$2:$H$10,7,FALSE))</f>
         <v>358</v>
       </c>
       <c r="F4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A4),Updates!$P$2:$P$99),VLOOKUP(A4,Baseline!$A$2:$H$10,8,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A4),Updates!$P$2:$P$100),VLOOKUP(A4,Baseline!$A$2:$H$10,8,FALSE))</f>
         <v>596</v>
       </c>
       <c r="G4" s="4">
-        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A4)*(Updates!$F$2:$F$99&lt;&gt;"Completed")*(Updates!$F$2:$F$99&lt;&gt;"Cancelled")*(Updates!$F$2:$F$99&lt;&gt;"Postponed")),Updates!$C$2:$C$99),"TBD")</f>
+        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A4)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
         <v>46280</v>
       </c>
       <c r="H4" t="str">
-        <f>IF(G4="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A4)*(Updates!$C$2:$C$99=G4)),Updates!$D$2:$D$99),"TBD"))</f>
+        <f>IF(G4="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A4)*(Updates!$C$2:$C$100=G4)),Updates!$D$2:$D$100),"TBD"))</f>
         <v>Zimbabwe</v>
       </c>
     </row>
@@ -5712,31 +5726,31 @@
         <v>39</v>
       </c>
       <c r="B5" t="str">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A5),Updates!$L$2:$L$99),VLOOKUP(A5,Baseline!$A$2:$H$10,4,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A5),Updates!$L$2:$L$100),VLOOKUP(A5,Baseline!$A$2:$H$10,4,FALSE))</f>
         <v>Australia</v>
       </c>
       <c r="C5" s="4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A5),Updates!$M$2:$M$99),VLOOKUP(A5,Baseline!$A$2:$H$10,5,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A5),Updates!$M$2:$M$100),VLOOKUP(A5,Baseline!$A$2:$H$10,5,FALSE))</f>
         <v>46077</v>
       </c>
       <c r="D5">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A5),Updates!$N$2:$N$99),VLOOKUP(A5,Baseline!$A$2:$H$10,6,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A5),Updates!$N$2:$N$100),VLOOKUP(A5,Baseline!$A$2:$H$10,6,FALSE))</f>
         <v>5</v>
       </c>
       <c r="E5">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A5),Updates!$O$2:$O$99),VLOOKUP(A5,Baseline!$A$2:$H$10,7,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A5),Updates!$O$2:$O$100),VLOOKUP(A5,Baseline!$A$2:$H$10,7,FALSE))</f>
         <v>120</v>
       </c>
       <c r="F5">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A5),Updates!$P$2:$P$99),VLOOKUP(A5,Baseline!$A$2:$H$10,8,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A5),Updates!$P$2:$P$100),VLOOKUP(A5,Baseline!$A$2:$H$10,8,FALSE))</f>
         <v>251</v>
       </c>
       <c r="G5" s="4">
-        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A5)*(Updates!$F$2:$F$99&lt;&gt;"Completed")*(Updates!$F$2:$F$99&lt;&gt;"Cancelled")*(Updates!$F$2:$F$99&lt;&gt;"Postponed")),Updates!$C$2:$C$99),"TBD")</f>
+        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A5)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
         <v>46304</v>
       </c>
       <c r="H5" t="str">
-        <f>IF(G5="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A5)*(Updates!$C$2:$C$99=G5)),Updates!$D$2:$D$99),"TBD"))</f>
+        <f>IF(G5="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A5)*(Updates!$C$2:$C$100=G5)),Updates!$D$2:$D$100),"TBD"))</f>
         <v>Bangladesh</v>
       </c>
     </row>
@@ -5745,31 +5759,31 @@
         <v>41</v>
       </c>
       <c r="B6" t="str">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A6),Updates!$L$2:$L$99),VLOOKUP(A6,Baseline!$A$2:$H$10,4,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A6),Updates!$L$2:$L$100),VLOOKUP(A6,Baseline!$A$2:$H$10,4,FALSE))</f>
         <v>Ireland</v>
       </c>
       <c r="C6" s="4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A6),Updates!$M$2:$M$99),VLOOKUP(A6,Baseline!$A$2:$H$10,5,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A6),Updates!$M$2:$M$100),VLOOKUP(A6,Baseline!$A$2:$H$10,5,FALSE))</f>
         <v>46199</v>
       </c>
       <c r="D6">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A6),Updates!$N$2:$N$99),VLOOKUP(A6,Baseline!$A$2:$H$10,6,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A6),Updates!$N$2:$N$100),VLOOKUP(A6,Baseline!$A$2:$H$10,6,FALSE))</f>
         <v>1</v>
       </c>
       <c r="E6">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A6),Updates!$O$2:$O$99),VLOOKUP(A6,Baseline!$A$2:$H$10,7,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A6),Updates!$O$2:$O$100),VLOOKUP(A6,Baseline!$A$2:$H$10,7,FALSE))</f>
         <v>89</v>
       </c>
       <c r="F6">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A6),Updates!$P$2:$P$99),VLOOKUP(A6,Baseline!$A$2:$H$10,8,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A6),Updates!$P$2:$P$100),VLOOKUP(A6,Baseline!$A$2:$H$10,8,FALSE))</f>
         <v>152</v>
       </c>
       <c r="G6" s="4" t="str">
-        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A6)*(Updates!$F$2:$F$99&lt;&gt;"Completed")*(Updates!$F$2:$F$99&lt;&gt;"Cancelled")*(Updates!$F$2:$F$99&lt;&gt;"Postponed")),Updates!$C$2:$C$99),"TBD")</f>
+        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A6)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
         <v>TBD</v>
       </c>
       <c r="H6" t="str">
-        <f>IF(G6="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A6)*(Updates!$C$2:$C$99=G6)),Updates!$D$2:$D$99),"TBD"))</f>
+        <f>IF(G6="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A6)*(Updates!$C$2:$C$100=G6)),Updates!$D$2:$D$100),"TBD"))</f>
         <v>TBD</v>
       </c>
     </row>
@@ -5778,31 +5792,31 @@
         <v>44</v>
       </c>
       <c r="B7" t="str">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A7),Updates!$L$2:$L$99),VLOOKUP(A7,Baseline!$A$2:$H$10,4,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A7),Updates!$L$2:$L$100),VLOOKUP(A7,Baseline!$A$2:$H$10,4,FALSE))</f>
         <v>Australia</v>
       </c>
       <c r="C7" s="4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A7),Updates!$M$2:$M$99),VLOOKUP(A7,Baseline!$A$2:$H$10,5,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A7),Updates!$M$2:$M$100),VLOOKUP(A7,Baseline!$A$2:$H$10,5,FALSE))</f>
         <v>46186</v>
       </c>
       <c r="D7">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A7),Updates!$N$2:$N$99),VLOOKUP(A7,Baseline!$A$2:$H$10,6,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A7),Updates!$N$2:$N$100),VLOOKUP(A7,Baseline!$A$2:$H$10,6,FALSE))</f>
         <v>6</v>
       </c>
       <c r="E7">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A7),Updates!$O$2:$O$99),VLOOKUP(A7,Baseline!$A$2:$H$10,7,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A7),Updates!$O$2:$O$100),VLOOKUP(A7,Baseline!$A$2:$H$10,7,FALSE))</f>
         <v>76</v>
       </c>
       <c r="F7">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A7),Updates!$P$2:$P$99),VLOOKUP(A7,Baseline!$A$2:$H$10,8,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A7),Updates!$P$2:$P$100),VLOOKUP(A7,Baseline!$A$2:$H$10,8,FALSE))</f>
         <v>139</v>
       </c>
       <c r="G7" s="4">
-        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A7)*(Updates!$F$2:$F$99&lt;&gt;"Completed")*(Updates!$F$2:$F$99&lt;&gt;"Cancelled")*(Updates!$F$2:$F$99&lt;&gt;"Postponed")),Updates!$C$2:$C$99),"TBD")</f>
+        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A7)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
         <v>46313</v>
       </c>
       <c r="H7" t="str">
-        <f>IF(G7="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A7)*(Updates!$C$2:$C$99=G7)),Updates!$D$2:$D$99),"TBD"))</f>
+        <f>IF(G7="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A7)*(Updates!$C$2:$C$100=G7)),Updates!$D$2:$D$100),"TBD"))</f>
         <v>New Zealand</v>
       </c>
     </row>
@@ -5811,31 +5825,31 @@
         <v>46</v>
       </c>
       <c r="B8" t="str">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A8),Updates!$L$2:$L$99),VLOOKUP(A8,Baseline!$A$2:$H$10,4,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A8),Updates!$L$2:$L$100),VLOOKUP(A8,Baseline!$A$2:$H$10,4,FALSE))</f>
         <v>Royal Challengers Bengaluru</v>
       </c>
       <c r="C8" s="4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A8),Updates!$M$2:$M$99),VLOOKUP(A8,Baseline!$A$2:$H$10,5,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A8),Updates!$M$2:$M$100),VLOOKUP(A8,Baseline!$A$2:$H$10,5,FALSE))</f>
         <v>46173</v>
       </c>
       <c r="D8">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A8),Updates!$N$2:$N$99),VLOOKUP(A8,Baseline!$A$2:$H$10,6,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A8),Updates!$N$2:$N$100),VLOOKUP(A8,Baseline!$A$2:$H$10,6,FALSE))</f>
         <v>0</v>
       </c>
       <c r="E8">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A8),Updates!$O$2:$O$99),VLOOKUP(A8,Baseline!$A$2:$H$10,7,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A8),Updates!$O$2:$O$100),VLOOKUP(A8,Baseline!$A$2:$H$10,7,FALSE))</f>
         <v>150</v>
       </c>
       <c r="F8">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A8),Updates!$P$2:$P$99),VLOOKUP(A8,Baseline!$A$2:$H$10,8,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A8),Updates!$P$2:$P$100),VLOOKUP(A8,Baseline!$A$2:$H$10,8,FALSE))</f>
         <v>125</v>
       </c>
       <c r="G8" s="4" t="str">
-        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A8)*(Updates!$F$2:$F$99&lt;&gt;"Completed")*(Updates!$F$2:$F$99&lt;&gt;"Cancelled")*(Updates!$F$2:$F$99&lt;&gt;"Postponed")),Updates!$C$2:$C$99),"TBD")</f>
+        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A8)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
         <v>TBD</v>
       </c>
       <c r="H8" t="str">
-        <f>IF(G8="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A8)*(Updates!$C$2:$C$99=G8)),Updates!$D$2:$D$99),"TBD"))</f>
+        <f>IF(G8="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A8)*(Updates!$C$2:$C$100=G8)),Updates!$D$2:$D$100),"TBD"))</f>
         <v>TBD</v>
       </c>
     </row>
@@ -5844,32 +5858,32 @@
         <v>49</v>
       </c>
       <c r="B9" t="str">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A9),Updates!$L$2:$L$99),VLOOKUP(A9,Baseline!$A$2:$H$10,4,FALSE))</f>
-        <v>VfB Stuttgart</v>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A9),Updates!$L$2:$L$100),VLOOKUP(A9,Baseline!$A$2:$H$10,4,FALSE))</f>
+        <v>Bayern München</v>
       </c>
       <c r="C9" s="4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A9),Updates!$M$2:$M$99),VLOOKUP(A9,Baseline!$A$2:$H$10,5,FALSE))</f>
-        <v>46262</v>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A9),Updates!$M$2:$M$100),VLOOKUP(A9,Baseline!$A$2:$H$10,5,FALSE))</f>
+        <v>46081</v>
       </c>
       <c r="D9">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A9),Updates!$N$2:$N$99),VLOOKUP(A9,Baseline!$A$2:$H$10,6,FALSE))</f>
-        <v>1</v>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A9),Updates!$N$2:$N$100),VLOOKUP(A9,Baseline!$A$2:$H$10,6,FALSE))</f>
+        <v>11</v>
       </c>
       <c r="E9">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A9),Updates!$O$2:$O$99),VLOOKUP(A9,Baseline!$A$2:$H$10,7,FALSE))</f>
-        <v>682</v>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A9),Updates!$O$2:$O$100),VLOOKUP(A9,Baseline!$A$2:$H$10,7,FALSE))</f>
+        <v>681</v>
       </c>
       <c r="F9">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A9),Updates!$P$2:$P$99),VLOOKUP(A9,Baseline!$A$2:$H$10,8,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A9),Updates!$P$2:$P$100),VLOOKUP(A9,Baseline!$A$2:$H$10,8,FALSE))</f>
         <v>1443</v>
       </c>
-      <c r="G9" s="4" t="str">
-        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A9)*(Updates!$F$2:$F$99&lt;&gt;"Completed")*(Updates!$F$2:$F$99&lt;&gt;"Cancelled")*(Updates!$F$2:$F$99&lt;&gt;"Postponed")),Updates!$C$2:$C$99),"TBD")</f>
-        <v>TBD</v>
+      <c r="G9" s="4">
+        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A9)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
+        <v>46269</v>
       </c>
       <c r="H9" t="str">
-        <f>IF(G9="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A9)*(Updates!$C$2:$C$99=G9)),Updates!$D$2:$D$99),"TBD"))</f>
-        <v>TBD</v>
+        <f>IF(G9="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A9)*(Updates!$C$2:$C$100=G9)),Updates!$D$2:$D$100),"TBD"))</f>
+        <v>FC Schalke 04</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -5877,37 +5891,36 @@
         <v>53</v>
       </c>
       <c r="B10" t="str">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A10),Updates!$L$2:$L$99),VLOOKUP(A10,Baseline!$A$2:$H$10,4,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A10),Updates!$L$2:$L$100),VLOOKUP(A10,Baseline!$A$2:$H$10,4,FALSE))</f>
         <v>Bayern München</v>
       </c>
       <c r="C10" s="4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A10),Updates!$M$2:$M$99),VLOOKUP(A10,Baseline!$A$2:$H$10,5,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A10),Updates!$M$2:$M$100),VLOOKUP(A10,Baseline!$A$2:$H$10,5,FALSE))</f>
         <v>45730</v>
       </c>
       <c r="D10">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A10),Updates!$N$2:$N$99),VLOOKUP(A10,Baseline!$A$2:$H$10,6,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A10),Updates!$N$2:$N$100),VLOOKUP(A10,Baseline!$A$2:$H$10,6,FALSE))</f>
         <v>32</v>
       </c>
       <c r="E10">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A10),Updates!$O$2:$O$99),VLOOKUP(A10,Baseline!$A$2:$H$10,7,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A10),Updates!$O$2:$O$100),VLOOKUP(A10,Baseline!$A$2:$H$10,7,FALSE))</f>
         <v>113</v>
       </c>
       <c r="F10">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A10),Updates!$P$2:$P$99),VLOOKUP(A10,Baseline!$A$2:$H$10,8,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A10),Updates!$P$2:$P$100),VLOOKUP(A10,Baseline!$A$2:$H$10,8,FALSE))</f>
         <v>655</v>
       </c>
       <c r="G10" s="4">
-        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A10)*(Updates!$F$2:$F$99&lt;&gt;"Completed")*(Updates!$F$2:$F$99&lt;&gt;"Cancelled")*(Updates!$F$2:$F$99&lt;&gt;"Postponed")),Updates!$C$2:$C$99),"TBD")</f>
+        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A10)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
         <v>46265</v>
       </c>
       <c r="H10" t="str">
-        <f>IF(G10="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A10)*(Updates!$C$2:$C$99=G10)),Updates!$D$2:$D$99),"TBD"))</f>
+        <f>IF(G10="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A10)*(Updates!$C$2:$C$100=G10)),Updates!$D$2:$D$100),"TBD"))</f>
         <v>1. FSV Mainz 05</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6191,31 +6204,31 @@
       </c>
       <c r="B9" t="str">
         <f>Dashboard!B9</f>
-        <v>VfB Stuttgart</v>
+        <v>Bayern München</v>
       </c>
       <c r="C9" s="9">
         <f>Dashboard!C9</f>
-        <v>46262</v>
+        <v>46081</v>
       </c>
       <c r="D9">
         <f>Dashboard!D9</f>
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E9">
         <f>Dashboard!E9</f>
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F9">
         <f>Dashboard!F9</f>
         <v>1443</v>
       </c>
-      <c r="G9" s="9" t="str">
+      <c r="G9" s="9">
         <f>Dashboard!G9</f>
-        <v>TBD</v>
+        <v>46269</v>
       </c>
       <c r="H9" t="str">
         <f>Dashboard!H9</f>
-        <v>TBD</v>
+        <v>FC Schalke 04</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -6254,6 +6267,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
--- a/LSC_Update_System.xlsx
+++ b/LSC_Update_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CH\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97C79068-F26B-4BD2-BDFB-D0572761CBA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01762227-DC3B-4A59-A6CF-F532DCA4838D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="119">
   <si>
     <t>LSC UPDATE SYSTEM — SAFE TEST</t>
   </si>
@@ -392,10 +392,7 @@
     <t>Fixture End Date (optional)</t>
   </si>
   <si>
-    <t xml:space="preserve">challenger win </t>
-  </si>
-  <si>
-    <t>outh Africa lost to Australia — TEST DATA</t>
+    <t>outh Africa lost to Australia</t>
   </si>
 </sst>
 </file>
@@ -1293,11 +1290,11 @@
       <c r="F2" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2" t="s">
         <v>118</v>
-      </c>
-      <c r="H2" t="s">
-        <v>119</v>
       </c>
       <c r="I2" s="5"/>
       <c r="J2" s="6" t="str">
@@ -1306,23 +1303,23 @@
       </c>
       <c r="K2" s="6" t="str">
         <f t="shared" ref="K2:K33" si="0">IF(B2="","",IF(F2&lt;&gt;"Completed",F2,IF(G2="Challenger win","Transfer",IF(OR(G2="Holder win",G2="Draw / tie"),"Defence",IF(G2="No result","No result","REVIEW")))))</f>
-        <v>REVIEW</v>
+        <v>Transfer</v>
       </c>
       <c r="L2" s="6" t="str">
         <f t="shared" ref="L2:L33" si="1">IF(B2="","",IF(K2="Transfer",D2,J2))</f>
-        <v>South Africa</v>
+        <v>Australia</v>
       </c>
       <c r="M2" s="8">
         <f>IF(B2="","",IF(K2="Transfer",C2,VLOOKUP(B2,Baseline!$A$2:$H$10,5,FALSE)))</f>
-        <v>45953</v>
+        <v>46304</v>
       </c>
       <c r="N2" s="6">
         <f>IF(B2="","",IF(K2="Transfer",0,VLOOKUP(B2,Baseline!$A$2:$H$10,6,FALSE)+IF(K2="Defence",1,0)))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O2" s="6">
         <f>IF(B2="","",VLOOKUP(B2,Baseline!$A$2:$H$10,7,FALSE)+IF(K2="Transfer",1,0))</f>
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P2" s="6">
         <f>IF(B2="","",VLOOKUP(B2,Baseline!$A$2:$H$10,8,FALSE)+IF(K2="Defence",1,0))</f>
@@ -5763,19 +5760,19 @@
       </c>
       <c r="B2" t="str">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A2),Updates!$L$2:$L$100),VLOOKUP(A2,Baseline!$A$2:$H$10,4,FALSE))</f>
-        <v>South Africa</v>
+        <v>Australia</v>
       </c>
       <c r="C2" s="4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A2),Updates!$M$2:$M$100),VLOOKUP(A2,Baseline!$A$2:$H$10,5,FALSE))</f>
-        <v>45953</v>
+        <v>46304</v>
       </c>
       <c r="D2">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A2),Updates!$N$2:$N$100),VLOOKUP(A2,Baseline!$A$2:$H$10,6,FALSE))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A2),Updates!$O$2:$O$100),VLOOKUP(A2,Baseline!$A$2:$H$10,7,FALSE))</f>
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F2">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A2),Updates!$P$2:$P$100),VLOOKUP(A2,Baseline!$A$2:$H$10,8,FALSE))</f>
@@ -6101,19 +6098,19 @@
       </c>
       <c r="B2" t="str">
         <f>Dashboard!B2</f>
-        <v>South Africa</v>
+        <v>Australia</v>
       </c>
       <c r="C2" s="9">
         <f>Dashboard!C2</f>
-        <v>45953</v>
+        <v>46304</v>
       </c>
       <c r="D2">
         <f>Dashboard!D2</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <f>Dashboard!E2</f>
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F2">
         <f>Dashboard!F2</f>

--- a/LSC_Update_System.xlsx
+++ b/LSC_Update_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CH\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01762227-DC3B-4A59-A6CF-F532DCA4838D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_023717A8391A607FB11835ABBFFFF4DEB130EFC4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="118">
   <si>
     <t>LSC UPDATE SYSTEM — SAFE TEST</t>
   </si>
@@ -390,9 +390,6 @@
   </si>
   <si>
     <t>Fixture End Date (optional)</t>
-  </si>
-  <si>
-    <t>outh Africa lost to Australia</t>
   </si>
 </sst>
 </file>
@@ -481,7 +478,19 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF991B1B"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFECACA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1288,41 +1297,37 @@
         <v>88</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H2" t="s">
-        <v>118</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="G2" s="5"/>
+      <c r="H2" s="10"/>
       <c r="I2" s="5"/>
       <c r="J2" s="6" t="str">
         <f>IF(B2="","",VLOOKUP(B2,Baseline!$A$2:$H$10,4,FALSE))</f>
         <v>South Africa</v>
       </c>
       <c r="K2" s="6" t="str">
-        <f t="shared" ref="K2:K33" si="0">IF(B2="","",IF(F2&lt;&gt;"Completed",F2,IF(G2="Challenger win","Transfer",IF(OR(G2="Holder win",G2="Draw / tie"),"Defence",IF(G2="No result","No result","REVIEW")))))</f>
-        <v>Transfer</v>
+        <f t="shared" ref="K2:K33" si="0">IF(B2="","",IF(F2&lt;&gt;"Completed",F2,IF(G2="Challenger win","Transfer",IF(OR(G2="Holder win",G2="Draw / tie"),"Defence",IF(G2="No result","No result","INVALID — CHECK RESULT TYPE")))))</f>
+        <v>Scheduled</v>
       </c>
       <c r="L2" s="6" t="str">
-        <f t="shared" ref="L2:L33" si="1">IF(B2="","",IF(K2="Transfer",D2,J2))</f>
-        <v>Australia</v>
+        <f t="shared" ref="L2:L33" si="1">IF(B2="","",IF(K2="INVALID — CHECK RESULT TYPE","",IF(K2="Transfer",D2,J2)))</f>
+        <v>South Africa</v>
       </c>
       <c r="M2" s="8">
-        <f>IF(B2="","",IF(K2="Transfer",C2,VLOOKUP(B2,Baseline!$A$2:$H$10,5,FALSE)))</f>
-        <v>46304</v>
+        <f>IF(B2="","",IF(K2="INVALID — CHECK RESULT TYPE","",IF(K2="Transfer",IF(R2&lt;&gt;"",R2,C2),VLOOKUP(B2,Baseline!$A$2:$H$10,5,FALSE))))</f>
+        <v>45953</v>
       </c>
       <c r="N2" s="6">
-        <f>IF(B2="","",IF(K2="Transfer",0,VLOOKUP(B2,Baseline!$A$2:$H$10,6,FALSE)+IF(K2="Defence",1,0)))</f>
-        <v>0</v>
+        <f>IF(B2="","",IF(K2="INVALID — CHECK RESULT TYPE","",IF(K2="Transfer",0,VLOOKUP(B2,Baseline!$A$2:$H$10,6,FALSE)+IF(K2="Defence",1,0))))</f>
+        <v>2</v>
       </c>
       <c r="O2" s="6">
-        <f>IF(B2="","",VLOOKUP(B2,Baseline!$A$2:$H$10,7,FALSE)+IF(K2="Transfer",1,0))</f>
-        <v>173</v>
+        <f>IF(B2="","",IF(K2="INVALID — CHECK RESULT TYPE","",VLOOKUP(B2,Baseline!$A$2:$H$10,7,FALSE)+IF(K2="Transfer",1,0)))</f>
+        <v>172</v>
       </c>
       <c r="P2" s="6">
-        <f>IF(B2="","",VLOOKUP(B2,Baseline!$A$2:$H$10,8,FALSE)+IF(K2="Defence",1,0))</f>
+        <f>IF(B2="","",IF(K2="INVALID — CHECK RESULT TYPE","",VLOOKUP(B2,Baseline!$A$2:$H$10,8,FALSE)+IF(K2="Defence",1,0)))</f>
         <v>270</v>
       </c>
       <c r="Q2" s="5"/>
@@ -1366,19 +1371,19 @@
         <v>Australia</v>
       </c>
       <c r="M3" s="8">
-        <f>IF(B3="","",IF(K3="Transfer",C3,IFERROR(LOOKUP(2,1/($B$2:B2=B3),$M$2:M2),VLOOKUP(B3,Baseline!$A$2:$H$10,5,FALSE))))</f>
+        <f>IF(B3="","",IF(K3="INVALID — CHECK RESULT TYPE","",IF(K3="Transfer",IF(R3&lt;&gt;"",R3,C3),IFERROR(LOOKUP(2,1/($B$2:B2=B3),$M$2:M2),VLOOKUP(B3,Baseline!$A$2:$H$10,5,FALSE)))))</f>
         <v>46089</v>
       </c>
       <c r="N3" s="6">
-        <f>IF(B3="","",IF(K3="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B2=B3),$N$2:N2),VLOOKUP(B3,Baseline!$A$2:$H$10,6,FALSE))+IF(K3="Defence",1,0)))</f>
+        <f>IF(B3="","",IF(K3="INVALID — CHECK RESULT TYPE","",IF(K3="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B2=B3),$N$2:N2),VLOOKUP(B3,Baseline!$A$2:$H$10,6,FALSE))+IF(K3="Defence",1,0))))</f>
         <v>0</v>
       </c>
       <c r="O3" s="6">
-        <f>IF(B3="","",IFERROR(LOOKUP(2,1/($B$2:B2=B3),$O$2:O2),VLOOKUP(B3,Baseline!$A$2:$H$10,7,FALSE))+IF(K3="Transfer",1,0))</f>
+        <f>IF(B3="","",IF(K3="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B2=B3),$O$2:O2),VLOOKUP(B3,Baseline!$A$2:$H$10,7,FALSE))+IF(K3="Transfer",1,0)))</f>
         <v>8</v>
       </c>
       <c r="P3" s="6">
-        <f>IF(B3="","",IFERROR(LOOKUP(2,1/($B$2:B2=B3),$P$2:P2),VLOOKUP(B3,Baseline!$A$2:$H$10,8,FALSE))+IF(K3="Defence",1,0))</f>
+        <f>IF(B3="","",IF(K3="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B2=B3),$P$2:P2),VLOOKUP(B3,Baseline!$A$2:$H$10,8,FALSE))+IF(K3="Defence",1,0)))</f>
         <v>4</v>
       </c>
       <c r="Q3" s="5" t="s">
@@ -1424,19 +1429,19 @@
         <v>Australia</v>
       </c>
       <c r="M4" s="8">
-        <f>IF(B4="","",IF(K4="Transfer",C4,IFERROR(LOOKUP(2,1/($B$2:B3=B4),$M$2:M3),VLOOKUP(B4,Baseline!$A$2:$H$10,5,FALSE))))</f>
+        <f>IF(B4="","",IF(K4="INVALID — CHECK RESULT TYPE","",IF(K4="Transfer",IF(R4&lt;&gt;"",R4,C4),IFERROR(LOOKUP(2,1/($B$2:B3=B4),$M$2:M3),VLOOKUP(B4,Baseline!$A$2:$H$10,5,FALSE)))))</f>
         <v>46187</v>
       </c>
       <c r="N4" s="6">
-        <f>IF(B4="","",IF(K4="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B3=B4),$N$2:N3),VLOOKUP(B4,Baseline!$A$2:$H$10,6,FALSE))+IF(K4="Defence",1,0)))</f>
+        <f>IF(B4="","",IF(K4="INVALID — CHECK RESULT TYPE","",IF(K4="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B3=B4),$N$2:N3),VLOOKUP(B4,Baseline!$A$2:$H$10,6,FALSE))+IF(K4="Defence",1,0))))</f>
         <v>0</v>
       </c>
       <c r="O4" s="6">
-        <f>IF(B4="","",IFERROR(LOOKUP(2,1/($B$2:B3=B4),$O$2:O3),VLOOKUP(B4,Baseline!$A$2:$H$10,7,FALSE))+IF(K4="Transfer",1,0))</f>
+        <f>IF(B4="","",IF(K4="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B3=B4),$O$2:O3),VLOOKUP(B4,Baseline!$A$2:$H$10,7,FALSE))+IF(K4="Transfer",1,0)))</f>
         <v>358</v>
       </c>
       <c r="P4" s="6">
-        <f>IF(B4="","",IFERROR(LOOKUP(2,1/($B$2:B3=B4),$P$2:P3),VLOOKUP(B4,Baseline!$A$2:$H$10,8,FALSE))+IF(K4="Defence",1,0))</f>
+        <f>IF(B4="","",IF(K4="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B3=B4),$P$2:P3),VLOOKUP(B4,Baseline!$A$2:$H$10,8,FALSE))+IF(K4="Defence",1,0)))</f>
         <v>596</v>
       </c>
       <c r="Q4" s="5"/>
@@ -1478,19 +1483,19 @@
         <v>Australia</v>
       </c>
       <c r="M5" s="8">
-        <f>IF(B5="","",IF(K5="Transfer",C5,IFERROR(LOOKUP(2,1/($B$2:B4=B5),$M$2:M4),VLOOKUP(B5,Baseline!$A$2:$H$10,5,FALSE))))</f>
+        <f>IF(B5="","",IF(K5="INVALID — CHECK RESULT TYPE","",IF(K5="Transfer",IF(R5&lt;&gt;"",R5,C5),IFERROR(LOOKUP(2,1/($B$2:B4=B5),$M$2:M4),VLOOKUP(B5,Baseline!$A$2:$H$10,5,FALSE)))))</f>
         <v>46077</v>
       </c>
       <c r="N5" s="6">
-        <f>IF(B5="","",IF(K5="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B4=B5),$N$2:N4),VLOOKUP(B5,Baseline!$A$2:$H$10,6,FALSE))+IF(K5="Defence",1,0)))</f>
+        <f>IF(B5="","",IF(K5="INVALID — CHECK RESULT TYPE","",IF(K5="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B4=B5),$N$2:N4),VLOOKUP(B5,Baseline!$A$2:$H$10,6,FALSE))+IF(K5="Defence",1,0))))</f>
         <v>5</v>
       </c>
       <c r="O5" s="6">
-        <f>IF(B5="","",IFERROR(LOOKUP(2,1/($B$2:B4=B5),$O$2:O4),VLOOKUP(B5,Baseline!$A$2:$H$10,7,FALSE))+IF(K5="Transfer",1,0))</f>
+        <f>IF(B5="","",IF(K5="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B4=B5),$O$2:O4),VLOOKUP(B5,Baseline!$A$2:$H$10,7,FALSE))+IF(K5="Transfer",1,0)))</f>
         <v>120</v>
       </c>
       <c r="P5" s="6">
-        <f>IF(B5="","",IFERROR(LOOKUP(2,1/($B$2:B4=B5),$P$2:P4),VLOOKUP(B5,Baseline!$A$2:$H$10,8,FALSE))+IF(K5="Defence",1,0))</f>
+        <f>IF(B5="","",IF(K5="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B4=B5),$P$2:P4),VLOOKUP(B5,Baseline!$A$2:$H$10,8,FALSE))+IF(K5="Defence",1,0)))</f>
         <v>251</v>
       </c>
       <c r="Q5" s="5"/>
@@ -1532,19 +1537,19 @@
         <v>Australia</v>
       </c>
       <c r="M6" s="8">
-        <f>IF(B6="","",IF(K6="Transfer",C6,IFERROR(LOOKUP(2,1/($B$2:B5=B6),$M$2:M5),VLOOKUP(B6,Baseline!$A$2:$H$10,5,FALSE))))</f>
+        <f>IF(B6="","",IF(K6="INVALID — CHECK RESULT TYPE","",IF(K6="Transfer",IF(R6&lt;&gt;"",R6,C6),IFERROR(LOOKUP(2,1/($B$2:B5=B6),$M$2:M5),VLOOKUP(B6,Baseline!$A$2:$H$10,5,FALSE)))))</f>
         <v>46186</v>
       </c>
       <c r="N6" s="6">
-        <f>IF(B6="","",IF(K6="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B5=B6),$N$2:N5),VLOOKUP(B6,Baseline!$A$2:$H$10,6,FALSE))+IF(K6="Defence",1,0)))</f>
+        <f>IF(B6="","",IF(K6="INVALID — CHECK RESULT TYPE","",IF(K6="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B5=B6),$N$2:N5),VLOOKUP(B6,Baseline!$A$2:$H$10,6,FALSE))+IF(K6="Defence",1,0))))</f>
         <v>6</v>
       </c>
       <c r="O6" s="6">
-        <f>IF(B6="","",IFERROR(LOOKUP(2,1/($B$2:B5=B6),$O$2:O5),VLOOKUP(B6,Baseline!$A$2:$H$10,7,FALSE))+IF(K6="Transfer",1,0))</f>
+        <f>IF(B6="","",IF(K6="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B5=B6),$O$2:O5),VLOOKUP(B6,Baseline!$A$2:$H$10,7,FALSE))+IF(K6="Transfer",1,0)))</f>
         <v>76</v>
       </c>
       <c r="P6" s="6">
-        <f>IF(B6="","",IFERROR(LOOKUP(2,1/($B$2:B5=B6),$P$2:P5),VLOOKUP(B6,Baseline!$A$2:$H$10,8,FALSE))+IF(K6="Defence",1,0))</f>
+        <f>IF(B6="","",IF(K6="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B5=B6),$P$2:P5),VLOOKUP(B6,Baseline!$A$2:$H$10,8,FALSE))+IF(K6="Defence",1,0)))</f>
         <v>139</v>
       </c>
       <c r="Q6" s="5"/>
@@ -1588,19 +1593,19 @@
         <v>Bayern München</v>
       </c>
       <c r="M7" s="8">
-        <f>IF(B7="","",IF(K7="Transfer",C7,IFERROR(LOOKUP(2,1/($B$2:B6=B7),$M$2:M6),VLOOKUP(B7,Baseline!$A$2:$H$10,5,FALSE))))</f>
+        <f>IF(B7="","",IF(K7="INVALID — CHECK RESULT TYPE","",IF(K7="Transfer",IF(R7&lt;&gt;"",R7,C7),IFERROR(LOOKUP(2,1/($B$2:B6=B7),$M$2:M6),VLOOKUP(B7,Baseline!$A$2:$H$10,5,FALSE)))))</f>
         <v>46081</v>
       </c>
       <c r="N7" s="6">
-        <f>IF(B7="","",IF(K7="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B6=B7),$N$2:N6),VLOOKUP(B7,Baseline!$A$2:$H$10,6,FALSE))+IF(K7="Defence",1,0)))</f>
+        <f>IF(B7="","",IF(K7="INVALID — CHECK RESULT TYPE","",IF(K7="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B6=B7),$N$2:N6),VLOOKUP(B7,Baseline!$A$2:$H$10,6,FALSE))+IF(K7="Defence",1,0))))</f>
         <v>11</v>
       </c>
       <c r="O7" s="6">
-        <f>IF(B7="","",IFERROR(LOOKUP(2,1/($B$2:B6=B7),$O$2:O6),VLOOKUP(B7,Baseline!$A$2:$H$10,7,FALSE))+IF(K7="Transfer",1,0))</f>
+        <f>IF(B7="","",IF(K7="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B6=B7),$O$2:O6),VLOOKUP(B7,Baseline!$A$2:$H$10,7,FALSE))+IF(K7="Transfer",1,0)))</f>
         <v>681</v>
       </c>
       <c r="P7" s="6">
-        <f>IF(B7="","",IFERROR(LOOKUP(2,1/($B$2:B6=B7),$P$2:P6),VLOOKUP(B7,Baseline!$A$2:$H$10,8,FALSE))+IF(K7="Defence",1,0))</f>
+        <f>IF(B7="","",IF(K7="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B6=B7),$P$2:P6),VLOOKUP(B7,Baseline!$A$2:$H$10,8,FALSE))+IF(K7="Defence",1,0)))</f>
         <v>1443</v>
       </c>
       <c r="Q7" s="5"/>
@@ -1640,19 +1645,19 @@
         <v>Bayern München</v>
       </c>
       <c r="M8" s="8">
-        <f>IF(B8="","",IF(K8="Transfer",C8,IFERROR(LOOKUP(2,1/($B$2:B7=B8),$M$2:M7),VLOOKUP(B8,Baseline!$A$2:$H$10,5,FALSE))))</f>
+        <f>IF(B8="","",IF(K8="INVALID — CHECK RESULT TYPE","",IF(K8="Transfer",IF(R8&lt;&gt;"",R8,C8),IFERROR(LOOKUP(2,1/($B$2:B7=B8),$M$2:M7),VLOOKUP(B8,Baseline!$A$2:$H$10,5,FALSE)))))</f>
         <v>45730</v>
       </c>
       <c r="N8" s="6">
-        <f>IF(B8="","",IF(K8="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B7=B8),$N$2:N7),VLOOKUP(B8,Baseline!$A$2:$H$10,6,FALSE))+IF(K8="Defence",1,0)))</f>
+        <f>IF(B8="","",IF(K8="INVALID — CHECK RESULT TYPE","",IF(K8="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B7=B8),$N$2:N7),VLOOKUP(B8,Baseline!$A$2:$H$10,6,FALSE))+IF(K8="Defence",1,0))))</f>
         <v>32</v>
       </c>
       <c r="O8" s="6">
-        <f>IF(B8="","",IFERROR(LOOKUP(2,1/($B$2:B7=B8),$O$2:O7),VLOOKUP(B8,Baseline!$A$2:$H$10,7,FALSE))+IF(K8="Transfer",1,0))</f>
+        <f>IF(B8="","",IF(K8="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B7=B8),$O$2:O7),VLOOKUP(B8,Baseline!$A$2:$H$10,7,FALSE))+IF(K8="Transfer",1,0)))</f>
         <v>113</v>
       </c>
       <c r="P8" s="6">
-        <f>IF(B8="","",IFERROR(LOOKUP(2,1/($B$2:B7=B8),$P$2:P7),VLOOKUP(B8,Baseline!$A$2:$H$10,8,FALSE))+IF(K8="Defence",1,0))</f>
+        <f>IF(B8="","",IF(K8="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B7=B8),$P$2:P7),VLOOKUP(B8,Baseline!$A$2:$H$10,8,FALSE))+IF(K8="Defence",1,0)))</f>
         <v>655</v>
       </c>
       <c r="Q8" s="5"/>
@@ -1692,19 +1697,19 @@
         <v>Bayern München</v>
       </c>
       <c r="M9" s="8">
-        <f>IF(B9="","",IF(K9="Transfer",C9,IFERROR(LOOKUP(2,1/($B$2:B8=B9),$M$2:M8),VLOOKUP(B9,Baseline!$A$2:$H$10,5,FALSE))))</f>
+        <f>IF(B9="","",IF(K9="INVALID — CHECK RESULT TYPE","",IF(K9="Transfer",IF(R9&lt;&gt;"",R9,C9),IFERROR(LOOKUP(2,1/($B$2:B8=B9),$M$2:M8),VLOOKUP(B9,Baseline!$A$2:$H$10,5,FALSE)))))</f>
         <v>46081</v>
       </c>
       <c r="N9" s="6">
-        <f>IF(B9="","",IF(K9="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B8=B9),$N$2:N8),VLOOKUP(B9,Baseline!$A$2:$H$10,6,FALSE))+IF(K9="Defence",1,0)))</f>
+        <f>IF(B9="","",IF(K9="INVALID — CHECK RESULT TYPE","",IF(K9="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B8=B9),$N$2:N8),VLOOKUP(B9,Baseline!$A$2:$H$10,6,FALSE))+IF(K9="Defence",1,0))))</f>
         <v>11</v>
       </c>
       <c r="O9" s="6">
-        <f>IF(B9="","",IFERROR(LOOKUP(2,1/($B$2:B8=B9),$O$2:O8),VLOOKUP(B9,Baseline!$A$2:$H$10,7,FALSE))+IF(K9="Transfer",1,0))</f>
+        <f>IF(B9="","",IF(K9="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B8=B9),$O$2:O8),VLOOKUP(B9,Baseline!$A$2:$H$10,7,FALSE))+IF(K9="Transfer",1,0)))</f>
         <v>681</v>
       </c>
       <c r="P9" s="6">
-        <f>IF(B9="","",IFERROR(LOOKUP(2,1/($B$2:B8=B9),$P$2:P8),VLOOKUP(B9,Baseline!$A$2:$H$10,8,FALSE))+IF(K9="Defence",1,0))</f>
+        <f>IF(B9="","",IF(K9="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B8=B9),$P$2:P8),VLOOKUP(B9,Baseline!$A$2:$H$10,8,FALSE))+IF(K9="Defence",1,0)))</f>
         <v>1443</v>
       </c>
       <c r="Q9" s="5"/>
@@ -5715,7 +5720,30 @@
       <c r="R100" s="12"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="K2:K100">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>K2="INVALID — CHECK RESULT TYPE"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0300-000000000000}">
+          <x14:formula1>
+            <xm:f>Lists!$D$2:$D$6</xm:f>
+          </x14:formula1>
+          <xm:sqref>F2:F100</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0300-000001000000}">
+          <x14:formula1>
+            <xm:f>Lists!$E$2:$E$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2:G100</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -5760,31 +5788,31 @@
       </c>
       <c r="B2" t="str">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A2),Updates!$L$2:$L$100),VLOOKUP(A2,Baseline!$A$2:$H$10,4,FALSE))</f>
-        <v>Australia</v>
+        <v>South Africa</v>
       </c>
       <c r="C2" s="4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A2),Updates!$M$2:$M$100),VLOOKUP(A2,Baseline!$A$2:$H$10,5,FALSE))</f>
-        <v>46304</v>
+        <v>45953</v>
       </c>
       <c r="D2">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A2),Updates!$N$2:$N$100),VLOOKUP(A2,Baseline!$A$2:$H$10,6,FALSE))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A2),Updates!$O$2:$O$100),VLOOKUP(A2,Baseline!$A$2:$H$10,7,FALSE))</f>
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F2">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A2),Updates!$P$2:$P$100),VLOOKUP(A2,Baseline!$A$2:$H$10,8,FALSE))</f>
         <v>270</v>
       </c>
-      <c r="G2" s="4" t="str">
+      <c r="G2" s="4">
         <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A2)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
-        <v>TBD</v>
+        <v>46304</v>
       </c>
       <c r="H2" t="str">
         <f>IF(G2="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A2)*(Updates!$C$2:$C$100=G2)),Updates!$D$2:$D$100),"TBD"))</f>
-        <v>TBD</v>
+        <v>Australia</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -6098,31 +6126,31 @@
       </c>
       <c r="B2" t="str">
         <f>Dashboard!B2</f>
-        <v>Australia</v>
+        <v>South Africa</v>
       </c>
       <c r="C2" s="9">
         <f>Dashboard!C2</f>
-        <v>46304</v>
+        <v>45953</v>
       </c>
       <c r="D2">
         <f>Dashboard!D2</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <f>Dashboard!E2</f>
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F2">
         <f>Dashboard!F2</f>
         <v>270</v>
       </c>
-      <c r="G2" s="9" t="str">
+      <c r="G2" s="9">
         <f>Dashboard!G2</f>
-        <v>TBD</v>
+        <v>46304</v>
       </c>
       <c r="H2" t="str">
         <f>Dashboard!H2</f>
-        <v>TBD</v>
+        <v>Australia</v>
       </c>
     </row>
     <row r="3" spans="1:8">

--- a/LSC_Update_System.xlsx
+++ b/LSC_Update_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CH\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_023717A8391A607FB11835ABBFFFF4DEB130EFC4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A44AD042-D3DC-4463-88FD-4FC9FFBBE275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="119">
   <si>
     <t>LSC UPDATE SYSTEM — SAFE TEST</t>
   </si>
@@ -390,6 +390,9 @@
   </si>
   <si>
     <t>Fixture End Date (optional)</t>
+  </si>
+  <si>
+    <t>Australia beat England by 5 wickets</t>
   </si>
 </sst>
 </file>
@@ -1353,10 +1356,14 @@
         <v>90</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="10"/>
+        <v>63</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H3" t="s">
+        <v>118</v>
+      </c>
       <c r="I3" s="5"/>
       <c r="J3" s="6" t="str">
         <f>IF(B3="","",IFERROR(LOOKUP(2,1/($B$2:B2=B3),$L$2:L2),VLOOKUP(B3,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -1364,7 +1371,7 @@
       </c>
       <c r="K3" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>Scheduled</v>
+        <v>Defence</v>
       </c>
       <c r="L3" s="6" t="str">
         <f t="shared" si="1"/>
@@ -1376,7 +1383,7 @@
       </c>
       <c r="N3" s="6">
         <f>IF(B3="","",IF(K3="INVALID — CHECK RESULT TYPE","",IF(K3="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B2=B3),$N$2:N2),VLOOKUP(B3,Baseline!$A$2:$H$10,6,FALSE))+IF(K3="Defence",1,0))))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" s="6">
         <f>IF(B3="","",IF(K3="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B2=B3),$O$2:O2),VLOOKUP(B3,Baseline!$A$2:$H$10,7,FALSE))+IF(K3="Transfer",1,0)))</f>
@@ -1384,7 +1391,7 @@
       </c>
       <c r="P3" s="6">
         <f>IF(B3="","",IF(K3="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B2=B3),$P$2:P2),VLOOKUP(B3,Baseline!$A$2:$H$10,8,FALSE))+IF(K3="Defence",1,0)))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>91</v>
@@ -5829,7 +5836,7 @@
       </c>
       <c r="D3">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A3),Updates!$N$2:$N$100),VLOOKUP(A3,Baseline!$A$2:$H$10,6,FALSE))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A3),Updates!$O$2:$O$100),VLOOKUP(A3,Baseline!$A$2:$H$10,7,FALSE))</f>
@@ -5837,15 +5844,15 @@
       </c>
       <c r="F3">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A3),Updates!$P$2:$P$100),VLOOKUP(A3,Baseline!$A$2:$H$10,8,FALSE))</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="4">
+        <v>5</v>
+      </c>
+      <c r="G3" s="4" t="str">
         <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A3)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
-        <v>46562</v>
+        <v>TBD</v>
       </c>
       <c r="H3" t="str">
         <f>IF(G3="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A3)*(Updates!$C$2:$C$100=G3)),Updates!$D$2:$D$100),"TBD"))</f>
-        <v>England</v>
+        <v>TBD</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -6168,7 +6175,7 @@
       </c>
       <c r="D3">
         <f>Dashboard!D3</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <f>Dashboard!E3</f>
@@ -6176,15 +6183,15 @@
       </c>
       <c r="F3">
         <f>Dashboard!F3</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="9">
+        <v>5</v>
+      </c>
+      <c r="G3" s="9" t="str">
         <f>Dashboard!G3</f>
-        <v>46562</v>
+        <v>TBD</v>
       </c>
       <c r="H3" t="str">
         <f>Dashboard!H3</f>
-        <v>England</v>
+        <v>TBD</v>
       </c>
     </row>
     <row r="4" spans="1:8">

--- a/LSC_Update_System.xlsx
+++ b/LSC_Update_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CH\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A44AD042-D3DC-4463-88FD-4FC9FFBBE275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07262448-1744-4058-B038-E73270C6D1D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -392,7 +392,7 @@
     <t>Fixture End Date (optional)</t>
   </si>
   <si>
-    <t>Australia beat England by 5 wickets</t>
+    <t>England beat Australia by 5 wickets</t>
   </si>
 </sst>
 </file>
@@ -1359,7 +1359,7 @@
         <v>63</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H3" t="s">
         <v>118</v>
@@ -1371,27 +1371,27 @@
       </c>
       <c r="K3" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>Defence</v>
+        <v>Transfer</v>
       </c>
       <c r="L3" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>Australia</v>
+        <v>England</v>
       </c>
       <c r="M3" s="8">
         <f>IF(B3="","",IF(K3="INVALID — CHECK RESULT TYPE","",IF(K3="Transfer",IF(R3&lt;&gt;"",R3,C3),IFERROR(LOOKUP(2,1/($B$2:B2=B3),$M$2:M2),VLOOKUP(B3,Baseline!$A$2:$H$10,5,FALSE)))))</f>
-        <v>46089</v>
+        <v>46565</v>
       </c>
       <c r="N3" s="6">
         <f>IF(B3="","",IF(K3="INVALID — CHECK RESULT TYPE","",IF(K3="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B2=B3),$N$2:N2),VLOOKUP(B3,Baseline!$A$2:$H$10,6,FALSE))+IF(K3="Defence",1,0))))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" s="6">
         <f>IF(B3="","",IF(K3="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B2=B3),$O$2:O2),VLOOKUP(B3,Baseline!$A$2:$H$10,7,FALSE))+IF(K3="Transfer",1,0)))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P3" s="6">
         <f>IF(B3="","",IF(K3="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B2=B3),$P$2:P2),VLOOKUP(B3,Baseline!$A$2:$H$10,8,FALSE))+IF(K3="Defence",1,0)))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>91</v>
@@ -5828,23 +5828,23 @@
       </c>
       <c r="B3" t="str">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A3),Updates!$L$2:$L$100),VLOOKUP(A3,Baseline!$A$2:$H$10,4,FALSE))</f>
-        <v>Australia</v>
+        <v>England</v>
       </c>
       <c r="C3" s="4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A3),Updates!$M$2:$M$100),VLOOKUP(A3,Baseline!$A$2:$H$10,5,FALSE))</f>
-        <v>46089</v>
+        <v>46565</v>
       </c>
       <c r="D3">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A3),Updates!$N$2:$N$100),VLOOKUP(A3,Baseline!$A$2:$H$10,6,FALSE))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A3),Updates!$O$2:$O$100),VLOOKUP(A3,Baseline!$A$2:$H$10,7,FALSE))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A3),Updates!$P$2:$P$100),VLOOKUP(A3,Baseline!$A$2:$H$10,8,FALSE))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G3" s="4" t="str">
         <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A3)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
@@ -6167,23 +6167,23 @@
       </c>
       <c r="B3" t="str">
         <f>Dashboard!B3</f>
-        <v>Australia</v>
+        <v>England</v>
       </c>
       <c r="C3" s="9">
         <f>Dashboard!C3</f>
-        <v>46089</v>
+        <v>46565</v>
       </c>
       <c r="D3">
         <f>Dashboard!D3</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <f>Dashboard!E3</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3">
         <f>Dashboard!F3</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G3" s="9" t="str">
         <f>Dashboard!G3</f>

--- a/LSC_Update_System.xlsx
+++ b/LSC_Update_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CH\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07262448-1744-4058-B038-E73270C6D1D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CBC5CA0-96C1-4FD7-AC43-13DDACDDC899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1359,7 +1359,7 @@
         <v>63</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H3" t="s">
         <v>118</v>
@@ -1371,27 +1371,27 @@
       </c>
       <c r="K3" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>Transfer</v>
+        <v>Defence</v>
       </c>
       <c r="L3" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>England</v>
+        <v>Australia</v>
       </c>
       <c r="M3" s="8">
         <f>IF(B3="","",IF(K3="INVALID — CHECK RESULT TYPE","",IF(K3="Transfer",IF(R3&lt;&gt;"",R3,C3),IFERROR(LOOKUP(2,1/($B$2:B2=B3),$M$2:M2),VLOOKUP(B3,Baseline!$A$2:$H$10,5,FALSE)))))</f>
-        <v>46565</v>
+        <v>46089</v>
       </c>
       <c r="N3" s="6">
         <f>IF(B3="","",IF(K3="INVALID — CHECK RESULT TYPE","",IF(K3="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B2=B3),$N$2:N2),VLOOKUP(B3,Baseline!$A$2:$H$10,6,FALSE))+IF(K3="Defence",1,0))))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" s="6">
         <f>IF(B3="","",IF(K3="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B2=B3),$O$2:O2),VLOOKUP(B3,Baseline!$A$2:$H$10,7,FALSE))+IF(K3="Transfer",1,0)))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P3" s="6">
         <f>IF(B3="","",IF(K3="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B2=B3),$P$2:P2),VLOOKUP(B3,Baseline!$A$2:$H$10,8,FALSE))+IF(K3="Defence",1,0)))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>91</v>
@@ -5828,23 +5828,23 @@
       </c>
       <c r="B3" t="str">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A3),Updates!$L$2:$L$100),VLOOKUP(A3,Baseline!$A$2:$H$10,4,FALSE))</f>
-        <v>England</v>
+        <v>Australia</v>
       </c>
       <c r="C3" s="4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A3),Updates!$M$2:$M$100),VLOOKUP(A3,Baseline!$A$2:$H$10,5,FALSE))</f>
-        <v>46565</v>
+        <v>46089</v>
       </c>
       <c r="D3">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A3),Updates!$N$2:$N$100),VLOOKUP(A3,Baseline!$A$2:$H$10,6,FALSE))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A3),Updates!$O$2:$O$100),VLOOKUP(A3,Baseline!$A$2:$H$10,7,FALSE))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A3),Updates!$P$2:$P$100),VLOOKUP(A3,Baseline!$A$2:$H$10,8,FALSE))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3" s="4" t="str">
         <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A3)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
@@ -6167,23 +6167,23 @@
       </c>
       <c r="B3" t="str">
         <f>Dashboard!B3</f>
-        <v>England</v>
+        <v>Australia</v>
       </c>
       <c r="C3" s="9">
         <f>Dashboard!C3</f>
-        <v>46565</v>
+        <v>46089</v>
       </c>
       <c r="D3">
         <f>Dashboard!D3</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <f>Dashboard!E3</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <f>Dashboard!F3</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3" s="9" t="str">
         <f>Dashboard!G3</f>

--- a/LSC_Update_System.xlsx
+++ b/LSC_Update_System.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CH\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CBC5CA0-96C1-4FD7-AC43-13DDACDDC899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24873BCB-2EB7-4561-BE17-C6D4F788A903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="START HERE" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="121">
   <si>
     <t>LSC UPDATE SYSTEM — SAFE TEST</t>
   </si>
@@ -393,6 +393,12 @@
   </si>
   <si>
     <t>England beat Australia by 5 wickets</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>England beat India by 4 wickets</t>
   </si>
 </sst>
 </file>
@@ -1359,7 +1365,7 @@
         <v>63</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H3" t="s">
         <v>118</v>
@@ -1371,27 +1377,27 @@
       </c>
       <c r="K3" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>Defence</v>
+        <v>Transfer</v>
       </c>
       <c r="L3" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>Australia</v>
+        <v>England</v>
       </c>
       <c r="M3" s="8">
         <f>IF(B3="","",IF(K3="INVALID — CHECK RESULT TYPE","",IF(K3="Transfer",IF(R3&lt;&gt;"",R3,C3),IFERROR(LOOKUP(2,1/($B$2:B2=B3),$M$2:M2),VLOOKUP(B3,Baseline!$A$2:$H$10,5,FALSE)))))</f>
-        <v>46089</v>
+        <v>46565</v>
       </c>
       <c r="N3" s="6">
         <f>IF(B3="","",IF(K3="INVALID — CHECK RESULT TYPE","",IF(K3="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B2=B3),$N$2:N2),VLOOKUP(B3,Baseline!$A$2:$H$10,6,FALSE))+IF(K3="Defence",1,0))))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" s="6">
         <f>IF(B3="","",IF(K3="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B2=B3),$O$2:O2),VLOOKUP(B3,Baseline!$A$2:$H$10,7,FALSE))+IF(K3="Transfer",1,0)))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P3" s="6">
         <f>IF(B3="","",IF(K3="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B2=B3),$P$2:P2),VLOOKUP(B3,Baseline!$A$2:$H$10,8,FALSE))+IF(K3="Defence",1,0)))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>91</v>
@@ -1725,46 +1731,60 @@
     <row r="10" spans="1:18">
       <c r="A10" s="6" t="str">
         <f>IF(OR(B10="",C10=""),"",VLOOKUP(B10,Lists!$A$2:$B$10,2,FALSE)&amp;"-"&amp;TEXT(C10,"yyyymmdd")&amp;"-"&amp;TEXT(COUNTIFS($B$2:B10,B10,$C$2:C10,C10),"00"))</f>
-        <v/>
-      </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="5"/>
+        <v>MMM-20270630-01</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="7">
+        <v>46568</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>119</v>
+      </c>
       <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="10"/>
+      <c r="F10" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>120</v>
+      </c>
       <c r="I10" s="5"/>
       <c r="J10" s="6" t="str">
         <f>IF(B10="","",IFERROR(LOOKUP(2,1/($B$2:B9=B10),$L$2:L9),VLOOKUP(B10,Baseline!$A$2:$H$10,4,FALSE)))</f>
-        <v/>
+        <v>England</v>
       </c>
       <c r="K10" s="6" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Defence</v>
       </c>
       <c r="L10" s="6" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M10" s="8" t="str">
+        <v>England</v>
+      </c>
+      <c r="M10" s="8">
         <f>IF(B10="","",IF(K10="Transfer",C10,IFERROR(LOOKUP(2,1/($B$2:B9=B10),$M$2:M9),VLOOKUP(B10,Baseline!$A$2:$H$10,5,FALSE))))</f>
-        <v/>
-      </c>
-      <c r="N10" s="6" t="str">
+        <v>46565</v>
+      </c>
+      <c r="N10" s="6">
         <f>IF(B10="","",IF(K10="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B9=B10),$N$2:N9),VLOOKUP(B10,Baseline!$A$2:$H$10,6,FALSE))+IF(K10="Defence",1,0)))</f>
-        <v/>
-      </c>
-      <c r="O10" s="6" t="str">
+        <v>1</v>
+      </c>
+      <c r="O10" s="6">
         <f>IF(B10="","",IFERROR(LOOKUP(2,1/($B$2:B9=B10),$O$2:O9),VLOOKUP(B10,Baseline!$A$2:$H$10,7,FALSE))+IF(K10="Transfer",1,0))</f>
-        <v/>
-      </c>
-      <c r="P10" s="6" t="str">
+        <v>9</v>
+      </c>
+      <c r="P10" s="6">
         <f>IF(B10="","",IFERROR(LOOKUP(2,1/($B$2:B9=B10),$P$2:P9),VLOOKUP(B10,Baseline!$A$2:$H$10,8,FALSE))+IF(K10="Defence",1,0))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="Q10" s="5"/>
-      <c r="R10" s="12"/>
+      <c r="R10" s="12">
+        <v>46571</v>
+      </c>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="6" t="str">
@@ -5828,11 +5848,11 @@
       </c>
       <c r="B3" t="str">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A3),Updates!$L$2:$L$100),VLOOKUP(A3,Baseline!$A$2:$H$10,4,FALSE))</f>
-        <v>Australia</v>
+        <v>England</v>
       </c>
       <c r="C3" s="4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A3),Updates!$M$2:$M$100),VLOOKUP(A3,Baseline!$A$2:$H$10,5,FALSE))</f>
-        <v>46089</v>
+        <v>46565</v>
       </c>
       <c r="D3">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A3),Updates!$N$2:$N$100),VLOOKUP(A3,Baseline!$A$2:$H$10,6,FALSE))</f>
@@ -5840,7 +5860,7 @@
       </c>
       <c r="E3">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A3),Updates!$O$2:$O$100),VLOOKUP(A3,Baseline!$A$2:$H$10,7,FALSE))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A3),Updates!$P$2:$P$100),VLOOKUP(A3,Baseline!$A$2:$H$10,8,FALSE))</f>
@@ -6167,11 +6187,11 @@
       </c>
       <c r="B3" t="str">
         <f>Dashboard!B3</f>
-        <v>Australia</v>
+        <v>England</v>
       </c>
       <c r="C3" s="9">
         <f>Dashboard!C3</f>
-        <v>46089</v>
+        <v>46565</v>
       </c>
       <c r="D3">
         <f>Dashboard!D3</f>
@@ -6179,7 +6199,7 @@
       </c>
       <c r="E3">
         <f>Dashboard!E3</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3">
         <f>Dashboard!F3</f>

--- a/LSC_Update_System.xlsx
+++ b/LSC_Update_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CH\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24873BCB-2EB7-4561-BE17-C6D4F788A903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AADD10E5-E803-4275-976C-0D18458EC925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="117">
   <si>
     <t>LSC UPDATE SYSTEM — SAFE TEST</t>
   </si>
@@ -305,12 +305,6 @@
     <t>Kingsmead · Durban</t>
   </si>
   <si>
-    <t>England</t>
-  </si>
-  <si>
-    <t>Headingley · Leeds</t>
-  </si>
-  <si>
     <t>24–27 June 2027</t>
   </si>
   <si>
@@ -392,13 +386,7 @@
     <t>Fixture End Date (optional)</t>
   </si>
   <si>
-    <t>England beat Australia by 5 wickets</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>England beat India by 4 wickets</t>
+    <t>Senwes Park, Potchesfstroom</t>
   </si>
 </sst>
 </file>
@@ -797,13 +785,13 @@
     </row>
     <row r="9" spans="1:3" ht="42.75">
       <c r="A9" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -1211,7 +1199,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:R100"/>
+  <dimension ref="A1:R99"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1285,7 +1273,7 @@
         <v>87</v>
       </c>
       <c r="R1" s="13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -1316,11 +1304,11 @@
         <v>South Africa</v>
       </c>
       <c r="K2" s="6" t="str">
-        <f t="shared" ref="K2:K33" si="0">IF(B2="","",IF(F2&lt;&gt;"Completed",F2,IF(G2="Challenger win","Transfer",IF(OR(G2="Holder win",G2="Draw / tie"),"Defence",IF(G2="No result","No result","INVALID — CHECK RESULT TYPE")))))</f>
+        <f t="shared" ref="K2:K32" si="0">IF(B2="","",IF(F2&lt;&gt;"Completed",F2,IF(G2="Challenger win","Transfer",IF(OR(G2="Holder win",G2="Draw / tie"),"Defence",IF(G2="No result","No result","INVALID — CHECK RESULT TYPE")))))</f>
         <v>Scheduled</v>
       </c>
       <c r="L2" s="6" t="str">
-        <f t="shared" ref="L2:L33" si="1">IF(B2="","",IF(K2="INVALID — CHECK RESULT TYPE","",IF(K2="Transfer",D2,J2)))</f>
+        <f t="shared" ref="L2:L32" si="1">IF(B2="","",IF(K2="INVALID — CHECK RESULT TYPE","",IF(K2="Transfer",D2,J2)))</f>
         <v>South Africa</v>
       </c>
       <c r="M2" s="8">
@@ -1347,29 +1335,24 @@
     <row r="3" spans="1:18">
       <c r="A3" s="6" t="str">
         <f>IF(OR(B3="",C3=""),"",VLOOKUP(B3,Lists!$A$2:$B$10,2,FALSE)&amp;"-"&amp;TEXT(C3,"yyyymmdd")&amp;"-"&amp;TEXT(COUNTIFS($B$2:B3,B3,$C$2:C3,C3),"00"))</f>
-        <v>MMM-20270624-01</v>
+        <v>MMM-20270408-01</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>32</v>
       </c>
       <c r="C3" s="7">
-        <v>46562</v>
+        <v>46485</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>89</v>
+        <v>31</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H3" t="s">
-        <v>118</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="G3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="6" t="str">
         <f>IF(B3="","",IFERROR(LOOKUP(2,1/($B$2:B2=B3),$L$2:L2),VLOOKUP(B3,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -1377,15 +1360,15 @@
       </c>
       <c r="K3" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>Transfer</v>
+        <v>Scheduled</v>
       </c>
       <c r="L3" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>England</v>
+        <v>Australia</v>
       </c>
       <c r="M3" s="8">
         <f>IF(B3="","",IF(K3="INVALID — CHECK RESULT TYPE","",IF(K3="Transfer",IF(R3&lt;&gt;"",R3,C3),IFERROR(LOOKUP(2,1/($B$2:B2=B3),$M$2:M2),VLOOKUP(B3,Baseline!$A$2:$H$10,5,FALSE)))))</f>
-        <v>46565</v>
+        <v>46089</v>
       </c>
       <c r="N3" s="6">
         <f>IF(B3="","",IF(K3="INVALID — CHECK RESULT TYPE","",IF(K3="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B2=B3),$N$2:N2),VLOOKUP(B3,Baseline!$A$2:$H$10,6,FALSE))+IF(K3="Defence",1,0))))</f>
@@ -1393,17 +1376,17 @@
       </c>
       <c r="O3" s="6">
         <f>IF(B3="","",IF(K3="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B2=B3),$O$2:O2),VLOOKUP(B3,Baseline!$A$2:$H$10,7,FALSE))+IF(K3="Transfer",1,0)))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P3" s="6">
         <f>IF(B3="","",IF(K3="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B2=B3),$P$2:P2),VLOOKUP(B3,Baseline!$A$2:$H$10,8,FALSE))+IF(K3="Defence",1,0)))</f>
         <v>4</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="R3" s="12">
-        <v>46565</v>
+        <v>46488</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1418,10 +1401,10 @@
         <v>46280</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>57</v>
@@ -1472,10 +1455,10 @@
         <v>46304</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>57</v>
@@ -1526,10 +1509,10 @@
         <v>46313</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>57</v>
@@ -1580,7 +1563,7 @@
         <v>46262</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5" t="s">
@@ -1590,7 +1573,7 @@
         <v>58</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I7" s="5"/>
       <c r="J7" s="6" t="str">
@@ -1636,7 +1619,7 @@
         <v>46265</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5" t="s">
@@ -1688,7 +1671,7 @@
         <v>46269</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5" t="s">
@@ -1731,60 +1714,46 @@
     <row r="10" spans="1:18">
       <c r="A10" s="6" t="str">
         <f>IF(OR(B10="",C10=""),"",VLOOKUP(B10,Lists!$A$2:$B$10,2,FALSE)&amp;"-"&amp;TEXT(C10,"yyyymmdd")&amp;"-"&amp;TEXT(COUNTIFS($B$2:B10,B10,$C$2:C10,C10),"00"))</f>
-        <v>MMM-20270630-01</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="7">
-        <v>46568</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>119</v>
-      </c>
+        <v/>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="5"/>
       <c r="E10" s="5"/>
-      <c r="F10" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>120</v>
-      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="10"/>
       <c r="I10" s="5"/>
       <c r="J10" s="6" t="str">
         <f>IF(B10="","",IFERROR(LOOKUP(2,1/($B$2:B9=B10),$L$2:L9),VLOOKUP(B10,Baseline!$A$2:$H$10,4,FALSE)))</f>
-        <v>England</v>
+        <v/>
       </c>
       <c r="K10" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>Defence</v>
+        <v/>
       </c>
       <c r="L10" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>England</v>
-      </c>
-      <c r="M10" s="8">
+        <v/>
+      </c>
+      <c r="M10" s="8" t="str">
         <f>IF(B10="","",IF(K10="Transfer",C10,IFERROR(LOOKUP(2,1/($B$2:B9=B10),$M$2:M9),VLOOKUP(B10,Baseline!$A$2:$H$10,5,FALSE))))</f>
-        <v>46565</v>
-      </c>
-      <c r="N10" s="6">
+        <v/>
+      </c>
+      <c r="N10" s="6" t="str">
         <f>IF(B10="","",IF(K10="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B9=B10),$N$2:N9),VLOOKUP(B10,Baseline!$A$2:$H$10,6,FALSE))+IF(K10="Defence",1,0)))</f>
-        <v>1</v>
-      </c>
-      <c r="O10" s="6">
+        <v/>
+      </c>
+      <c r="O10" s="6" t="str">
         <f>IF(B10="","",IFERROR(LOOKUP(2,1/($B$2:B9=B10),$O$2:O9),VLOOKUP(B10,Baseline!$A$2:$H$10,7,FALSE))+IF(K10="Transfer",1,0))</f>
-        <v>9</v>
-      </c>
-      <c r="P10" s="6">
+        <v/>
+      </c>
+      <c r="P10" s="6" t="str">
         <f>IF(B10="","",IFERROR(LOOKUP(2,1/($B$2:B9=B10),$P$2:P9),VLOOKUP(B10,Baseline!$A$2:$H$10,8,FALSE))+IF(K10="Defence",1,0))</f>
-        <v>5</v>
+        <v/>
       </c>
       <c r="Q10" s="5"/>
-      <c r="R10" s="12">
-        <v>46571</v>
-      </c>
+      <c r="R10" s="12"/>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="6" t="str">
@@ -2772,11 +2741,11 @@
         <v/>
       </c>
       <c r="K33" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="K33:K64" si="2">IF(B33="","",IF(F33&lt;&gt;"Completed",F33,IF(G33="Challenger win","Transfer",IF(OR(G33="Holder win",G33="Draw / tie"),"Defence",IF(G33="No result","No result","REVIEW")))))</f>
         <v/>
       </c>
       <c r="L33" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="L33:L64" si="3">IF(B33="","",IF(K33="Transfer",D33,J33))</f>
         <v/>
       </c>
       <c r="M33" s="8" t="str">
@@ -2816,11 +2785,11 @@
         <v/>
       </c>
       <c r="K34" s="6" t="str">
-        <f t="shared" ref="K34:K65" si="2">IF(B34="","",IF(F34&lt;&gt;"Completed",F34,IF(G34="Challenger win","Transfer",IF(OR(G34="Holder win",G34="Draw / tie"),"Defence",IF(G34="No result","No result","REVIEW")))))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L34" s="6" t="str">
-        <f t="shared" ref="L34:L65" si="3">IF(B34="","",IF(K34="Transfer",D34,J34))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M34" s="8" t="str">
@@ -4180,11 +4149,11 @@
         <v/>
       </c>
       <c r="K65" s="6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="K65:K99" si="4">IF(B65="","",IF(F65&lt;&gt;"Completed",F65,IF(G65="Challenger win","Transfer",IF(OR(G65="Holder win",G65="Draw / tie"),"Defence",IF(G65="No result","No result","REVIEW")))))</f>
         <v/>
       </c>
       <c r="L65" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="L65:L96" si="5">IF(B65="","",IF(K65="Transfer",D65,J65))</f>
         <v/>
       </c>
       <c r="M65" s="8" t="str">
@@ -4224,11 +4193,11 @@
         <v/>
       </c>
       <c r="K66" s="6" t="str">
-        <f t="shared" ref="K66:K100" si="4">IF(B66="","",IF(F66&lt;&gt;"Completed",F66,IF(G66="Challenger win","Transfer",IF(OR(G66="Holder win",G66="Draw / tie"),"Defence",IF(G66="No result","No result","REVIEW")))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L66" s="6" t="str">
-        <f t="shared" ref="L66:L97" si="5">IF(B66="","",IF(K66="Transfer",D66,J66))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="M66" s="8" t="str">
@@ -5592,7 +5561,7 @@
         <v/>
       </c>
       <c r="L97" s="6" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="L97:L99" si="6">IF(B97="","",IF(K97="Transfer",D97,J97))</f>
         <v/>
       </c>
       <c r="M97" s="8" t="str">
@@ -5636,7 +5605,7 @@
         <v/>
       </c>
       <c r="L98" s="6" t="str">
-        <f t="shared" ref="L98:L100" si="6">IF(B98="","",IF(K98="Transfer",D98,J98))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="M98" s="8" t="str">
@@ -5702,52 +5671,8 @@
       <c r="Q99" s="5"/>
       <c r="R99" s="12"/>
     </row>
-    <row r="100" spans="1:18">
-      <c r="A100" s="6" t="str">
-        <f>IF(OR(B100="",C100=""),"",VLOOKUP(B100,Lists!$A$2:$B$10,2,FALSE)&amp;"-"&amp;TEXT(C100,"yyyymmdd")&amp;"-"&amp;TEXT(COUNTIFS($B$2:B100,B100,$C$2:C100,C100),"00"))</f>
-        <v/>
-      </c>
-      <c r="B100" s="5"/>
-      <c r="C100" s="7"/>
-      <c r="D100" s="5"/>
-      <c r="E100" s="5"/>
-      <c r="F100" s="5"/>
-      <c r="G100" s="5"/>
-      <c r="H100" s="10"/>
-      <c r="I100" s="5"/>
-      <c r="J100" s="6" t="str">
-        <f>IF(B100="","",IFERROR(LOOKUP(2,1/($B$2:B99=B100),$L$2:L99),VLOOKUP(B100,Baseline!$A$2:$H$10,4,FALSE)))</f>
-        <v/>
-      </c>
-      <c r="K100" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L100" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="M100" s="8" t="str">
-        <f>IF(B100="","",IF(K100="Transfer",C100,IFERROR(LOOKUP(2,1/($B$2:B99=B100),$M$2:M99),VLOOKUP(B100,Baseline!$A$2:$H$10,5,FALSE))))</f>
-        <v/>
-      </c>
-      <c r="N100" s="6" t="str">
-        <f>IF(B100="","",IF(K100="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B99=B100),$N$2:N99),VLOOKUP(B100,Baseline!$A$2:$H$10,6,FALSE))+IF(K100="Defence",1,0)))</f>
-        <v/>
-      </c>
-      <c r="O100" s="6" t="str">
-        <f>IF(B100="","",IFERROR(LOOKUP(2,1/($B$2:B99=B100),$O$2:O99),VLOOKUP(B100,Baseline!$A$2:$H$10,7,FALSE))+IF(K100="Transfer",1,0))</f>
-        <v/>
-      </c>
-      <c r="P100" s="6" t="str">
-        <f>IF(B100="","",IFERROR(LOOKUP(2,1/($B$2:B99=B100),$P$2:P99),VLOOKUP(B100,Baseline!$A$2:$H$10,8,FALSE))+IF(K100="Defence",1,0))</f>
-        <v/>
-      </c>
-      <c r="Q100" s="5"/>
-      <c r="R100" s="12"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="K2:K100">
+  <conditionalFormatting sqref="K2:K99">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>K2="INVALID — CHECK RESULT TYPE"</formula>
     </cfRule>
@@ -5760,13 +5685,13 @@
           <x14:formula1>
             <xm:f>Lists!$D$2:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F100</xm:sqref>
+          <xm:sqref>F2:F99</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0300-000001000000}">
           <x14:formula1>
             <xm:f>Lists!$E$2:$E$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G100</xm:sqref>
+          <xm:sqref>G2:G99</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5788,10 +5713,10 @@
         <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>25</v>
@@ -5803,10 +5728,10 @@
         <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5814,31 +5739,31 @@
         <v>28</v>
       </c>
       <c r="B2" t="str">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A2),Updates!$L$2:$L$100),VLOOKUP(A2,Baseline!$A$2:$H$10,4,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A2),Updates!$L$2:$L$99),VLOOKUP(A2,Baseline!$A$2:$H$10,4,FALSE))</f>
         <v>South Africa</v>
       </c>
       <c r="C2" s="4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A2),Updates!$M$2:$M$100),VLOOKUP(A2,Baseline!$A$2:$H$10,5,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A2),Updates!$M$2:$M$99),VLOOKUP(A2,Baseline!$A$2:$H$10,5,FALSE))</f>
         <v>45953</v>
       </c>
       <c r="D2">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A2),Updates!$N$2:$N$100),VLOOKUP(A2,Baseline!$A$2:$H$10,6,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A2),Updates!$N$2:$N$99),VLOOKUP(A2,Baseline!$A$2:$H$10,6,FALSE))</f>
         <v>2</v>
       </c>
       <c r="E2">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A2),Updates!$O$2:$O$100),VLOOKUP(A2,Baseline!$A$2:$H$10,7,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A2),Updates!$O$2:$O$99),VLOOKUP(A2,Baseline!$A$2:$H$10,7,FALSE))</f>
         <v>172</v>
       </c>
       <c r="F2">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A2),Updates!$P$2:$P$100),VLOOKUP(A2,Baseline!$A$2:$H$10,8,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A2),Updates!$P$2:$P$99),VLOOKUP(A2,Baseline!$A$2:$H$10,8,FALSE))</f>
         <v>270</v>
       </c>
       <c r="G2" s="4">
-        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A2)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
+        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A2)*(Updates!$F$2:$F$99&lt;&gt;"Completed")*(Updates!$F$2:$F$99&lt;&gt;"Cancelled")*(Updates!$F$2:$F$99&lt;&gt;"Postponed")),Updates!$C$2:$C$99),"TBD")</f>
         <v>46304</v>
       </c>
       <c r="H2" t="str">
-        <f>IF(G2="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A2)*(Updates!$C$2:$C$100=G2)),Updates!$D$2:$D$100),"TBD"))</f>
+        <f>IF(G2="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A2)*(Updates!$C$2:$C$99=G2)),Updates!$D$2:$D$99),"TBD"))</f>
         <v>Australia</v>
       </c>
     </row>
@@ -5847,32 +5772,32 @@
         <v>32</v>
       </c>
       <c r="B3" t="str">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A3),Updates!$L$2:$L$100),VLOOKUP(A3,Baseline!$A$2:$H$10,4,FALSE))</f>
-        <v>England</v>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A3),Updates!$L$2:$L$99),VLOOKUP(A3,Baseline!$A$2:$H$10,4,FALSE))</f>
+        <v>Australia</v>
       </c>
       <c r="C3" s="4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A3),Updates!$M$2:$M$100),VLOOKUP(A3,Baseline!$A$2:$H$10,5,FALSE))</f>
-        <v>46565</v>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A3),Updates!$M$2:$M$99),VLOOKUP(A3,Baseline!$A$2:$H$10,5,FALSE))</f>
+        <v>46089</v>
       </c>
       <c r="D3">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A3),Updates!$N$2:$N$100),VLOOKUP(A3,Baseline!$A$2:$H$10,6,FALSE))</f>
-        <v>1</v>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A3),Updates!$N$2:$N$99),VLOOKUP(A3,Baseline!$A$2:$H$10,6,FALSE))</f>
+        <v>0</v>
       </c>
       <c r="E3">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A3),Updates!$O$2:$O$100),VLOOKUP(A3,Baseline!$A$2:$H$10,7,FALSE))</f>
-        <v>9</v>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A3),Updates!$O$2:$O$99),VLOOKUP(A3,Baseline!$A$2:$H$10,7,FALSE))</f>
+        <v>8</v>
       </c>
       <c r="F3">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A3),Updates!$P$2:$P$100),VLOOKUP(A3,Baseline!$A$2:$H$10,8,FALSE))</f>
-        <v>5</v>
-      </c>
-      <c r="G3" s="4" t="str">
-        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A3)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
-        <v>TBD</v>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A3),Updates!$P$2:$P$99),VLOOKUP(A3,Baseline!$A$2:$H$10,8,FALSE))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="4">
+        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A3)*(Updates!$F$2:$F$99&lt;&gt;"Completed")*(Updates!$F$2:$F$99&lt;&gt;"Cancelled")*(Updates!$F$2:$F$99&lt;&gt;"Postponed")),Updates!$C$2:$C$99),"TBD")</f>
+        <v>46485</v>
       </c>
       <c r="H3" t="str">
-        <f>IF(G3="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A3)*(Updates!$C$2:$C$100=G3)),Updates!$D$2:$D$100),"TBD"))</f>
-        <v>TBD</v>
+        <f>IF(G3="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A3)*(Updates!$C$2:$C$99=G3)),Updates!$D$2:$D$99),"TBD"))</f>
+        <v>South Africa</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -5880,31 +5805,31 @@
         <v>35</v>
       </c>
       <c r="B4" t="str">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A4),Updates!$L$2:$L$100),VLOOKUP(A4,Baseline!$A$2:$H$10,4,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A4),Updates!$L$2:$L$99),VLOOKUP(A4,Baseline!$A$2:$H$10,4,FALSE))</f>
         <v>Australia</v>
       </c>
       <c r="C4" s="4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A4),Updates!$M$2:$M$100),VLOOKUP(A4,Baseline!$A$2:$H$10,5,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A4),Updates!$M$2:$M$99),VLOOKUP(A4,Baseline!$A$2:$H$10,5,FALSE))</f>
         <v>46187</v>
       </c>
       <c r="D4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A4),Updates!$N$2:$N$100),VLOOKUP(A4,Baseline!$A$2:$H$10,6,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A4),Updates!$N$2:$N$99),VLOOKUP(A4,Baseline!$A$2:$H$10,6,FALSE))</f>
         <v>0</v>
       </c>
       <c r="E4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A4),Updates!$O$2:$O$100),VLOOKUP(A4,Baseline!$A$2:$H$10,7,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A4),Updates!$O$2:$O$99),VLOOKUP(A4,Baseline!$A$2:$H$10,7,FALSE))</f>
         <v>358</v>
       </c>
       <c r="F4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A4),Updates!$P$2:$P$100),VLOOKUP(A4,Baseline!$A$2:$H$10,8,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A4),Updates!$P$2:$P$99),VLOOKUP(A4,Baseline!$A$2:$H$10,8,FALSE))</f>
         <v>596</v>
       </c>
       <c r="G4" s="4">
-        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A4)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
+        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A4)*(Updates!$F$2:$F$99&lt;&gt;"Completed")*(Updates!$F$2:$F$99&lt;&gt;"Cancelled")*(Updates!$F$2:$F$99&lt;&gt;"Postponed")),Updates!$C$2:$C$99),"TBD")</f>
         <v>46280</v>
       </c>
       <c r="H4" t="str">
-        <f>IF(G4="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A4)*(Updates!$C$2:$C$100=G4)),Updates!$D$2:$D$100),"TBD"))</f>
+        <f>IF(G4="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A4)*(Updates!$C$2:$C$99=G4)),Updates!$D$2:$D$99),"TBD"))</f>
         <v>Zimbabwe</v>
       </c>
     </row>
@@ -5913,31 +5838,31 @@
         <v>37</v>
       </c>
       <c r="B5" t="str">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A5),Updates!$L$2:$L$100),VLOOKUP(A5,Baseline!$A$2:$H$10,4,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A5),Updates!$L$2:$L$99),VLOOKUP(A5,Baseline!$A$2:$H$10,4,FALSE))</f>
         <v>Australia</v>
       </c>
       <c r="C5" s="4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A5),Updates!$M$2:$M$100),VLOOKUP(A5,Baseline!$A$2:$H$10,5,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A5),Updates!$M$2:$M$99),VLOOKUP(A5,Baseline!$A$2:$H$10,5,FALSE))</f>
         <v>46077</v>
       </c>
       <c r="D5">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A5),Updates!$N$2:$N$100),VLOOKUP(A5,Baseline!$A$2:$H$10,6,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A5),Updates!$N$2:$N$99),VLOOKUP(A5,Baseline!$A$2:$H$10,6,FALSE))</f>
         <v>5</v>
       </c>
       <c r="E5">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A5),Updates!$O$2:$O$100),VLOOKUP(A5,Baseline!$A$2:$H$10,7,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A5),Updates!$O$2:$O$99),VLOOKUP(A5,Baseline!$A$2:$H$10,7,FALSE))</f>
         <v>120</v>
       </c>
       <c r="F5">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A5),Updates!$P$2:$P$100),VLOOKUP(A5,Baseline!$A$2:$H$10,8,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A5),Updates!$P$2:$P$99),VLOOKUP(A5,Baseline!$A$2:$H$10,8,FALSE))</f>
         <v>251</v>
       </c>
       <c r="G5" s="4">
-        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A5)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
+        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A5)*(Updates!$F$2:$F$99&lt;&gt;"Completed")*(Updates!$F$2:$F$99&lt;&gt;"Cancelled")*(Updates!$F$2:$F$99&lt;&gt;"Postponed")),Updates!$C$2:$C$99),"TBD")</f>
         <v>46304</v>
       </c>
       <c r="H5" t="str">
-        <f>IF(G5="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A5)*(Updates!$C$2:$C$100=G5)),Updates!$D$2:$D$100),"TBD"))</f>
+        <f>IF(G5="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A5)*(Updates!$C$2:$C$99=G5)),Updates!$D$2:$D$99),"TBD"))</f>
         <v>Bangladesh</v>
       </c>
     </row>
@@ -5946,31 +5871,31 @@
         <v>39</v>
       </c>
       <c r="B6" t="str">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A6),Updates!$L$2:$L$100),VLOOKUP(A6,Baseline!$A$2:$H$10,4,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A6),Updates!$L$2:$L$99),VLOOKUP(A6,Baseline!$A$2:$H$10,4,FALSE))</f>
         <v>Ireland</v>
       </c>
       <c r="C6" s="4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A6),Updates!$M$2:$M$100),VLOOKUP(A6,Baseline!$A$2:$H$10,5,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A6),Updates!$M$2:$M$99),VLOOKUP(A6,Baseline!$A$2:$H$10,5,FALSE))</f>
         <v>46199</v>
       </c>
       <c r="D6">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A6),Updates!$N$2:$N$100),VLOOKUP(A6,Baseline!$A$2:$H$10,6,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A6),Updates!$N$2:$N$99),VLOOKUP(A6,Baseline!$A$2:$H$10,6,FALSE))</f>
         <v>1</v>
       </c>
       <c r="E6">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A6),Updates!$O$2:$O$100),VLOOKUP(A6,Baseline!$A$2:$H$10,7,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A6),Updates!$O$2:$O$99),VLOOKUP(A6,Baseline!$A$2:$H$10,7,FALSE))</f>
         <v>89</v>
       </c>
       <c r="F6">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A6),Updates!$P$2:$P$100),VLOOKUP(A6,Baseline!$A$2:$H$10,8,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A6),Updates!$P$2:$P$99),VLOOKUP(A6,Baseline!$A$2:$H$10,8,FALSE))</f>
         <v>152</v>
       </c>
       <c r="G6" s="4" t="str">
-        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A6)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
+        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A6)*(Updates!$F$2:$F$99&lt;&gt;"Completed")*(Updates!$F$2:$F$99&lt;&gt;"Cancelled")*(Updates!$F$2:$F$99&lt;&gt;"Postponed")),Updates!$C$2:$C$99),"TBD")</f>
         <v>TBD</v>
       </c>
       <c r="H6" t="str">
-        <f>IF(G6="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A6)*(Updates!$C$2:$C$100=G6)),Updates!$D$2:$D$100),"TBD"))</f>
+        <f>IF(G6="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A6)*(Updates!$C$2:$C$99=G6)),Updates!$D$2:$D$99),"TBD"))</f>
         <v>TBD</v>
       </c>
     </row>
@@ -5979,31 +5904,31 @@
         <v>42</v>
       </c>
       <c r="B7" t="str">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A7),Updates!$L$2:$L$100),VLOOKUP(A7,Baseline!$A$2:$H$10,4,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A7),Updates!$L$2:$L$99),VLOOKUP(A7,Baseline!$A$2:$H$10,4,FALSE))</f>
         <v>Australia</v>
       </c>
       <c r="C7" s="4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A7),Updates!$M$2:$M$100),VLOOKUP(A7,Baseline!$A$2:$H$10,5,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A7),Updates!$M$2:$M$99),VLOOKUP(A7,Baseline!$A$2:$H$10,5,FALSE))</f>
         <v>46186</v>
       </c>
       <c r="D7">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A7),Updates!$N$2:$N$100),VLOOKUP(A7,Baseline!$A$2:$H$10,6,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A7),Updates!$N$2:$N$99),VLOOKUP(A7,Baseline!$A$2:$H$10,6,FALSE))</f>
         <v>6</v>
       </c>
       <c r="E7">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A7),Updates!$O$2:$O$100),VLOOKUP(A7,Baseline!$A$2:$H$10,7,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A7),Updates!$O$2:$O$99),VLOOKUP(A7,Baseline!$A$2:$H$10,7,FALSE))</f>
         <v>76</v>
       </c>
       <c r="F7">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A7),Updates!$P$2:$P$100),VLOOKUP(A7,Baseline!$A$2:$H$10,8,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A7),Updates!$P$2:$P$99),VLOOKUP(A7,Baseline!$A$2:$H$10,8,FALSE))</f>
         <v>139</v>
       </c>
       <c r="G7" s="4">
-        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A7)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
+        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A7)*(Updates!$F$2:$F$99&lt;&gt;"Completed")*(Updates!$F$2:$F$99&lt;&gt;"Cancelled")*(Updates!$F$2:$F$99&lt;&gt;"Postponed")),Updates!$C$2:$C$99),"TBD")</f>
         <v>46313</v>
       </c>
       <c r="H7" t="str">
-        <f>IF(G7="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A7)*(Updates!$C$2:$C$100=G7)),Updates!$D$2:$D$100),"TBD"))</f>
+        <f>IF(G7="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A7)*(Updates!$C$2:$C$99=G7)),Updates!$D$2:$D$99),"TBD"))</f>
         <v>New Zealand</v>
       </c>
     </row>
@@ -6012,31 +5937,31 @@
         <v>44</v>
       </c>
       <c r="B8" t="str">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A8),Updates!$L$2:$L$100),VLOOKUP(A8,Baseline!$A$2:$H$10,4,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A8),Updates!$L$2:$L$99),VLOOKUP(A8,Baseline!$A$2:$H$10,4,FALSE))</f>
         <v>Royal Challengers Bengaluru</v>
       </c>
       <c r="C8" s="4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A8),Updates!$M$2:$M$100),VLOOKUP(A8,Baseline!$A$2:$H$10,5,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A8),Updates!$M$2:$M$99),VLOOKUP(A8,Baseline!$A$2:$H$10,5,FALSE))</f>
         <v>46173</v>
       </c>
       <c r="D8">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A8),Updates!$N$2:$N$100),VLOOKUP(A8,Baseline!$A$2:$H$10,6,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A8),Updates!$N$2:$N$99),VLOOKUP(A8,Baseline!$A$2:$H$10,6,FALSE))</f>
         <v>0</v>
       </c>
       <c r="E8">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A8),Updates!$O$2:$O$100),VLOOKUP(A8,Baseline!$A$2:$H$10,7,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A8),Updates!$O$2:$O$99),VLOOKUP(A8,Baseline!$A$2:$H$10,7,FALSE))</f>
         <v>150</v>
       </c>
       <c r="F8">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A8),Updates!$P$2:$P$100),VLOOKUP(A8,Baseline!$A$2:$H$10,8,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A8),Updates!$P$2:$P$99),VLOOKUP(A8,Baseline!$A$2:$H$10,8,FALSE))</f>
         <v>125</v>
       </c>
       <c r="G8" s="4" t="str">
-        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A8)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
+        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A8)*(Updates!$F$2:$F$99&lt;&gt;"Completed")*(Updates!$F$2:$F$99&lt;&gt;"Cancelled")*(Updates!$F$2:$F$99&lt;&gt;"Postponed")),Updates!$C$2:$C$99),"TBD")</f>
         <v>TBD</v>
       </c>
       <c r="H8" t="str">
-        <f>IF(G8="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A8)*(Updates!$C$2:$C$100=G8)),Updates!$D$2:$D$100),"TBD"))</f>
+        <f>IF(G8="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A8)*(Updates!$C$2:$C$99=G8)),Updates!$D$2:$D$99),"TBD"))</f>
         <v>TBD</v>
       </c>
     </row>
@@ -6045,31 +5970,31 @@
         <v>47</v>
       </c>
       <c r="B9" t="str">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A9),Updates!$L$2:$L$100),VLOOKUP(A9,Baseline!$A$2:$H$10,4,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A9),Updates!$L$2:$L$99),VLOOKUP(A9,Baseline!$A$2:$H$10,4,FALSE))</f>
         <v>Bayern München</v>
       </c>
       <c r="C9" s="4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A9),Updates!$M$2:$M$100),VLOOKUP(A9,Baseline!$A$2:$H$10,5,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A9),Updates!$M$2:$M$99),VLOOKUP(A9,Baseline!$A$2:$H$10,5,FALSE))</f>
         <v>46081</v>
       </c>
       <c r="D9">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A9),Updates!$N$2:$N$100),VLOOKUP(A9,Baseline!$A$2:$H$10,6,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A9),Updates!$N$2:$N$99),VLOOKUP(A9,Baseline!$A$2:$H$10,6,FALSE))</f>
         <v>11</v>
       </c>
       <c r="E9">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A9),Updates!$O$2:$O$100),VLOOKUP(A9,Baseline!$A$2:$H$10,7,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A9),Updates!$O$2:$O$99),VLOOKUP(A9,Baseline!$A$2:$H$10,7,FALSE))</f>
         <v>681</v>
       </c>
       <c r="F9">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A9),Updates!$P$2:$P$100),VLOOKUP(A9,Baseline!$A$2:$H$10,8,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A9),Updates!$P$2:$P$99),VLOOKUP(A9,Baseline!$A$2:$H$10,8,FALSE))</f>
         <v>1443</v>
       </c>
       <c r="G9" s="4">
-        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A9)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
+        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A9)*(Updates!$F$2:$F$99&lt;&gt;"Completed")*(Updates!$F$2:$F$99&lt;&gt;"Cancelled")*(Updates!$F$2:$F$99&lt;&gt;"Postponed")),Updates!$C$2:$C$99),"TBD")</f>
         <v>46269</v>
       </c>
       <c r="H9" t="str">
-        <f>IF(G9="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A9)*(Updates!$C$2:$C$100=G9)),Updates!$D$2:$D$100),"TBD"))</f>
+        <f>IF(G9="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A9)*(Updates!$C$2:$C$99=G9)),Updates!$D$2:$D$99),"TBD"))</f>
         <v>Schalke FC</v>
       </c>
     </row>
@@ -6078,31 +6003,31 @@
         <v>51</v>
       </c>
       <c r="B10" t="str">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A10),Updates!$L$2:$L$100),VLOOKUP(A10,Baseline!$A$2:$H$10,4,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A10),Updates!$L$2:$L$99),VLOOKUP(A10,Baseline!$A$2:$H$10,4,FALSE))</f>
         <v>Bayern München</v>
       </c>
       <c r="C10" s="4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A10),Updates!$M$2:$M$100),VLOOKUP(A10,Baseline!$A$2:$H$10,5,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A10),Updates!$M$2:$M$99),VLOOKUP(A10,Baseline!$A$2:$H$10,5,FALSE))</f>
         <v>45730</v>
       </c>
       <c r="D10">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A10),Updates!$N$2:$N$100),VLOOKUP(A10,Baseline!$A$2:$H$10,6,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A10),Updates!$N$2:$N$99),VLOOKUP(A10,Baseline!$A$2:$H$10,6,FALSE))</f>
         <v>32</v>
       </c>
       <c r="E10">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A10),Updates!$O$2:$O$100),VLOOKUP(A10,Baseline!$A$2:$H$10,7,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A10),Updates!$O$2:$O$99),VLOOKUP(A10,Baseline!$A$2:$H$10,7,FALSE))</f>
         <v>113</v>
       </c>
       <c r="F10">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A10),Updates!$P$2:$P$100),VLOOKUP(A10,Baseline!$A$2:$H$10,8,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A10),Updates!$P$2:$P$99),VLOOKUP(A10,Baseline!$A$2:$H$10,8,FALSE))</f>
         <v>655</v>
       </c>
       <c r="G10" s="4">
-        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A10)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
+        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A10)*(Updates!$F$2:$F$99&lt;&gt;"Completed")*(Updates!$F$2:$F$99&lt;&gt;"Cancelled")*(Updates!$F$2:$F$99&lt;&gt;"Postponed")),Updates!$C$2:$C$99),"TBD")</f>
         <v>46265</v>
       </c>
       <c r="H10" t="str">
-        <f>IF(G10="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A10)*(Updates!$C$2:$C$100=G10)),Updates!$D$2:$D$100),"TBD"))</f>
+        <f>IF(G10="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A10)*(Updates!$C$2:$C$99=G10)),Updates!$D$2:$D$99),"TBD"))</f>
         <v>1. FSV Mainz 05</v>
       </c>
     </row>
@@ -6122,28 +6047,28 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15">
       <c r="A1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -6187,31 +6112,31 @@
       </c>
       <c r="B3" t="str">
         <f>Dashboard!B3</f>
-        <v>England</v>
+        <v>Australia</v>
       </c>
       <c r="C3" s="9">
         <f>Dashboard!C3</f>
-        <v>46565</v>
+        <v>46089</v>
       </c>
       <c r="D3">
         <f>Dashboard!D3</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <f>Dashboard!E3</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <f>Dashboard!F3</f>
-        <v>5</v>
-      </c>
-      <c r="G3" s="9" t="str">
+        <v>4</v>
+      </c>
+      <c r="G3" s="9">
         <f>Dashboard!G3</f>
-        <v>TBD</v>
+        <v>46485</v>
       </c>
       <c r="H3" t="str">
         <f>Dashboard!H3</f>
-        <v>TBD</v>
+        <v>South Africa</v>
       </c>
     </row>
     <row r="4" spans="1:8">

--- a/LSC_Update_System.xlsx
+++ b/LSC_Update_System.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CH\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AADD10E5-E803-4275-976C-0D18458EC925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8A0F1A8-18D3-435C-9D7F-5B2808EE1C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="START HERE" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="118">
   <si>
     <t>LSC UPDATE SYSTEM — SAFE TEST</t>
   </si>
@@ -387,6 +387,9 @@
   </si>
   <si>
     <t>Senwes Park, Potchesfstroom</t>
+  </si>
+  <si>
+    <t>Australia win by 10 wickets</t>
   </si>
 </sst>
 </file>
@@ -1407,10 +1410,14 @@
         <v>91</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="10"/>
+        <v>63</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>117</v>
+      </c>
       <c r="I4" s="5"/>
       <c r="J4" s="6" t="str">
         <f>IF(B4="","",IFERROR(LOOKUP(2,1/($B$2:B3=B4),$L$2:L3),VLOOKUP(B4,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -1418,7 +1425,7 @@
       </c>
       <c r="K4" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>Scheduled</v>
+        <v>Defence</v>
       </c>
       <c r="L4" s="6" t="str">
         <f t="shared" si="1"/>
@@ -1430,7 +1437,7 @@
       </c>
       <c r="N4" s="6">
         <f>IF(B4="","",IF(K4="INVALID — CHECK RESULT TYPE","",IF(K4="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B3=B4),$N$2:N3),VLOOKUP(B4,Baseline!$A$2:$H$10,6,FALSE))+IF(K4="Defence",1,0))))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" s="6">
         <f>IF(B4="","",IF(K4="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B3=B4),$O$2:O3),VLOOKUP(B4,Baseline!$A$2:$H$10,7,FALSE))+IF(K4="Transfer",1,0)))</f>
@@ -1438,7 +1445,7 @@
       </c>
       <c r="P4" s="6">
         <f>IF(B4="","",IF(K4="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B3=B4),$P$2:P3),VLOOKUP(B4,Baseline!$A$2:$H$10,8,FALSE))+IF(K4="Defence",1,0)))</f>
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="Q4" s="5"/>
       <c r="R4" s="12"/>
@@ -5814,7 +5821,7 @@
       </c>
       <c r="D4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A4),Updates!$N$2:$N$99),VLOOKUP(A4,Baseline!$A$2:$H$10,6,FALSE))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A4),Updates!$O$2:$O$99),VLOOKUP(A4,Baseline!$A$2:$H$10,7,FALSE))</f>
@@ -5822,15 +5829,15 @@
       </c>
       <c r="F4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A4),Updates!$P$2:$P$99),VLOOKUP(A4,Baseline!$A$2:$H$10,8,FALSE))</f>
-        <v>596</v>
-      </c>
-      <c r="G4" s="4">
+        <v>597</v>
+      </c>
+      <c r="G4" s="4" t="str">
         <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A4)*(Updates!$F$2:$F$99&lt;&gt;"Completed")*(Updates!$F$2:$F$99&lt;&gt;"Cancelled")*(Updates!$F$2:$F$99&lt;&gt;"Postponed")),Updates!$C$2:$C$99),"TBD")</f>
-        <v>46280</v>
+        <v>TBD</v>
       </c>
       <c r="H4" t="str">
         <f>IF(G4="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A4)*(Updates!$C$2:$C$99=G4)),Updates!$D$2:$D$99),"TBD"))</f>
-        <v>Zimbabwe</v>
+        <v>TBD</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -6154,7 +6161,7 @@
       </c>
       <c r="D4">
         <f>Dashboard!D4</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <f>Dashboard!E4</f>
@@ -6162,15 +6169,15 @@
       </c>
       <c r="F4">
         <f>Dashboard!F4</f>
-        <v>596</v>
-      </c>
-      <c r="G4" s="9">
+        <v>597</v>
+      </c>
+      <c r="G4" s="9" t="str">
         <f>Dashboard!G4</f>
-        <v>46280</v>
+        <v>TBD</v>
       </c>
       <c r="H4" t="str">
         <f>Dashboard!H4</f>
-        <v>Zimbabwe</v>
+        <v>TBD</v>
       </c>
     </row>
     <row r="5" spans="1:8">

--- a/LSC_Update_System.xlsx
+++ b/LSC_Update_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CH\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8A0F1A8-18D3-435C-9D7F-5B2808EE1C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{384AA9C4-FC90-4DCA-8C3B-1CB10BF4F20C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -389,7 +389,7 @@
     <t>Senwes Park, Potchesfstroom</t>
   </si>
   <si>
-    <t>Australia win by 10 wickets</t>
+    <t>ZImbabwe win by 10 wickets</t>
   </si>
 </sst>
 </file>
@@ -1413,7 +1413,7 @@
         <v>63</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H4" s="10" t="s">
         <v>117</v>
@@ -1425,27 +1425,27 @@
       </c>
       <c r="K4" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>Defence</v>
+        <v>Transfer</v>
       </c>
       <c r="L4" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>Australia</v>
+        <v>Zimbabwe</v>
       </c>
       <c r="M4" s="8">
         <f>IF(B4="","",IF(K4="INVALID — CHECK RESULT TYPE","",IF(K4="Transfer",IF(R4&lt;&gt;"",R4,C4),IFERROR(LOOKUP(2,1/($B$2:B3=B4),$M$2:M3),VLOOKUP(B4,Baseline!$A$2:$H$10,5,FALSE)))))</f>
-        <v>46187</v>
+        <v>46280</v>
       </c>
       <c r="N4" s="6">
         <f>IF(B4="","",IF(K4="INVALID — CHECK RESULT TYPE","",IF(K4="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B3=B4),$N$2:N3),VLOOKUP(B4,Baseline!$A$2:$H$10,6,FALSE))+IF(K4="Defence",1,0))))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" s="6">
         <f>IF(B4="","",IF(K4="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B3=B4),$O$2:O3),VLOOKUP(B4,Baseline!$A$2:$H$10,7,FALSE))+IF(K4="Transfer",1,0)))</f>
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P4" s="6">
         <f>IF(B4="","",IF(K4="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B3=B4),$P$2:P3),VLOOKUP(B4,Baseline!$A$2:$H$10,8,FALSE))+IF(K4="Defence",1,0)))</f>
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="Q4" s="5"/>
       <c r="R4" s="12"/>
@@ -5813,23 +5813,23 @@
       </c>
       <c r="B4" t="str">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A4),Updates!$L$2:$L$99),VLOOKUP(A4,Baseline!$A$2:$H$10,4,FALSE))</f>
-        <v>Australia</v>
+        <v>Zimbabwe</v>
       </c>
       <c r="C4" s="4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A4),Updates!$M$2:$M$99),VLOOKUP(A4,Baseline!$A$2:$H$10,5,FALSE))</f>
-        <v>46187</v>
+        <v>46280</v>
       </c>
       <c r="D4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A4),Updates!$N$2:$N$99),VLOOKUP(A4,Baseline!$A$2:$H$10,6,FALSE))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A4),Updates!$O$2:$O$99),VLOOKUP(A4,Baseline!$A$2:$H$10,7,FALSE))</f>
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A4),Updates!$P$2:$P$99),VLOOKUP(A4,Baseline!$A$2:$H$10,8,FALSE))</f>
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G4" s="4" t="str">
         <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A4)*(Updates!$F$2:$F$99&lt;&gt;"Completed")*(Updates!$F$2:$F$99&lt;&gt;"Cancelled")*(Updates!$F$2:$F$99&lt;&gt;"Postponed")),Updates!$C$2:$C$99),"TBD")</f>
@@ -6153,23 +6153,23 @@
       </c>
       <c r="B4" t="str">
         <f>Dashboard!B4</f>
-        <v>Australia</v>
+        <v>Zimbabwe</v>
       </c>
       <c r="C4" s="9">
         <f>Dashboard!C4</f>
-        <v>46187</v>
+        <v>46280</v>
       </c>
       <c r="D4">
         <f>Dashboard!D4</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <f>Dashboard!E4</f>
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F4">
         <f>Dashboard!F4</f>
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G4" s="9" t="str">
         <f>Dashboard!G4</f>

--- a/LSC_Update_System.xlsx
+++ b/LSC_Update_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CH\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{384AA9C4-FC90-4DCA-8C3B-1CB10BF4F20C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71D61A04-6A66-4A3E-A651-F68B186E9029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="120">
   <si>
     <t>LSC UPDATE SYSTEM — SAFE TEST</t>
   </si>
@@ -390,6 +390,12 @@
   </si>
   <si>
     <t>ZImbabwe win by 10 wickets</t>
+  </si>
+  <si>
+    <t>ireland</t>
+  </si>
+  <si>
+    <t>zimbabwe win by 5 wickets</t>
   </si>
 </sst>
 </file>
@@ -1721,43 +1727,55 @@
     <row r="10" spans="1:18">
       <c r="A10" s="6" t="str">
         <f>IF(OR(B10="",C10=""),"",VLOOKUP(B10,Lists!$A$2:$B$10,2,FALSE)&amp;"-"&amp;TEXT(C10,"yyyymmdd")&amp;"-"&amp;TEXT(COUNTIFS($B$2:B10,B10,$C$2:C10,C10),"00"))</f>
-        <v/>
-      </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="5"/>
+        <v>JEJ-20261231-01</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="7">
+        <v>46387</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>118</v>
+      </c>
       <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="10"/>
+      <c r="F10" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>119</v>
+      </c>
       <c r="I10" s="5"/>
       <c r="J10" s="6" t="str">
         <f>IF(B10="","",IFERROR(LOOKUP(2,1/($B$2:B9=B10),$L$2:L9),VLOOKUP(B10,Baseline!$A$2:$H$10,4,FALSE)))</f>
-        <v/>
+        <v>Zimbabwe</v>
       </c>
       <c r="K10" s="6" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Defence</v>
       </c>
       <c r="L10" s="6" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M10" s="8" t="str">
+        <v>Zimbabwe</v>
+      </c>
+      <c r="M10" s="8">
         <f>IF(B10="","",IF(K10="Transfer",C10,IFERROR(LOOKUP(2,1/($B$2:B9=B10),$M$2:M9),VLOOKUP(B10,Baseline!$A$2:$H$10,5,FALSE))))</f>
-        <v/>
-      </c>
-      <c r="N10" s="6" t="str">
+        <v>46280</v>
+      </c>
+      <c r="N10" s="6">
         <f>IF(B10="","",IF(K10="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B9=B10),$N$2:N9),VLOOKUP(B10,Baseline!$A$2:$H$10,6,FALSE))+IF(K10="Defence",1,0)))</f>
-        <v/>
-      </c>
-      <c r="O10" s="6" t="str">
+        <v>1</v>
+      </c>
+      <c r="O10" s="6">
         <f>IF(B10="","",IFERROR(LOOKUP(2,1/($B$2:B9=B10),$O$2:O9),VLOOKUP(B10,Baseline!$A$2:$H$10,7,FALSE))+IF(K10="Transfer",1,0))</f>
-        <v/>
-      </c>
-      <c r="P10" s="6" t="str">
+        <v>359</v>
+      </c>
+      <c r="P10" s="6">
         <f>IF(B10="","",IFERROR(LOOKUP(2,1/($B$2:B9=B10),$P$2:P9),VLOOKUP(B10,Baseline!$A$2:$H$10,8,FALSE))+IF(K10="Defence",1,0))</f>
-        <v/>
+        <v>597</v>
       </c>
       <c r="Q10" s="5"/>
       <c r="R10" s="12"/>
@@ -5821,7 +5839,7 @@
       </c>
       <c r="D4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A4),Updates!$N$2:$N$99),VLOOKUP(A4,Baseline!$A$2:$H$10,6,FALSE))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A4),Updates!$O$2:$O$99),VLOOKUP(A4,Baseline!$A$2:$H$10,7,FALSE))</f>
@@ -5829,7 +5847,7 @@
       </c>
       <c r="F4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A4),Updates!$P$2:$P$99),VLOOKUP(A4,Baseline!$A$2:$H$10,8,FALSE))</f>
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="G4" s="4" t="str">
         <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A4)*(Updates!$F$2:$F$99&lt;&gt;"Completed")*(Updates!$F$2:$F$99&lt;&gt;"Cancelled")*(Updates!$F$2:$F$99&lt;&gt;"Postponed")),Updates!$C$2:$C$99),"TBD")</f>
@@ -6161,7 +6179,7 @@
       </c>
       <c r="D4">
         <f>Dashboard!D4</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <f>Dashboard!E4</f>
@@ -6169,7 +6187,7 @@
       </c>
       <c r="F4">
         <f>Dashboard!F4</f>
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="G4" s="9" t="str">
         <f>Dashboard!G4</f>

--- a/LSC_Update_System.xlsx
+++ b/LSC_Update_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CH\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71D61A04-6A66-4A3E-A651-F68B186E9029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7187EA3-C3B5-4C4E-9677-E82F2F8E6A36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="117">
   <si>
     <t>LSC UPDATE SYSTEM — SAFE TEST</t>
   </si>
@@ -387,15 +387,6 @@
   </si>
   <si>
     <t>Senwes Park, Potchesfstroom</t>
-  </si>
-  <si>
-    <t>ZImbabwe win by 10 wickets</t>
-  </si>
-  <si>
-    <t>ireland</t>
-  </si>
-  <si>
-    <t>zimbabwe win by 5 wickets</t>
   </si>
 </sst>
 </file>
@@ -1208,7 +1199,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:R99"/>
+  <dimension ref="A1:R98"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1313,11 +1304,11 @@
         <v>South Africa</v>
       </c>
       <c r="K2" s="6" t="str">
-        <f t="shared" ref="K2:K32" si="0">IF(B2="","",IF(F2&lt;&gt;"Completed",F2,IF(G2="Challenger win","Transfer",IF(OR(G2="Holder win",G2="Draw / tie"),"Defence",IF(G2="No result","No result","INVALID — CHECK RESULT TYPE")))))</f>
+        <f t="shared" ref="K2:K31" si="0">IF(B2="","",IF(F2&lt;&gt;"Completed",F2,IF(G2="Challenger win","Transfer",IF(OR(G2="Holder win",G2="Draw / tie"),"Defence",IF(G2="No result","No result","INVALID — CHECK RESULT TYPE")))))</f>
         <v>Scheduled</v>
       </c>
       <c r="L2" s="6" t="str">
-        <f t="shared" ref="L2:L32" si="1">IF(B2="","",IF(K2="INVALID — CHECK RESULT TYPE","",IF(K2="Transfer",D2,J2)))</f>
+        <f t="shared" ref="L2:L31" si="1">IF(B2="","",IF(K2="INVALID — CHECK RESULT TYPE","",IF(K2="Transfer",D2,J2)))</f>
         <v>South Africa</v>
       </c>
       <c r="M2" s="8">
@@ -1416,14 +1407,10 @@
         <v>91</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>117</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="10"/>
       <c r="I4" s="5"/>
       <c r="J4" s="6" t="str">
         <f>IF(B4="","",IFERROR(LOOKUP(2,1/($B$2:B3=B4),$L$2:L3),VLOOKUP(B4,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -1431,15 +1418,15 @@
       </c>
       <c r="K4" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>Transfer</v>
+        <v>Scheduled</v>
       </c>
       <c r="L4" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>Zimbabwe</v>
+        <v>Australia</v>
       </c>
       <c r="M4" s="8">
         <f>IF(B4="","",IF(K4="INVALID — CHECK RESULT TYPE","",IF(K4="Transfer",IF(R4&lt;&gt;"",R4,C4),IFERROR(LOOKUP(2,1/($B$2:B3=B4),$M$2:M3),VLOOKUP(B4,Baseline!$A$2:$H$10,5,FALSE)))))</f>
-        <v>46280</v>
+        <v>46187</v>
       </c>
       <c r="N4" s="6">
         <f>IF(B4="","",IF(K4="INVALID — CHECK RESULT TYPE","",IF(K4="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B3=B4),$N$2:N3),VLOOKUP(B4,Baseline!$A$2:$H$10,6,FALSE))+IF(K4="Defence",1,0))))</f>
@@ -1447,7 +1434,7 @@
       </c>
       <c r="O4" s="6">
         <f>IF(B4="","",IF(K4="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B3=B4),$O$2:O3),VLOOKUP(B4,Baseline!$A$2:$H$10,7,FALSE))+IF(K4="Transfer",1,0)))</f>
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="P4" s="6">
         <f>IF(B4="","",IF(K4="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B3=B4),$P$2:P3),VLOOKUP(B4,Baseline!$A$2:$H$10,8,FALSE))+IF(K4="Defence",1,0)))</f>
@@ -1727,55 +1714,43 @@
     <row r="10" spans="1:18">
       <c r="A10" s="6" t="str">
         <f>IF(OR(B10="",C10=""),"",VLOOKUP(B10,Lists!$A$2:$B$10,2,FALSE)&amp;"-"&amp;TEXT(C10,"yyyymmdd")&amp;"-"&amp;TEXT(COUNTIFS($B$2:B10,B10,$C$2:C10,C10),"00"))</f>
-        <v>JEJ-20261231-01</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="7">
-        <v>46387</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>118</v>
-      </c>
+        <v/>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="5"/>
       <c r="E10" s="5"/>
-      <c r="F10" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>119</v>
-      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="10"/>
       <c r="I10" s="5"/>
       <c r="J10" s="6" t="str">
         <f>IF(B10="","",IFERROR(LOOKUP(2,1/($B$2:B9=B10),$L$2:L9),VLOOKUP(B10,Baseline!$A$2:$H$10,4,FALSE)))</f>
-        <v>Zimbabwe</v>
+        <v/>
       </c>
       <c r="K10" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>Defence</v>
+        <v/>
       </c>
       <c r="L10" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>Zimbabwe</v>
-      </c>
-      <c r="M10" s="8">
+        <v/>
+      </c>
+      <c r="M10" s="8" t="str">
         <f>IF(B10="","",IF(K10="Transfer",C10,IFERROR(LOOKUP(2,1/($B$2:B9=B10),$M$2:M9),VLOOKUP(B10,Baseline!$A$2:$H$10,5,FALSE))))</f>
-        <v>46280</v>
-      </c>
-      <c r="N10" s="6">
+        <v/>
+      </c>
+      <c r="N10" s="6" t="str">
         <f>IF(B10="","",IF(K10="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B9=B10),$N$2:N9),VLOOKUP(B10,Baseline!$A$2:$H$10,6,FALSE))+IF(K10="Defence",1,0)))</f>
-        <v>1</v>
-      </c>
-      <c r="O10" s="6">
+        <v/>
+      </c>
+      <c r="O10" s="6" t="str">
         <f>IF(B10="","",IFERROR(LOOKUP(2,1/($B$2:B9=B10),$O$2:O9),VLOOKUP(B10,Baseline!$A$2:$H$10,7,FALSE))+IF(K10="Transfer",1,0))</f>
-        <v>359</v>
-      </c>
-      <c r="P10" s="6">
+        <v/>
+      </c>
+      <c r="P10" s="6" t="str">
         <f>IF(B10="","",IFERROR(LOOKUP(2,1/($B$2:B9=B10),$P$2:P9),VLOOKUP(B10,Baseline!$A$2:$H$10,8,FALSE))+IF(K10="Defence",1,0))</f>
-        <v>597</v>
+        <v/>
       </c>
       <c r="Q10" s="5"/>
       <c r="R10" s="12"/>
@@ -2722,11 +2697,11 @@
         <v/>
       </c>
       <c r="K32" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="K32:K63" si="2">IF(B32="","",IF(F32&lt;&gt;"Completed",F32,IF(G32="Challenger win","Transfer",IF(OR(G32="Holder win",G32="Draw / tie"),"Defence",IF(G32="No result","No result","REVIEW")))))</f>
         <v/>
       </c>
       <c r="L32" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="L32:L63" si="3">IF(B32="","",IF(K32="Transfer",D32,J32))</f>
         <v/>
       </c>
       <c r="M32" s="8" t="str">
@@ -2766,11 +2741,11 @@
         <v/>
       </c>
       <c r="K33" s="6" t="str">
-        <f t="shared" ref="K33:K64" si="2">IF(B33="","",IF(F33&lt;&gt;"Completed",F33,IF(G33="Challenger win","Transfer",IF(OR(G33="Holder win",G33="Draw / tie"),"Defence",IF(G33="No result","No result","REVIEW")))))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L33" s="6" t="str">
-        <f t="shared" ref="L33:L64" si="3">IF(B33="","",IF(K33="Transfer",D33,J33))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M33" s="8" t="str">
@@ -4130,11 +4105,11 @@
         <v/>
       </c>
       <c r="K64" s="6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="K64:K98" si="4">IF(B64="","",IF(F64&lt;&gt;"Completed",F64,IF(G64="Challenger win","Transfer",IF(OR(G64="Holder win",G64="Draw / tie"),"Defence",IF(G64="No result","No result","REVIEW")))))</f>
         <v/>
       </c>
       <c r="L64" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="L64:L95" si="5">IF(B64="","",IF(K64="Transfer",D64,J64))</f>
         <v/>
       </c>
       <c r="M64" s="8" t="str">
@@ -4174,11 +4149,11 @@
         <v/>
       </c>
       <c r="K65" s="6" t="str">
-        <f t="shared" ref="K65:K99" si="4">IF(B65="","",IF(F65&lt;&gt;"Completed",F65,IF(G65="Challenger win","Transfer",IF(OR(G65="Holder win",G65="Draw / tie"),"Defence",IF(G65="No result","No result","REVIEW")))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L65" s="6" t="str">
-        <f t="shared" ref="L65:L96" si="5">IF(B65="","",IF(K65="Transfer",D65,J65))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="M65" s="8" t="str">
@@ -5542,7 +5517,7 @@
         <v/>
       </c>
       <c r="L96" s="6" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="L96:L98" si="6">IF(B96="","",IF(K96="Transfer",D96,J96))</f>
         <v/>
       </c>
       <c r="M96" s="8" t="str">
@@ -5586,7 +5561,7 @@
         <v/>
       </c>
       <c r="L97" s="6" t="str">
-        <f t="shared" ref="L97:L99" si="6">IF(B97="","",IF(K97="Transfer",D97,J97))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="M97" s="8" t="str">
@@ -5652,52 +5627,8 @@
       <c r="Q98" s="5"/>
       <c r="R98" s="12"/>
     </row>
-    <row r="99" spans="1:18">
-      <c r="A99" s="6" t="str">
-        <f>IF(OR(B99="",C99=""),"",VLOOKUP(B99,Lists!$A$2:$B$10,2,FALSE)&amp;"-"&amp;TEXT(C99,"yyyymmdd")&amp;"-"&amp;TEXT(COUNTIFS($B$2:B99,B99,$C$2:C99,C99),"00"))</f>
-        <v/>
-      </c>
-      <c r="B99" s="5"/>
-      <c r="C99" s="7"/>
-      <c r="D99" s="5"/>
-      <c r="E99" s="5"/>
-      <c r="F99" s="5"/>
-      <c r="G99" s="5"/>
-      <c r="H99" s="10"/>
-      <c r="I99" s="5"/>
-      <c r="J99" s="6" t="str">
-        <f>IF(B99="","",IFERROR(LOOKUP(2,1/($B$2:B98=B99),$L$2:L98),VLOOKUP(B99,Baseline!$A$2:$H$10,4,FALSE)))</f>
-        <v/>
-      </c>
-      <c r="K99" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L99" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="M99" s="8" t="str">
-        <f>IF(B99="","",IF(K99="Transfer",C99,IFERROR(LOOKUP(2,1/($B$2:B98=B99),$M$2:M98),VLOOKUP(B99,Baseline!$A$2:$H$10,5,FALSE))))</f>
-        <v/>
-      </c>
-      <c r="N99" s="6" t="str">
-        <f>IF(B99="","",IF(K99="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B98=B99),$N$2:N98),VLOOKUP(B99,Baseline!$A$2:$H$10,6,FALSE))+IF(K99="Defence",1,0)))</f>
-        <v/>
-      </c>
-      <c r="O99" s="6" t="str">
-        <f>IF(B99="","",IFERROR(LOOKUP(2,1/($B$2:B98=B99),$O$2:O98),VLOOKUP(B99,Baseline!$A$2:$H$10,7,FALSE))+IF(K99="Transfer",1,0))</f>
-        <v/>
-      </c>
-      <c r="P99" s="6" t="str">
-        <f>IF(B99="","",IFERROR(LOOKUP(2,1/($B$2:B98=B99),$P$2:P98),VLOOKUP(B99,Baseline!$A$2:$H$10,8,FALSE))+IF(K99="Defence",1,0))</f>
-        <v/>
-      </c>
-      <c r="Q99" s="5"/>
-      <c r="R99" s="12"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="K2:K99">
+  <conditionalFormatting sqref="K2:K98">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>K2="INVALID — CHECK RESULT TYPE"</formula>
     </cfRule>
@@ -5710,13 +5641,13 @@
           <x14:formula1>
             <xm:f>Lists!$D$2:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F99</xm:sqref>
+          <xm:sqref>F2:F98</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0300-000001000000}">
           <x14:formula1>
             <xm:f>Lists!$E$2:$E$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G99</xm:sqref>
+          <xm:sqref>G2:G98</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5764,31 +5695,31 @@
         <v>28</v>
       </c>
       <c r="B2" t="str">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A2),Updates!$L$2:$L$99),VLOOKUP(A2,Baseline!$A$2:$H$10,4,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A2),Updates!$L$2:$L$98),VLOOKUP(A2,Baseline!$A$2:$H$10,4,FALSE))</f>
         <v>South Africa</v>
       </c>
       <c r="C2" s="4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A2),Updates!$M$2:$M$99),VLOOKUP(A2,Baseline!$A$2:$H$10,5,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A2),Updates!$M$2:$M$98),VLOOKUP(A2,Baseline!$A$2:$H$10,5,FALSE))</f>
         <v>45953</v>
       </c>
       <c r="D2">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A2),Updates!$N$2:$N$99),VLOOKUP(A2,Baseline!$A$2:$H$10,6,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A2),Updates!$N$2:$N$98),VLOOKUP(A2,Baseline!$A$2:$H$10,6,FALSE))</f>
         <v>2</v>
       </c>
       <c r="E2">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A2),Updates!$O$2:$O$99),VLOOKUP(A2,Baseline!$A$2:$H$10,7,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A2),Updates!$O$2:$O$98),VLOOKUP(A2,Baseline!$A$2:$H$10,7,FALSE))</f>
         <v>172</v>
       </c>
       <c r="F2">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A2),Updates!$P$2:$P$99),VLOOKUP(A2,Baseline!$A$2:$H$10,8,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A2),Updates!$P$2:$P$98),VLOOKUP(A2,Baseline!$A$2:$H$10,8,FALSE))</f>
         <v>270</v>
       </c>
       <c r="G2" s="4">
-        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A2)*(Updates!$F$2:$F$99&lt;&gt;"Completed")*(Updates!$F$2:$F$99&lt;&gt;"Cancelled")*(Updates!$F$2:$F$99&lt;&gt;"Postponed")),Updates!$C$2:$C$99),"TBD")</f>
+        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$98=A2)*(Updates!$F$2:$F$98&lt;&gt;"Completed")*(Updates!$F$2:$F$98&lt;&gt;"Cancelled")*(Updates!$F$2:$F$98&lt;&gt;"Postponed")),Updates!$C$2:$C$98),"TBD")</f>
         <v>46304</v>
       </c>
       <c r="H2" t="str">
-        <f>IF(G2="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A2)*(Updates!$C$2:$C$99=G2)),Updates!$D$2:$D$99),"TBD"))</f>
+        <f>IF(G2="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$98=A2)*(Updates!$C$2:$C$98=G2)),Updates!$D$2:$D$98),"TBD"))</f>
         <v>Australia</v>
       </c>
     </row>
@@ -5797,31 +5728,31 @@
         <v>32</v>
       </c>
       <c r="B3" t="str">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A3),Updates!$L$2:$L$99),VLOOKUP(A3,Baseline!$A$2:$H$10,4,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A3),Updates!$L$2:$L$98),VLOOKUP(A3,Baseline!$A$2:$H$10,4,FALSE))</f>
         <v>Australia</v>
       </c>
       <c r="C3" s="4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A3),Updates!$M$2:$M$99),VLOOKUP(A3,Baseline!$A$2:$H$10,5,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A3),Updates!$M$2:$M$98),VLOOKUP(A3,Baseline!$A$2:$H$10,5,FALSE))</f>
         <v>46089</v>
       </c>
       <c r="D3">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A3),Updates!$N$2:$N$99),VLOOKUP(A3,Baseline!$A$2:$H$10,6,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A3),Updates!$N$2:$N$98),VLOOKUP(A3,Baseline!$A$2:$H$10,6,FALSE))</f>
         <v>0</v>
       </c>
       <c r="E3">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A3),Updates!$O$2:$O$99),VLOOKUP(A3,Baseline!$A$2:$H$10,7,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A3),Updates!$O$2:$O$98),VLOOKUP(A3,Baseline!$A$2:$H$10,7,FALSE))</f>
         <v>8</v>
       </c>
       <c r="F3">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A3),Updates!$P$2:$P$99),VLOOKUP(A3,Baseline!$A$2:$H$10,8,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A3),Updates!$P$2:$P$98),VLOOKUP(A3,Baseline!$A$2:$H$10,8,FALSE))</f>
         <v>4</v>
       </c>
       <c r="G3" s="4">
-        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A3)*(Updates!$F$2:$F$99&lt;&gt;"Completed")*(Updates!$F$2:$F$99&lt;&gt;"Cancelled")*(Updates!$F$2:$F$99&lt;&gt;"Postponed")),Updates!$C$2:$C$99),"TBD")</f>
+        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$98=A3)*(Updates!$F$2:$F$98&lt;&gt;"Completed")*(Updates!$F$2:$F$98&lt;&gt;"Cancelled")*(Updates!$F$2:$F$98&lt;&gt;"Postponed")),Updates!$C$2:$C$98),"TBD")</f>
         <v>46485</v>
       </c>
       <c r="H3" t="str">
-        <f>IF(G3="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A3)*(Updates!$C$2:$C$99=G3)),Updates!$D$2:$D$99),"TBD"))</f>
+        <f>IF(G3="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$98=A3)*(Updates!$C$2:$C$98=G3)),Updates!$D$2:$D$98),"TBD"))</f>
         <v>South Africa</v>
       </c>
     </row>
@@ -5830,32 +5761,32 @@
         <v>35</v>
       </c>
       <c r="B4" t="str">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A4),Updates!$L$2:$L$99),VLOOKUP(A4,Baseline!$A$2:$H$10,4,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A4),Updates!$L$2:$L$98),VLOOKUP(A4,Baseline!$A$2:$H$10,4,FALSE))</f>
+        <v>Australia</v>
+      </c>
+      <c r="C4" s="4">
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A4),Updates!$M$2:$M$98),VLOOKUP(A4,Baseline!$A$2:$H$10,5,FALSE))</f>
+        <v>46187</v>
+      </c>
+      <c r="D4">
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A4),Updates!$N$2:$N$98),VLOOKUP(A4,Baseline!$A$2:$H$10,6,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A4),Updates!$O$2:$O$98),VLOOKUP(A4,Baseline!$A$2:$H$10,7,FALSE))</f>
+        <v>358</v>
+      </c>
+      <c r="F4">
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A4),Updates!$P$2:$P$98),VLOOKUP(A4,Baseline!$A$2:$H$10,8,FALSE))</f>
+        <v>596</v>
+      </c>
+      <c r="G4" s="4">
+        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$98=A4)*(Updates!$F$2:$F$98&lt;&gt;"Completed")*(Updates!$F$2:$F$98&lt;&gt;"Cancelled")*(Updates!$F$2:$F$98&lt;&gt;"Postponed")),Updates!$C$2:$C$98),"TBD")</f>
+        <v>46280</v>
+      </c>
+      <c r="H4" t="str">
+        <f>IF(G4="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$98=A4)*(Updates!$C$2:$C$98=G4)),Updates!$D$2:$D$98),"TBD"))</f>
         <v>Zimbabwe</v>
-      </c>
-      <c r="C4" s="4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A4),Updates!$M$2:$M$99),VLOOKUP(A4,Baseline!$A$2:$H$10,5,FALSE))</f>
-        <v>46280</v>
-      </c>
-      <c r="D4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A4),Updates!$N$2:$N$99),VLOOKUP(A4,Baseline!$A$2:$H$10,6,FALSE))</f>
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A4),Updates!$O$2:$O$99),VLOOKUP(A4,Baseline!$A$2:$H$10,7,FALSE))</f>
-        <v>359</v>
-      </c>
-      <c r="F4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A4),Updates!$P$2:$P$99),VLOOKUP(A4,Baseline!$A$2:$H$10,8,FALSE))</f>
-        <v>597</v>
-      </c>
-      <c r="G4" s="4" t="str">
-        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A4)*(Updates!$F$2:$F$99&lt;&gt;"Completed")*(Updates!$F$2:$F$99&lt;&gt;"Cancelled")*(Updates!$F$2:$F$99&lt;&gt;"Postponed")),Updates!$C$2:$C$99),"TBD")</f>
-        <v>TBD</v>
-      </c>
-      <c r="H4" t="str">
-        <f>IF(G4="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A4)*(Updates!$C$2:$C$99=G4)),Updates!$D$2:$D$99),"TBD"))</f>
-        <v>TBD</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -5863,31 +5794,31 @@
         <v>37</v>
       </c>
       <c r="B5" t="str">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A5),Updates!$L$2:$L$99),VLOOKUP(A5,Baseline!$A$2:$H$10,4,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A5),Updates!$L$2:$L$98),VLOOKUP(A5,Baseline!$A$2:$H$10,4,FALSE))</f>
         <v>Australia</v>
       </c>
       <c r="C5" s="4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A5),Updates!$M$2:$M$99),VLOOKUP(A5,Baseline!$A$2:$H$10,5,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A5),Updates!$M$2:$M$98),VLOOKUP(A5,Baseline!$A$2:$H$10,5,FALSE))</f>
         <v>46077</v>
       </c>
       <c r="D5">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A5),Updates!$N$2:$N$99),VLOOKUP(A5,Baseline!$A$2:$H$10,6,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A5),Updates!$N$2:$N$98),VLOOKUP(A5,Baseline!$A$2:$H$10,6,FALSE))</f>
         <v>5</v>
       </c>
       <c r="E5">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A5),Updates!$O$2:$O$99),VLOOKUP(A5,Baseline!$A$2:$H$10,7,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A5),Updates!$O$2:$O$98),VLOOKUP(A5,Baseline!$A$2:$H$10,7,FALSE))</f>
         <v>120</v>
       </c>
       <c r="F5">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A5),Updates!$P$2:$P$99),VLOOKUP(A5,Baseline!$A$2:$H$10,8,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A5),Updates!$P$2:$P$98),VLOOKUP(A5,Baseline!$A$2:$H$10,8,FALSE))</f>
         <v>251</v>
       </c>
       <c r="G5" s="4">
-        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A5)*(Updates!$F$2:$F$99&lt;&gt;"Completed")*(Updates!$F$2:$F$99&lt;&gt;"Cancelled")*(Updates!$F$2:$F$99&lt;&gt;"Postponed")),Updates!$C$2:$C$99),"TBD")</f>
+        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$98=A5)*(Updates!$F$2:$F$98&lt;&gt;"Completed")*(Updates!$F$2:$F$98&lt;&gt;"Cancelled")*(Updates!$F$2:$F$98&lt;&gt;"Postponed")),Updates!$C$2:$C$98),"TBD")</f>
         <v>46304</v>
       </c>
       <c r="H5" t="str">
-        <f>IF(G5="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A5)*(Updates!$C$2:$C$99=G5)),Updates!$D$2:$D$99),"TBD"))</f>
+        <f>IF(G5="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$98=A5)*(Updates!$C$2:$C$98=G5)),Updates!$D$2:$D$98),"TBD"))</f>
         <v>Bangladesh</v>
       </c>
     </row>
@@ -5896,31 +5827,31 @@
         <v>39</v>
       </c>
       <c r="B6" t="str">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A6),Updates!$L$2:$L$99),VLOOKUP(A6,Baseline!$A$2:$H$10,4,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A6),Updates!$L$2:$L$98),VLOOKUP(A6,Baseline!$A$2:$H$10,4,FALSE))</f>
         <v>Ireland</v>
       </c>
       <c r="C6" s="4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A6),Updates!$M$2:$M$99),VLOOKUP(A6,Baseline!$A$2:$H$10,5,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A6),Updates!$M$2:$M$98),VLOOKUP(A6,Baseline!$A$2:$H$10,5,FALSE))</f>
         <v>46199</v>
       </c>
       <c r="D6">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A6),Updates!$N$2:$N$99),VLOOKUP(A6,Baseline!$A$2:$H$10,6,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A6),Updates!$N$2:$N$98),VLOOKUP(A6,Baseline!$A$2:$H$10,6,FALSE))</f>
         <v>1</v>
       </c>
       <c r="E6">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A6),Updates!$O$2:$O$99),VLOOKUP(A6,Baseline!$A$2:$H$10,7,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A6),Updates!$O$2:$O$98),VLOOKUP(A6,Baseline!$A$2:$H$10,7,FALSE))</f>
         <v>89</v>
       </c>
       <c r="F6">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A6),Updates!$P$2:$P$99),VLOOKUP(A6,Baseline!$A$2:$H$10,8,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A6),Updates!$P$2:$P$98),VLOOKUP(A6,Baseline!$A$2:$H$10,8,FALSE))</f>
         <v>152</v>
       </c>
       <c r="G6" s="4" t="str">
-        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A6)*(Updates!$F$2:$F$99&lt;&gt;"Completed")*(Updates!$F$2:$F$99&lt;&gt;"Cancelled")*(Updates!$F$2:$F$99&lt;&gt;"Postponed")),Updates!$C$2:$C$99),"TBD")</f>
+        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$98=A6)*(Updates!$F$2:$F$98&lt;&gt;"Completed")*(Updates!$F$2:$F$98&lt;&gt;"Cancelled")*(Updates!$F$2:$F$98&lt;&gt;"Postponed")),Updates!$C$2:$C$98),"TBD")</f>
         <v>TBD</v>
       </c>
       <c r="H6" t="str">
-        <f>IF(G6="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A6)*(Updates!$C$2:$C$99=G6)),Updates!$D$2:$D$99),"TBD"))</f>
+        <f>IF(G6="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$98=A6)*(Updates!$C$2:$C$98=G6)),Updates!$D$2:$D$98),"TBD"))</f>
         <v>TBD</v>
       </c>
     </row>
@@ -5929,31 +5860,31 @@
         <v>42</v>
       </c>
       <c r="B7" t="str">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A7),Updates!$L$2:$L$99),VLOOKUP(A7,Baseline!$A$2:$H$10,4,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A7),Updates!$L$2:$L$98),VLOOKUP(A7,Baseline!$A$2:$H$10,4,FALSE))</f>
         <v>Australia</v>
       </c>
       <c r="C7" s="4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A7),Updates!$M$2:$M$99),VLOOKUP(A7,Baseline!$A$2:$H$10,5,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A7),Updates!$M$2:$M$98),VLOOKUP(A7,Baseline!$A$2:$H$10,5,FALSE))</f>
         <v>46186</v>
       </c>
       <c r="D7">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A7),Updates!$N$2:$N$99),VLOOKUP(A7,Baseline!$A$2:$H$10,6,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A7),Updates!$N$2:$N$98),VLOOKUP(A7,Baseline!$A$2:$H$10,6,FALSE))</f>
         <v>6</v>
       </c>
       <c r="E7">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A7),Updates!$O$2:$O$99),VLOOKUP(A7,Baseline!$A$2:$H$10,7,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A7),Updates!$O$2:$O$98),VLOOKUP(A7,Baseline!$A$2:$H$10,7,FALSE))</f>
         <v>76</v>
       </c>
       <c r="F7">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A7),Updates!$P$2:$P$99),VLOOKUP(A7,Baseline!$A$2:$H$10,8,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A7),Updates!$P$2:$P$98),VLOOKUP(A7,Baseline!$A$2:$H$10,8,FALSE))</f>
         <v>139</v>
       </c>
       <c r="G7" s="4">
-        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A7)*(Updates!$F$2:$F$99&lt;&gt;"Completed")*(Updates!$F$2:$F$99&lt;&gt;"Cancelled")*(Updates!$F$2:$F$99&lt;&gt;"Postponed")),Updates!$C$2:$C$99),"TBD")</f>
+        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$98=A7)*(Updates!$F$2:$F$98&lt;&gt;"Completed")*(Updates!$F$2:$F$98&lt;&gt;"Cancelled")*(Updates!$F$2:$F$98&lt;&gt;"Postponed")),Updates!$C$2:$C$98),"TBD")</f>
         <v>46313</v>
       </c>
       <c r="H7" t="str">
-        <f>IF(G7="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A7)*(Updates!$C$2:$C$99=G7)),Updates!$D$2:$D$99),"TBD"))</f>
+        <f>IF(G7="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$98=A7)*(Updates!$C$2:$C$98=G7)),Updates!$D$2:$D$98),"TBD"))</f>
         <v>New Zealand</v>
       </c>
     </row>
@@ -5962,31 +5893,31 @@
         <v>44</v>
       </c>
       <c r="B8" t="str">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A8),Updates!$L$2:$L$99),VLOOKUP(A8,Baseline!$A$2:$H$10,4,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A8),Updates!$L$2:$L$98),VLOOKUP(A8,Baseline!$A$2:$H$10,4,FALSE))</f>
         <v>Royal Challengers Bengaluru</v>
       </c>
       <c r="C8" s="4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A8),Updates!$M$2:$M$99),VLOOKUP(A8,Baseline!$A$2:$H$10,5,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A8),Updates!$M$2:$M$98),VLOOKUP(A8,Baseline!$A$2:$H$10,5,FALSE))</f>
         <v>46173</v>
       </c>
       <c r="D8">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A8),Updates!$N$2:$N$99),VLOOKUP(A8,Baseline!$A$2:$H$10,6,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A8),Updates!$N$2:$N$98),VLOOKUP(A8,Baseline!$A$2:$H$10,6,FALSE))</f>
         <v>0</v>
       </c>
       <c r="E8">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A8),Updates!$O$2:$O$99),VLOOKUP(A8,Baseline!$A$2:$H$10,7,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A8),Updates!$O$2:$O$98),VLOOKUP(A8,Baseline!$A$2:$H$10,7,FALSE))</f>
         <v>150</v>
       </c>
       <c r="F8">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A8),Updates!$P$2:$P$99),VLOOKUP(A8,Baseline!$A$2:$H$10,8,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A8),Updates!$P$2:$P$98),VLOOKUP(A8,Baseline!$A$2:$H$10,8,FALSE))</f>
         <v>125</v>
       </c>
       <c r="G8" s="4" t="str">
-        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A8)*(Updates!$F$2:$F$99&lt;&gt;"Completed")*(Updates!$F$2:$F$99&lt;&gt;"Cancelled")*(Updates!$F$2:$F$99&lt;&gt;"Postponed")),Updates!$C$2:$C$99),"TBD")</f>
+        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$98=A8)*(Updates!$F$2:$F$98&lt;&gt;"Completed")*(Updates!$F$2:$F$98&lt;&gt;"Cancelled")*(Updates!$F$2:$F$98&lt;&gt;"Postponed")),Updates!$C$2:$C$98),"TBD")</f>
         <v>TBD</v>
       </c>
       <c r="H8" t="str">
-        <f>IF(G8="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A8)*(Updates!$C$2:$C$99=G8)),Updates!$D$2:$D$99),"TBD"))</f>
+        <f>IF(G8="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$98=A8)*(Updates!$C$2:$C$98=G8)),Updates!$D$2:$D$98),"TBD"))</f>
         <v>TBD</v>
       </c>
     </row>
@@ -5995,31 +5926,31 @@
         <v>47</v>
       </c>
       <c r="B9" t="str">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A9),Updates!$L$2:$L$99),VLOOKUP(A9,Baseline!$A$2:$H$10,4,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A9),Updates!$L$2:$L$98),VLOOKUP(A9,Baseline!$A$2:$H$10,4,FALSE))</f>
         <v>Bayern München</v>
       </c>
       <c r="C9" s="4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A9),Updates!$M$2:$M$99),VLOOKUP(A9,Baseline!$A$2:$H$10,5,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A9),Updates!$M$2:$M$98),VLOOKUP(A9,Baseline!$A$2:$H$10,5,FALSE))</f>
         <v>46081</v>
       </c>
       <c r="D9">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A9),Updates!$N$2:$N$99),VLOOKUP(A9,Baseline!$A$2:$H$10,6,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A9),Updates!$N$2:$N$98),VLOOKUP(A9,Baseline!$A$2:$H$10,6,FALSE))</f>
         <v>11</v>
       </c>
       <c r="E9">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A9),Updates!$O$2:$O$99),VLOOKUP(A9,Baseline!$A$2:$H$10,7,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A9),Updates!$O$2:$O$98),VLOOKUP(A9,Baseline!$A$2:$H$10,7,FALSE))</f>
         <v>681</v>
       </c>
       <c r="F9">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A9),Updates!$P$2:$P$99),VLOOKUP(A9,Baseline!$A$2:$H$10,8,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A9),Updates!$P$2:$P$98),VLOOKUP(A9,Baseline!$A$2:$H$10,8,FALSE))</f>
         <v>1443</v>
       </c>
       <c r="G9" s="4">
-        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A9)*(Updates!$F$2:$F$99&lt;&gt;"Completed")*(Updates!$F$2:$F$99&lt;&gt;"Cancelled")*(Updates!$F$2:$F$99&lt;&gt;"Postponed")),Updates!$C$2:$C$99),"TBD")</f>
+        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$98=A9)*(Updates!$F$2:$F$98&lt;&gt;"Completed")*(Updates!$F$2:$F$98&lt;&gt;"Cancelled")*(Updates!$F$2:$F$98&lt;&gt;"Postponed")),Updates!$C$2:$C$98),"TBD")</f>
         <v>46269</v>
       </c>
       <c r="H9" t="str">
-        <f>IF(G9="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A9)*(Updates!$C$2:$C$99=G9)),Updates!$D$2:$D$99),"TBD"))</f>
+        <f>IF(G9="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$98=A9)*(Updates!$C$2:$C$98=G9)),Updates!$D$2:$D$98),"TBD"))</f>
         <v>Schalke FC</v>
       </c>
     </row>
@@ -6028,31 +5959,31 @@
         <v>51</v>
       </c>
       <c r="B10" t="str">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A10),Updates!$L$2:$L$99),VLOOKUP(A10,Baseline!$A$2:$H$10,4,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A10),Updates!$L$2:$L$98),VLOOKUP(A10,Baseline!$A$2:$H$10,4,FALSE))</f>
         <v>Bayern München</v>
       </c>
       <c r="C10" s="4">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A10),Updates!$M$2:$M$99),VLOOKUP(A10,Baseline!$A$2:$H$10,5,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A10),Updates!$M$2:$M$98),VLOOKUP(A10,Baseline!$A$2:$H$10,5,FALSE))</f>
         <v>45730</v>
       </c>
       <c r="D10">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A10),Updates!$N$2:$N$99),VLOOKUP(A10,Baseline!$A$2:$H$10,6,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A10),Updates!$N$2:$N$98),VLOOKUP(A10,Baseline!$A$2:$H$10,6,FALSE))</f>
         <v>32</v>
       </c>
       <c r="E10">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A10),Updates!$O$2:$O$99),VLOOKUP(A10,Baseline!$A$2:$H$10,7,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A10),Updates!$O$2:$O$98),VLOOKUP(A10,Baseline!$A$2:$H$10,7,FALSE))</f>
         <v>113</v>
       </c>
       <c r="F10">
-        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$99=A10),Updates!$P$2:$P$99),VLOOKUP(A10,Baseline!$A$2:$H$10,8,FALSE))</f>
+        <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$98=A10),Updates!$P$2:$P$98),VLOOKUP(A10,Baseline!$A$2:$H$10,8,FALSE))</f>
         <v>655</v>
       </c>
       <c r="G10" s="4">
-        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A10)*(Updates!$F$2:$F$99&lt;&gt;"Completed")*(Updates!$F$2:$F$99&lt;&gt;"Cancelled")*(Updates!$F$2:$F$99&lt;&gt;"Postponed")),Updates!$C$2:$C$99),"TBD")</f>
+        <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$98=A10)*(Updates!$F$2:$F$98&lt;&gt;"Completed")*(Updates!$F$2:$F$98&lt;&gt;"Cancelled")*(Updates!$F$2:$F$98&lt;&gt;"Postponed")),Updates!$C$2:$C$98),"TBD")</f>
         <v>46265</v>
       </c>
       <c r="H10" t="str">
-        <f>IF(G10="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$99=A10)*(Updates!$C$2:$C$99=G10)),Updates!$D$2:$D$99),"TBD"))</f>
+        <f>IF(G10="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$98=A10)*(Updates!$C$2:$C$98=G10)),Updates!$D$2:$D$98),"TBD"))</f>
         <v>1. FSV Mainz 05</v>
       </c>
     </row>
@@ -6171,31 +6102,31 @@
       </c>
       <c r="B4" t="str">
         <f>Dashboard!B4</f>
-        <v>Zimbabwe</v>
+        <v>Australia</v>
       </c>
       <c r="C4" s="9">
         <f>Dashboard!C4</f>
-        <v>46280</v>
+        <v>46187</v>
       </c>
       <c r="D4">
         <f>Dashboard!D4</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <f>Dashboard!E4</f>
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F4">
         <f>Dashboard!F4</f>
-        <v>597</v>
-      </c>
-      <c r="G4" s="9" t="str">
+        <v>596</v>
+      </c>
+      <c r="G4" s="9">
         <f>Dashboard!G4</f>
-        <v>TBD</v>
+        <v>46280</v>
       </c>
       <c r="H4" t="str">
         <f>Dashboard!H4</f>
-        <v>TBD</v>
+        <v>Zimbabwe</v>
       </c>
     </row>
     <row r="5" spans="1:8">
